--- a/data/美股PE監看表.xlsx
+++ b/data/美股PE監看表.xlsx
@@ -10,8 +10,9 @@
     <sheet name="監看表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="買進_成長未反映" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="買進_未來便宜" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="警示_未來過熱" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="警示_未來偏貴" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="買進_便宜" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="警示_未來過熱" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="警示_未來偏貴" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q96"/>
+  <dimension ref="A1:S96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,30 +479,40 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>漲跌%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>前次股價</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>ROE%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收CAGR%</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>市值(億美)</t>
         </is>
@@ -534,7 +545,9 @@
       <c r="F2" t="n">
         <v>377.27</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>87.5</v>
+      </c>
       <c r="H2" t="n">
         <v>33.8</v>
       </c>
@@ -550,17 +563,23 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="N2" t="n">
         <v>21.1</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>1.56</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>15.4</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -589,7 +608,9 @@
       <c r="F3" t="n">
         <v>283.78</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>34.2</v>
+      </c>
       <c r="H3" t="n">
         <v>22.1</v>
       </c>
@@ -605,17 +626,23 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>283.78</v>
+      </c>
+      <c r="N3" t="n">
         <v>146.7</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>3.3</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,7 +671,9 @@
       <c r="F4" t="n">
         <v>379.09</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>71.3</v>
+      </c>
       <c r="H4" t="n">
         <v>28.7</v>
       </c>
@@ -660,17 +689,23 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="N4" t="n">
         <v>65.8</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>1.15</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>6</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -699,7 +734,9 @@
       <c r="F5" t="n">
         <v>626.84</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>58.6</v>
+      </c>
       <c r="H5" t="n">
         <v>27.6</v>
       </c>
@@ -715,17 +752,23 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>626.84</v>
+      </c>
+      <c r="N5" t="n">
         <v>39.8</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>1.14</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>5.3</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -754,7 +797,9 @@
       <c r="F6" t="n">
         <v>223</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>105.7</v>
+      </c>
       <c r="H6" t="n">
         <v>34.8</v>
       </c>
@@ -770,21 +815,27 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>223</v>
+      </c>
+      <c r="N6" t="n">
         <v>15.6</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>1.69</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>2.6</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -813,7 +864,9 @@
       <c r="F7" t="n">
         <v>586.45</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>31.4</v>
+      </c>
       <c r="H7" t="n">
         <v>11.5</v>
       </c>
@@ -829,21 +882,27 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>586.45</v>
+      </c>
+      <c r="N7" t="n">
         <v>91.90000000000001</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.91</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>-13.4</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -872,7 +931,9 @@
       <c r="F8" t="n">
         <v>479.5</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>155.2</v>
+      </c>
       <c r="H8" t="n">
         <v>33.6</v>
       </c>
@@ -886,21 +947,27 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="N8" t="n">
         <v>15.7</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>6.54</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>7.1</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -929,7 +996,9 @@
       <c r="F9" t="n">
         <v>380.56</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>166.2</v>
+      </c>
       <c r="H9" t="n">
         <v>30.7</v>
       </c>
@@ -941,21 +1010,27 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="N9" t="n">
         <v>5.3</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>12.84</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>16.9</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -984,7 +1059,9 @@
       <c r="F10" t="n">
         <v>2090.71</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>68.59999999999999</v>
+      </c>
       <c r="H10" t="n">
         <v>154.5</v>
       </c>
@@ -996,25 +1073,31 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2090.71</v>
+      </c>
+      <c r="N10" t="n">
         <v>42.3</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>-0.05</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>-9</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>⚠️現金流為負(含金量-0.05)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1043,7 +1126,9 @@
       <c r="F11" t="n">
         <v>379.71</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>315.5</v>
+      </c>
       <c r="H11" t="n">
         <v>41.9</v>
       </c>
@@ -1057,25 +1142,31 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="N11" t="n">
         <v>4.8</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>3.89</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>15.2</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>⚠️EPS落後營收(EPS3y -34&lt;營收CAGR 15×50%) | ⚠️ROE滑落(5&lt;5年均17×67%)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1104,7 +1195,9 @@
       <c r="F12" t="n">
         <v>248.64</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>69.90000000000001</v>
+      </c>
       <c r="H12" t="n">
         <v>32.6</v>
       </c>
@@ -1120,21 +1213,27 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>248.64</v>
+      </c>
+      <c r="N12" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>15.1</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>🟡ROE弱化(89&lt;5年均117×80%)</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>3247.9</v>
       </c>
     </row>
@@ -1165,7 +1264,9 @@
       <c r="F13" t="n">
         <v>952.54</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>47.8</v>
+      </c>
       <c r="H13" t="n">
         <v>33.4</v>
       </c>
@@ -1181,17 +1282,23 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>952.54</v>
+      </c>
+      <c r="N13" t="n">
         <v>28.3</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>1.65</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>8.9</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1220,7 +1327,9 @@
       <c r="F14" t="n">
         <v>10.78</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>13.5</v>
+      </c>
       <c r="H14" t="n">
         <v>10.9</v>
       </c>
@@ -1236,17 +1345,23 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="N14" t="n">
         <v>31.8</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>1.22</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>5.4</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1275,7 +1390,9 @@
       <c r="F15" t="n">
         <v>303.95</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>74.5</v>
+      </c>
       <c r="H15" t="n">
         <v>19.1</v>
       </c>
@@ -1287,21 +1404,27 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>303.95</v>
+      </c>
+      <c r="N15" t="n">
         <v>42.1</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>1.59</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>19.6</v>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1330,7 +1453,9 @@
       <c r="F16" t="n">
         <v>816.98</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>131.6</v>
+      </c>
       <c r="H16" t="n">
         <v>18.4</v>
       </c>
@@ -1344,21 +1469,27 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>816.98</v>
+      </c>
+      <c r="N16" t="n">
         <v>30.7</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>4.88</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>-1</v>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1387,7 +1518,9 @@
       <c r="F17" t="n">
         <v>266.77</v>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>90.8</v>
+      </c>
       <c r="H17" t="n">
         <v>28.4</v>
       </c>
@@ -1399,21 +1532,27 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>266.77</v>
+      </c>
+      <c r="N17" t="n">
         <v>16.8</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.66</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>16.4</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1442,7 +1581,9 @@
       <c r="F18" t="n">
         <v>498.66</v>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>14.8</v>
+      </c>
       <c r="H18" t="n">
         <v>23</v>
       </c>
@@ -1454,21 +1595,27 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>498.66</v>
+      </c>
+      <c r="N18" t="n">
         <v>10.3</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>7.7</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1497,7 +1644,9 @@
       <c r="F19" t="n">
         <v>31.34</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>20.9</v>
+      </c>
       <c r="H19" t="n">
         <v>16.8</v>
       </c>
@@ -1513,17 +1662,23 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>31.34</v>
+      </c>
+      <c r="N19" t="n">
         <v>90.8</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>1.37</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>7.3</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>550.4</v>
       </c>
     </row>
@@ -1554,7 +1709,9 @@
       <c r="F20" t="n">
         <v>488.58</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>59.1</v>
+      </c>
       <c r="H20" t="n">
         <v>37.6</v>
       </c>
@@ -1570,17 +1727,23 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>488.58</v>
+      </c>
+      <c r="N20" t="n">
         <v>21.2</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.95</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>20.6</v>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>155.3</v>
       </c>
     </row>
@@ -1611,7 +1774,9 @@
       <c r="F21" t="n">
         <v>997.47</v>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>49.4</v>
+      </c>
       <c r="H21" t="n">
         <v>26.3</v>
       </c>
@@ -1627,17 +1792,23 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>997.47</v>
+      </c>
+      <c r="N21" t="n">
         <v>47.5</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>1.32</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>7.3</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1666,7 +1837,9 @@
       <c r="F22" t="n">
         <v>101.59</v>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>20.9</v>
+      </c>
       <c r="H22" t="n">
         <v>14.5</v>
       </c>
@@ -1682,17 +1855,23 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>101.59</v>
+      </c>
+      <c r="N22" t="n">
         <v>24.5</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>1.52</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>11</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1721,7 +1900,9 @@
       <c r="F23" t="n">
         <v>128.98</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>10.2</v>
+      </c>
       <c r="H23" t="n">
         <v>6.9</v>
       </c>
@@ -1737,17 +1918,23 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>128.98</v>
+      </c>
+      <c r="N23" t="n">
         <v>25</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>1.49</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>8.4</v>
       </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1776,7 +1963,9 @@
       <c r="F24" t="n">
         <v>105.73</v>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>9.5</v>
+      </c>
       <c r="H24" t="n">
         <v>14.4</v>
       </c>
@@ -1790,21 +1979,27 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>105.73</v>
+      </c>
+      <c r="N24" t="n">
         <v>35.2</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>1.89</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1833,7 +2028,9 @@
       <c r="F25" t="n">
         <v>232.69</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>27.4</v>
+      </c>
       <c r="H25" t="n">
         <v>12</v>
       </c>
@@ -1845,21 +2042,27 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>232.69</v>
+      </c>
+      <c r="N25" t="n">
         <v>23.3</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>1.8</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>11.1</v>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1888,7 +2091,9 @@
       <c r="F26" t="n">
         <v>368.34</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>35.8</v>
+      </c>
       <c r="H26" t="n">
         <v>26.8</v>
       </c>
@@ -1904,17 +2109,23 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>368.34</v>
+      </c>
+      <c r="N26" t="n">
         <v>41.9</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>2.62</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>13.7</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
         <v>650.2</v>
       </c>
     </row>
@@ -1945,7 +2156,9 @@
       <c r="F27" t="n">
         <v>151.35</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>58.2</v>
+      </c>
       <c r="H27" t="n">
         <v>45.8</v>
       </c>
@@ -1961,17 +2174,23 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>151.35</v>
+      </c>
+      <c r="N27" t="n">
         <v>155.7</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>1.4</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>19.4</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
         <v>1108.9</v>
       </c>
     </row>
@@ -2002,7 +2221,9 @@
       <c r="F28" t="n">
         <v>223.55</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>20.8</v>
+      </c>
       <c r="H28" t="n">
         <v>16.8</v>
       </c>
@@ -2018,17 +2239,23 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>223.55</v>
+      </c>
+      <c r="N28" t="n">
         <v>68.7</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>1.21</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
         <v>893.6</v>
       </c>
     </row>
@@ -2059,7 +2286,9 @@
       <c r="F29" t="n">
         <v>1794.62</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>61</v>
+      </c>
       <c r="H29" t="n">
         <v>26.5</v>
       </c>
@@ -2075,17 +2304,23 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1794.62</v>
+      </c>
+      <c r="N29" t="n">
         <v>52</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>1.27</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>15.1</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
         <v>6916.8</v>
       </c>
     </row>
@@ -2116,7 +2351,9 @@
       <c r="F30" t="n">
         <v>336.23</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>29.3</v>
+      </c>
       <c r="H30" t="n">
         <v>17.8</v>
       </c>
@@ -2132,17 +2369,23 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>336.23</v>
+      </c>
+      <c r="N30" t="n">
         <v>58.9</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>1.15</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>13.5</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
         <v>6444.9</v>
       </c>
     </row>
@@ -2173,7 +2416,9 @@
       <c r="F31" t="n">
         <v>283.65</v>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>38.1</v>
+      </c>
       <c r="H31" t="n">
         <v>26.3</v>
       </c>
@@ -2189,21 +2434,27 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>283.65</v>
+      </c>
+      <c r="N31" t="n">
         <v>21.7</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>1.42</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>6</v>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
         <v>798.3</v>
       </c>
     </row>
@@ -2234,7 +2485,9 @@
       <c r="F32" t="n">
         <v>70.53</v>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>34.1</v>
+      </c>
       <c r="H32" t="n">
         <v>19.9</v>
       </c>
@@ -2250,17 +2503,23 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="N32" t="n">
         <v>11.3</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>1.63</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>15.1</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2289,7 +2548,9 @@
       <c r="F33" t="n">
         <v>115.69</v>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>40.6</v>
+      </c>
       <c r="H33" t="n">
         <v>28.5</v>
       </c>
@@ -2305,17 +2566,23 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>115.69</v>
+      </c>
+      <c r="N33" t="n">
         <v>24.3</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>1.9</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>5.6</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2344,7 +2611,9 @@
       <c r="F34" t="n">
         <v>106.34</v>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>23.3</v>
+      </c>
       <c r="H34" t="n">
         <v>16.9</v>
       </c>
@@ -2360,17 +2629,23 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>106.34</v>
+      </c>
+      <c r="N34" t="n">
         <v>21.3</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>1.23</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>18.5</v>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
         <v>30.5</v>
       </c>
     </row>
@@ -2401,7 +2676,9 @@
       <c r="F35" t="n">
         <v>113.32</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>28.6</v>
+      </c>
       <c r="H35" t="n">
         <v>21.8</v>
       </c>
@@ -2417,17 +2694,23 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>113.32</v>
+      </c>
+      <c r="N35" t="n">
         <v>21.3</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>1.29</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>18.3</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
         <v>514.6</v>
       </c>
     </row>
@@ -2458,7 +2741,9 @@
       <c r="F36" t="n">
         <v>550.25</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>19.7</v>
+      </c>
       <c r="H36" t="n">
         <v>9.800000000000001</v>
       </c>
@@ -2474,17 +2759,23 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>550.25</v>
+      </c>
+      <c r="N36" t="n">
         <v>33.2</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>1.92</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>14.3</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
         <v>13967.7</v>
       </c>
     </row>
@@ -2515,7 +2806,9 @@
       <c r="F37" t="n">
         <v>334.69</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>25.5</v>
+      </c>
       <c r="H37" t="n">
         <v>13.9</v>
       </c>
@@ -2531,17 +2824,23 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>334.69</v>
+      </c>
+      <c r="N37" t="n">
         <v>39</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>1.25</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>11.8</v>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
         <v>40660.1</v>
       </c>
     </row>
@@ -2572,7 +2871,9 @@
       <c r="F38" t="n">
         <v>328.43</v>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>14.4</v>
+      </c>
       <c r="H38" t="n">
         <v>14.3</v>
       </c>
@@ -2588,17 +2889,23 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>328.43</v>
+      </c>
+      <c r="N38" t="n">
         <v>28</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>2.07</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>30.1</v>
       </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
         <v>75.7</v>
       </c>
     </row>
@@ -2629,7 +2936,9 @@
       <c r="F39" t="n">
         <v>200.29</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>19.3</v>
+      </c>
       <c r="H39" t="n">
         <v>12.4</v>
       </c>
@@ -2645,17 +2954,23 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>200.29</v>
+      </c>
+      <c r="N39" t="n">
         <v>24.4</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>1.25</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>12.6</v>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
         <v>290.5</v>
       </c>
     </row>
@@ -2686,7 +3001,9 @@
       <c r="F40" t="n">
         <v>70.14</v>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>29.2</v>
+      </c>
       <c r="H40" t="n">
         <v>13.9</v>
       </c>
@@ -2702,17 +3019,23 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="N40" t="n">
         <v>33.8</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>1.72</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>17.5</v>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
         <v>270.7</v>
       </c>
     </row>
@@ -2743,7 +3066,9 @@
       <c r="F41" t="n">
         <v>168.52</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>25.1</v>
+      </c>
       <c r="H41" t="n">
         <v>11.1</v>
       </c>
@@ -2759,17 +3084,23 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>168.52</v>
+      </c>
+      <c r="N41" t="n">
         <v>21.6</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>1.64</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>26</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
         <v>169.4</v>
       </c>
     </row>
@@ -2800,7 +3131,9 @@
       <c r="F42" t="n">
         <v>372.97</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>22.1</v>
+      </c>
       <c r="H42" t="n">
         <v>11.2</v>
       </c>
@@ -2816,17 +3149,23 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="N42" t="n">
         <v>33.1</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>1.34</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>13.8</v>
       </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="n">
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
         <v>27705.8</v>
       </c>
     </row>
@@ -2857,7 +3196,9 @@
       <c r="F43" t="n">
         <v>432.35</v>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>31.5</v>
+      </c>
       <c r="H43" t="n">
         <v>0.7</v>
       </c>
@@ -2873,17 +3214,23 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>432.35</v>
+      </c>
+      <c r="N43" t="n">
         <v>36.9</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>1.37</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>24.8</v>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="n">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
         <v>22423.7</v>
       </c>
     </row>
@@ -2914,7 +3261,9 @@
       <c r="F44" t="n">
         <v>157.6</v>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>53.2</v>
+      </c>
       <c r="H44" t="n">
         <v>22.2</v>
       </c>
@@ -2930,17 +3279,23 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="N44" t="n">
         <v>30.6</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>1.25</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>32.2</v>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
         <v>1984.5</v>
       </c>
     </row>
@@ -2971,7 +3326,9 @@
       <c r="F45" t="n">
         <v>202.73</v>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H45" t="n">
         <v>5.8</v>
       </c>
@@ -2987,17 +3344,23 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>202.73</v>
+      </c>
+      <c r="N45" t="n">
         <v>62.4</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>1.41</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>10.8</v>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
         <v>805.9</v>
       </c>
     </row>
@@ -3028,7 +3391,9 @@
       <c r="F46" t="n">
         <v>129.18</v>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>14.9</v>
+      </c>
       <c r="H46" t="n">
         <v>9.800000000000001</v>
       </c>
@@ -3044,17 +3409,23 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>129.18</v>
+      </c>
+      <c r="N46" t="n">
         <v>31</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>1.5</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>18.1</v>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="n">
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="n">
         <v>70.5</v>
       </c>
     </row>
@@ -3085,7 +3456,9 @@
       <c r="F47" t="n">
         <v>123.27</v>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>22</v>
+      </c>
       <c r="H47" t="n">
         <v>12.2</v>
       </c>
@@ -3101,17 +3474,23 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>123.27</v>
+      </c>
+      <c r="N47" t="n">
         <v>37.2</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>1.56</v>
       </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
         <v>12.9</v>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="n">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="n">
         <v>43.4</v>
       </c>
     </row>
@@ -3142,7 +3521,9 @@
       <c r="F48" t="n">
         <v>275.86</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>19.4</v>
+      </c>
       <c r="H48" t="n">
         <v>18.7</v>
       </c>
@@ -3158,17 +3539,23 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>275.86</v>
+      </c>
+      <c r="N48" t="n">
         <v>33.4</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>1.34</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>18.3</v>
       </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="n">
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="n">
         <v>71.3</v>
       </c>
     </row>
@@ -3199,7 +3586,9 @@
       <c r="F49" t="n">
         <v>196.26</v>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>28.4</v>
+      </c>
       <c r="H49" t="n">
         <v>10.8</v>
       </c>
@@ -3215,17 +3604,23 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>196.26</v>
+      </c>
+      <c r="N49" t="n">
         <v>49.4</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>2.18</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>13.2</v>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="n">
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="n">
         <v>414.4</v>
       </c>
     </row>
@@ -3256,7 +3651,9 @@
       <c r="F50" t="n">
         <v>44.29</v>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H50" t="n">
         <v>5.8</v>
       </c>
@@ -3272,17 +3669,23 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="N50" t="n">
         <v>25.1</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>1.23</v>
       </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
         <v>6.9</v>
       </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="n">
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="n">
         <v>390.7</v>
       </c>
     </row>
@@ -3313,7 +3716,9 @@
       <c r="F51" t="n">
         <v>65.14</v>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>10</v>
+      </c>
       <c r="H51" t="n">
         <v>9.800000000000001</v>
       </c>
@@ -3329,17 +3734,23 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>65.14</v>
+      </c>
+      <c r="N51" t="n">
         <v>155.3</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>1.28</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>6.4</v>
       </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="n">
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="n">
         <v>147.1</v>
       </c>
     </row>
@@ -3370,7 +3781,9 @@
       <c r="F52" t="n">
         <v>271.63</v>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>23.6</v>
+      </c>
       <c r="H52" t="n">
         <v>21.3</v>
       </c>
@@ -3386,21 +3799,27 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>271.63</v>
+      </c>
+      <c r="N52" t="n">
         <v>35.5</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>1.25</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>4.2</v>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="n">
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="n">
         <v>2553</v>
       </c>
     </row>
@@ -3431,7 +3850,9 @@
       <c r="F53" t="n">
         <v>123.71</v>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>15.2</v>
+      </c>
       <c r="H53" t="n">
         <v>1.4</v>
       </c>
@@ -3447,17 +3868,23 @@
         </is>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>123.71</v>
+      </c>
+      <c r="N53" t="n">
         <v>21.6</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>1.46</v>
       </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
         <v>6.5</v>
       </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="n">
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="n">
         <v>789.8</v>
       </c>
     </row>
@@ -3488,7 +3915,9 @@
       <c r="F54" t="n">
         <v>104.56</v>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>14.8</v>
+      </c>
       <c r="H54" t="n">
         <v>10.4</v>
       </c>
@@ -3504,17 +3933,23 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>104.56</v>
+      </c>
+      <c r="N54" t="n">
         <v>40.8</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>1.15</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>14.7</v>
       </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="n">
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="n">
         <v>145.2</v>
       </c>
     </row>
@@ -3545,7 +3980,9 @@
       <c r="F55" t="n">
         <v>76.55</v>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>7.5</v>
+      </c>
       <c r="H55" t="n">
         <v>0.8</v>
       </c>
@@ -3561,21 +3998,27 @@
         </is>
       </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="N55" t="n">
         <v>24</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>1.09</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>46.4</v>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="n">
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="n">
         <v>1089.6</v>
       </c>
     </row>
@@ -3606,7 +4049,9 @@
       <c r="F56" t="n">
         <v>48.025</v>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H56" t="n">
         <v>1.7</v>
       </c>
@@ -3622,17 +4067,23 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>48.025</v>
+      </c>
+      <c r="N56" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>1.16</v>
       </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
         <v>21.7</v>
       </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="n">
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="n">
         <v>2134.1</v>
       </c>
     </row>
@@ -3663,7 +4114,9 @@
       <c r="F57" t="n">
         <v>54.77</v>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>17.6</v>
+      </c>
       <c r="H57" t="n">
         <v>15</v>
       </c>
@@ -3679,17 +4132,23 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="N57" t="n">
         <v>40.2</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>1.13</v>
       </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
         <v>12.8</v>
       </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="n">
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="n">
         <v>137.7</v>
       </c>
     </row>
@@ -3720,7 +4179,9 @@
       <c r="F58" t="n">
         <v>268.87</v>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>61.8</v>
+      </c>
       <c r="H58" t="n">
         <v>30.5</v>
       </c>
@@ -3736,17 +4197,23 @@
         </is>
       </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>268.87</v>
+      </c>
+      <c r="N58" t="n">
         <v>33.1</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>1.25</v>
       </c>
-      <c r="N58" t="n">
+      <c r="P58" t="n">
         <v>13.5</v>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="n">
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
         <v>1075.8</v>
       </c>
     </row>
@@ -3777,7 +4244,9 @@
       <c r="F59" t="n">
         <v>21.76</v>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>21.8</v>
+      </c>
       <c r="H59" t="n">
         <v>3.7</v>
       </c>
@@ -3793,17 +4262,23 @@
         </is>
       </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="N59" t="n">
         <v>24.2</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>1.88</v>
       </c>
-      <c r="N59" t="n">
+      <c r="P59" t="n">
         <v>33.2</v>
       </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="n">
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
         <v>12286.6</v>
       </c>
     </row>
@@ -3834,7 +4309,9 @@
       <c r="F60" t="n">
         <v>88.56</v>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>22.4</v>
+      </c>
       <c r="H60" t="n">
         <v>15.9</v>
       </c>
@@ -3850,17 +4327,23 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="N60" t="n">
         <v>15.2</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>1.83</v>
       </c>
-      <c r="N60" t="n">
+      <c r="P60" t="n">
         <v>12.6</v>
       </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="n">
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="n">
         <v>1846.8</v>
       </c>
     </row>
@@ -3891,7 +4374,9 @@
       <c r="F61" t="n">
         <v>365.02</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>59</v>
+      </c>
       <c r="H61" t="n">
         <v>10.4</v>
       </c>
@@ -3907,17 +4392,23 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>365.02</v>
+      </c>
+      <c r="N61" t="n">
         <v>36.4</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>1.19</v>
       </c>
-      <c r="N61" t="n">
+      <c r="P61" t="n">
         <v>23.5</v>
       </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="n">
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="n">
         <v>17366.1</v>
       </c>
     </row>
@@ -3948,7 +4439,9 @@
       <c r="F62" t="n">
         <v>163.72</v>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>44.7</v>
+      </c>
       <c r="H62" t="n">
         <v>21.7</v>
       </c>
@@ -3964,17 +4457,23 @@
         </is>
       </c>
       <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>163.72</v>
+      </c>
+      <c r="N62" t="n">
         <v>34.8</v>
       </c>
-      <c r="M62" t="n">
+      <c r="O62" t="n">
         <v>1.26</v>
       </c>
-      <c r="N62" t="n">
+      <c r="P62" t="n">
         <v>20.7</v>
       </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="n">
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="n">
         <v>2014.1</v>
       </c>
     </row>
@@ -4005,7 +4504,9 @@
       <c r="F63" t="n">
         <v>267.72</v>
       </c>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>16.2</v>
+      </c>
       <c r="H63" t="n">
         <v>6.6</v>
       </c>
@@ -4021,17 +4522,23 @@
         </is>
       </c>
       <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>267.72</v>
+      </c>
+      <c r="N63" t="n">
         <v>23.3</v>
       </c>
-      <c r="M63" t="n">
+      <c r="O63" t="n">
         <v>1.6</v>
       </c>
-      <c r="N63" t="n">
+      <c r="P63" t="n">
         <v>18.2</v>
       </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="n">
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+      <c r="S63" t="n">
         <v>732.3</v>
       </c>
     </row>
@@ -4062,7 +4569,9 @@
       <c r="F64" t="n">
         <v>106.35</v>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>22.4</v>
+      </c>
       <c r="H64" t="n">
         <v>11.1</v>
       </c>
@@ -4078,17 +4587,23 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="N64" t="n">
         <v>22.4</v>
       </c>
-      <c r="M64" t="n">
+      <c r="O64" t="n">
         <v>1.84</v>
       </c>
-      <c r="N64" t="n">
+      <c r="P64" t="n">
         <v>25.9</v>
       </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="n">
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+      <c r="S64" t="n">
         <v>56.9</v>
       </c>
     </row>
@@ -4119,7 +4634,9 @@
       <c r="F65" t="n">
         <v>499.02</v>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>28.8</v>
+      </c>
       <c r="H65" t="n">
         <v>14.5</v>
       </c>
@@ -4135,17 +4652,23 @@
         </is>
       </c>
       <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>499.02</v>
+      </c>
+      <c r="N65" t="n">
         <v>206.1</v>
       </c>
-      <c r="M65" t="n">
+      <c r="O65" t="n">
         <v>1.16</v>
       </c>
-      <c r="N65" t="n">
+      <c r="P65" t="n">
         <v>14.8</v>
       </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="n">
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="n">
         <v>4409.3</v>
       </c>
     </row>
@@ -4176,7 +4699,9 @@
       <c r="F66" t="n">
         <v>519.62</v>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>34.3</v>
+      </c>
       <c r="H66" t="n">
         <v>20.7</v>
       </c>
@@ -4192,17 +4717,23 @@
         </is>
       </c>
       <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>519.62</v>
+      </c>
+      <c r="N66" t="n">
         <v>18.5</v>
       </c>
-      <c r="M66" t="n">
+      <c r="O66" t="n">
         <v>1.5</v>
       </c>
-      <c r="N66" t="n">
+      <c r="P66" t="n">
         <v>2.5</v>
       </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="n">
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="n">
         <v>2403.8</v>
       </c>
     </row>
@@ -4233,7 +4764,9 @@
       <c r="F67" t="n">
         <v>133.89</v>
       </c>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="H67" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -4249,17 +4782,23 @@
         </is>
       </c>
       <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>133.89</v>
+      </c>
+      <c r="N67" t="n">
         <v>22</v>
       </c>
-      <c r="M67" t="n">
+      <c r="O67" t="n">
         <v>1.54</v>
       </c>
-      <c r="N67" t="n">
+      <c r="P67" t="n">
         <v>6.9</v>
       </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="n">
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="n">
         <v>367</v>
       </c>
     </row>
@@ -4290,7 +4829,9 @@
       <c r="F68" t="n">
         <v>33.33</v>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>12.5</v>
+      </c>
       <c r="H68" t="n">
         <v>10.6</v>
       </c>
@@ -4306,17 +4847,23 @@
         </is>
       </c>
       <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N68" t="n">
         <v>17.2</v>
       </c>
-      <c r="M68" t="n">
+      <c r="O68" t="n">
         <v>1.41</v>
       </c>
-      <c r="N68" t="n">
+      <c r="P68" t="n">
         <v>5.1</v>
       </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="n">
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="n">
         <v>20.9</v>
       </c>
     </row>
@@ -4347,7 +4894,9 @@
       <c r="F69" t="n">
         <v>145.69</v>
       </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>6</v>
+      </c>
       <c r="H69" t="n">
         <v>4.9</v>
       </c>
@@ -4363,17 +4912,23 @@
         </is>
       </c>
       <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>145.69</v>
+      </c>
+      <c r="N69" t="n">
         <v>20.9</v>
       </c>
-      <c r="M69" t="n">
+      <c r="O69" t="n">
         <v>1.25</v>
       </c>
-      <c r="N69" t="n">
+      <c r="P69" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="n">
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+      <c r="S69" t="n">
         <v>91.2</v>
       </c>
     </row>
@@ -4404,7 +4959,9 @@
       <c r="F70" t="n">
         <v>1675.1</v>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>44.2</v>
+      </c>
       <c r="H70" t="n">
         <v>9.6</v>
       </c>
@@ -4420,21 +4977,27 @@
         </is>
       </c>
       <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1675.1</v>
+      </c>
+      <c r="N70" t="n">
         <v>29.6</v>
       </c>
-      <c r="M70" t="n">
+      <c r="O70" t="n">
         <v>6.07</v>
       </c>
-      <c r="N70" t="n">
+      <c r="P70" t="n">
         <v>42.2</v>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="n">
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="n">
         <v>849.2</v>
       </c>
     </row>
@@ -4465,7 +5028,9 @@
       <c r="F71" t="n">
         <v>97.54000000000001</v>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>7.4</v>
+      </c>
       <c r="H71" t="n">
         <v>9.1</v>
       </c>
@@ -4481,17 +5046,23 @@
         </is>
       </c>
       <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="N71" t="n">
         <v>20.5</v>
       </c>
-      <c r="M71" t="n">
+      <c r="O71" t="n">
         <v>1.4</v>
       </c>
-      <c r="N71" t="n">
+      <c r="P71" t="n">
         <v>22.2</v>
       </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="n">
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="n">
         <v>340.8</v>
       </c>
     </row>
@@ -4522,7 +5093,9 @@
       <c r="F72" t="n">
         <v>340.36</v>
       </c>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>21.2</v>
+      </c>
       <c r="H72" t="n">
         <v>12</v>
       </c>
@@ -4538,17 +5111,23 @@
         </is>
       </c>
       <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>340.36</v>
+      </c>
+      <c r="N72" t="n">
         <v>33.9</v>
       </c>
-      <c r="M72" t="n">
+      <c r="O72" t="n">
         <v>1.7</v>
       </c>
-      <c r="N72" t="n">
+      <c r="P72" t="n">
         <v>16</v>
       </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="n">
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="n">
         <v>2322.4</v>
       </c>
     </row>
@@ -4579,7 +5158,9 @@
       <c r="F73" t="n">
         <v>98.34</v>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>58.2</v>
+      </c>
       <c r="H73" t="n">
         <v>10.8</v>
       </c>
@@ -4595,17 +5176,23 @@
         </is>
       </c>
       <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>98.34</v>
+      </c>
+      <c r="N73" t="n">
         <v>15</v>
       </c>
-      <c r="M73" t="n">
+      <c r="O73" t="n">
         <v>3.11</v>
       </c>
-      <c r="N73" t="n">
+      <c r="P73" t="n">
         <v>22.5</v>
       </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="n">
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="n">
         <v>1014.2</v>
       </c>
     </row>
@@ -4636,7 +5223,9 @@
       <c r="F74" t="n">
         <v>158.37</v>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>18.3</v>
+      </c>
       <c r="H74" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -4652,21 +5241,27 @@
         </is>
       </c>
       <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>158.37</v>
+      </c>
+      <c r="N74" t="n">
         <v>14.9</v>
       </c>
-      <c r="M74" t="n">
+      <c r="O74" t="n">
         <v>2.01</v>
       </c>
-      <c r="N74" t="n">
+      <c r="P74" t="n">
         <v>11.9</v>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="n">
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="n">
         <v>1297.1</v>
       </c>
     </row>
@@ -4697,7 +5292,9 @@
       <c r="F75" t="n">
         <v>73.81</v>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>23.4</v>
+      </c>
       <c r="H75" t="n">
         <v>11.9</v>
       </c>
@@ -4713,17 +5310,23 @@
         </is>
       </c>
       <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="N75" t="n">
         <v>49.2</v>
       </c>
-      <c r="M75" t="n">
+      <c r="O75" t="n">
         <v>0.92</v>
       </c>
-      <c r="N75" t="n">
+      <c r="P75" t="n">
         <v>11.1</v>
       </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="n">
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="n">
         <v>3108</v>
       </c>
     </row>
@@ -4754,7 +5357,9 @@
       <c r="F76" t="n">
         <v>1206.505</v>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>42.8</v>
+      </c>
       <c r="H76" t="n">
         <v>19</v>
       </c>
@@ -4770,17 +5375,23 @@
         </is>
       </c>
       <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1206.505</v>
+      </c>
+      <c r="N76" t="n">
         <v>101.3</v>
       </c>
-      <c r="M76" t="n">
+      <c r="O76" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="N76" t="n">
+      <c r="P76" t="n">
         <v>23.2</v>
       </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="n">
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="n">
         <v>11362.2</v>
       </c>
     </row>
@@ -4811,7 +5422,9 @@
       <c r="F77" t="n">
         <v>192.53</v>
       </c>
-      <c r="G77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>29.3</v>
+      </c>
       <c r="H77" t="n">
         <v>9.6</v>
       </c>
@@ -4827,17 +5440,23 @@
         </is>
       </c>
       <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>192.53</v>
+      </c>
+      <c r="N77" t="n">
         <v>111.7</v>
       </c>
-      <c r="M77" t="n">
+      <c r="O77" t="n">
         <v>0.86</v>
       </c>
-      <c r="N77" t="n">
+      <c r="P77" t="n">
         <v>68.3</v>
       </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="n">
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="n">
         <v>46632.7</v>
       </c>
     </row>
@@ -4868,7 +5487,9 @@
       <c r="F78" t="n">
         <v>182.68</v>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>19.4</v>
+      </c>
       <c r="H78" t="n">
         <v>9.199999999999999</v>
       </c>
@@ -4884,17 +5505,23 @@
         </is>
       </c>
       <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>182.68</v>
+      </c>
+      <c r="N78" t="n">
         <v>17.8</v>
       </c>
-      <c r="M78" t="n">
+      <c r="O78" t="n">
         <v>2.54</v>
       </c>
-      <c r="N78" t="n">
+      <c r="P78" t="n">
         <v>2.5</v>
       </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4923,7 +5550,9 @@
       <c r="F79" t="n">
         <v>137.93</v>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>14.6</v>
+      </c>
       <c r="H79" t="n">
         <v>10</v>
       </c>
@@ -4939,17 +5568,23 @@
         </is>
       </c>
       <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="N79" t="n">
         <v>40.1</v>
       </c>
-      <c r="M79" t="n">
+      <c r="O79" t="n">
         <v>1.4</v>
       </c>
-      <c r="N79" t="n">
+      <c r="P79" t="n">
         <v>8.4</v>
       </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4978,7 +5613,9 @@
       <c r="F80" t="n">
         <v>9.130000000000001</v>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>23.4</v>
+      </c>
       <c r="H80" t="n">
         <v>18.6</v>
       </c>
@@ -4994,17 +5631,23 @@
         </is>
       </c>
       <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="N80" t="n">
         <v>14.6</v>
       </c>
-      <c r="M80" t="n">
+      <c r="O80" t="n">
         <v>1.21</v>
       </c>
-      <c r="N80" t="n">
+      <c r="P80" t="n">
         <v>1.9</v>
       </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5033,7 +5676,9 @@
       <c r="F81" t="n">
         <v>107.09</v>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>17</v>
+      </c>
       <c r="H81" t="n">
         <v>0.6</v>
       </c>
@@ -5049,17 +5694,23 @@
         </is>
       </c>
       <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>107.09</v>
+      </c>
+      <c r="N81" t="n">
         <v>16.4</v>
       </c>
-      <c r="M81" t="n">
+      <c r="O81" t="n">
         <v>1.09</v>
       </c>
-      <c r="N81" t="n">
+      <c r="P81" t="n">
         <v>10.6</v>
       </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5088,7 +5739,9 @@
       <c r="F82" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>10</v>
+      </c>
       <c r="H82" t="n">
         <v>3.7</v>
       </c>
@@ -5104,17 +5757,23 @@
         </is>
       </c>
       <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="N82" t="n">
         <v>14</v>
       </c>
-      <c r="M82" t="n">
+      <c r="O82" t="n">
         <v>1.18</v>
       </c>
-      <c r="N82" t="n">
+      <c r="P82" t="n">
         <v>11.3</v>
       </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5143,7 +5802,9 @@
       <c r="F83" t="n">
         <v>52.5</v>
       </c>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="n">
+        <v>13.7</v>
+      </c>
       <c r="H83" t="n">
         <v>11.8</v>
       </c>
@@ -5157,25 +5818,31 @@
         </is>
       </c>
       <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N83" t="n">
         <v>35.8</v>
       </c>
-      <c r="M83" t="n">
+      <c r="O83" t="n">
         <v>1.25</v>
       </c>
-      <c r="N83" t="n">
+      <c r="P83" t="n">
         <v>7.2</v>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>🟡ROE弱化(36&lt;5年均49×80%)</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr"/>
+      <c r="S83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5204,7 +5871,9 @@
       <c r="F84" t="n">
         <v>341.98</v>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H84" t="n">
         <v>7.6</v>
       </c>
@@ -5218,21 +5887,27 @@
         </is>
       </c>
       <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>341.98</v>
+      </c>
+      <c r="N84" t="n">
         <v>23.4</v>
       </c>
-      <c r="M84" t="n">
+      <c r="O84" t="n">
         <v>1.41</v>
       </c>
-      <c r="N84" t="n">
+      <c r="P84" t="n">
         <v>0.3</v>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5261,7 +5936,9 @@
       <c r="F85" t="n">
         <v>78.45</v>
       </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="G85" t="n">
+        <v>10.5</v>
+      </c>
       <c r="H85" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5275,21 +5952,27 @@
         </is>
       </c>
       <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="N85" t="n">
         <v>20.4</v>
       </c>
-      <c r="M85" t="n">
+      <c r="O85" t="n">
         <v>2.12</v>
       </c>
-      <c r="N85" t="n">
+      <c r="P85" t="n">
         <v>6.9</v>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5318,7 +6001,9 @@
       <c r="F86" t="n">
         <v>148.81</v>
       </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="n">
+        <v>6.4</v>
+      </c>
       <c r="H86" t="n">
         <v>8.300000000000001</v>
       </c>
@@ -5330,21 +6015,27 @@
         </is>
       </c>
       <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>148.81</v>
+      </c>
+      <c r="N86" t="n">
         <v>21.6</v>
       </c>
-      <c r="M86" t="n">
+      <c r="O86" t="n">
         <v>1.44</v>
       </c>
-      <c r="N86" t="n">
+      <c r="P86" t="n">
         <v>15.6</v>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5373,7 +6064,9 @@
       <c r="F87" t="n">
         <v>43.01</v>
       </c>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="n">
+        <v>13.9</v>
+      </c>
       <c r="H87" t="n">
         <v>8.6</v>
       </c>
@@ -5387,21 +6080,27 @@
         </is>
       </c>
       <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="N87" t="n">
         <v>35</v>
       </c>
-      <c r="M87" t="n">
+      <c r="O87" t="n">
         <v>1.87</v>
       </c>
-      <c r="N87" t="n">
+      <c r="P87" t="n">
         <v>7.5</v>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5430,7 +6129,9 @@
       <c r="F88" t="n">
         <v>1132.33</v>
       </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="n">
+        <v>25.3</v>
+      </c>
       <c r="H88" t="n">
         <v>4.3</v>
       </c>
@@ -5444,21 +6145,27 @@
         </is>
       </c>
       <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1132.33</v>
+      </c>
+      <c r="N88" t="n">
         <v>40.8</v>
       </c>
-      <c r="M88" t="n">
+      <c r="O88" t="n">
         <v>2.05</v>
       </c>
-      <c r="N88" t="n">
+      <c r="P88" t="n">
         <v>7.8</v>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5487,7 +6194,9 @@
       <c r="F89" t="n">
         <v>239.07</v>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>15.4</v>
+      </c>
       <c r="H89" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -5499,21 +6208,27 @@
         </is>
       </c>
       <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>239.07</v>
+      </c>
+      <c r="N89" t="n">
         <v>18</v>
       </c>
-      <c r="M89" t="n">
+      <c r="O89" t="n">
         <v>1.35</v>
       </c>
-      <c r="N89" t="n">
+      <c r="P89" t="n">
         <v>15.6</v>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5542,7 +6257,9 @@
       <c r="F90" t="n">
         <v>337.53</v>
       </c>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="n">
+        <v>40.5</v>
+      </c>
       <c r="H90" t="n">
         <v>18.5</v>
       </c>
@@ -5558,17 +6275,23 @@
         </is>
       </c>
       <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="N90" t="n">
         <v>47.7</v>
       </c>
-      <c r="M90" t="n">
+      <c r="O90" t="n">
         <v>0.79</v>
       </c>
-      <c r="N90" t="n">
+      <c r="P90" t="n">
         <v>22.3</v>
       </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5597,7 +6320,9 @@
       <c r="F91" t="n">
         <v>112.93</v>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="n">
+        <v>117.6</v>
+      </c>
       <c r="H91" t="n">
         <v>8.5</v>
       </c>
@@ -5609,21 +6334,27 @@
         </is>
       </c>
       <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>112.93</v>
+      </c>
+      <c r="N91" t="n">
         <v>32.2</v>
       </c>
-      <c r="M91" t="n">
+      <c r="O91" t="n">
         <v>1.31</v>
       </c>
-      <c r="N91" t="n">
+      <c r="P91" t="n">
         <v>30.5</v>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5652,7 +6383,9 @@
       <c r="F92" t="n">
         <v>521.58</v>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="n">
+        <v>169.3</v>
+      </c>
       <c r="H92" t="n">
         <v>17.4</v>
       </c>
@@ -5668,21 +6401,27 @@
         </is>
       </c>
       <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>521.58</v>
+      </c>
+      <c r="N92" t="n">
         <v>8.1</v>
       </c>
-      <c r="M92" t="n">
+      <c r="O92" t="n">
         <v>1.78</v>
       </c>
-      <c r="N92" t="n">
+      <c r="P92" t="n">
         <v>20.5</v>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5711,7 +6450,9 @@
       <c r="F93" t="n">
         <v>94.83</v>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="n">
+        <v>13.7</v>
+      </c>
       <c r="H93" t="n">
         <v>1.3</v>
       </c>
@@ -5727,21 +6468,27 @@
         </is>
       </c>
       <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="N93" t="n">
         <v>10</v>
       </c>
-      <c r="M93" t="n">
+      <c r="O93" t="n">
         <v>0.74</v>
       </c>
-      <c r="N93" t="n">
+      <c r="P93" t="n">
         <v>4.7</v>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5760,7 +6507,9 @@
       <c r="F94" t="n">
         <v>63.8</v>
       </c>
-      <c r="G94" t="inlineStr"/>
+      <c r="G94" t="n">
+        <v>8.4</v>
+      </c>
       <c r="H94" t="n">
         <v>5</v>
       </c>
@@ -5771,12 +6520,18 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>63.8</v>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5805,7 +6560,9 @@
       <c r="F95" t="n">
         <v>109.48</v>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="n">
+        <v>9.5</v>
+      </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
         <v>-29.9</v>
@@ -5813,25 +6570,31 @@
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>109.48</v>
+      </c>
+      <c r="N95" t="n">
         <v>40.1</v>
       </c>
-      <c r="M95" t="n">
+      <c r="O95" t="n">
         <v>1.52</v>
       </c>
-      <c r="N95" t="n">
+      <c r="P95" t="n">
         <v>3.3</v>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5869,12 +6632,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>373.63</v>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5887,7 +6656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5948,30 +6717,40 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>漲跌%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>前次股價</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>ROE%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收CAGR%</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>市值(億美)</t>
         </is>
@@ -6004,7 +6783,9 @@
       <c r="F2" t="n">
         <v>368.34</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>35.8</v>
+      </c>
       <c r="H2" t="n">
         <v>26.8</v>
       </c>
@@ -6020,17 +6801,23 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>368.34</v>
+      </c>
+      <c r="N2" t="n">
         <v>41.9</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>2.62</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>13.7</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>650.2</v>
       </c>
     </row>
@@ -6061,7 +6848,9 @@
       <c r="F3" t="n">
         <v>151.35</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>58.2</v>
+      </c>
       <c r="H3" t="n">
         <v>45.8</v>
       </c>
@@ -6077,17 +6866,23 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>151.35</v>
+      </c>
+      <c r="N3" t="n">
         <v>155.7</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>1.4</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>19.4</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>1108.9</v>
       </c>
     </row>
@@ -6118,7 +6913,9 @@
       <c r="F4" t="n">
         <v>223.55</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>20.8</v>
+      </c>
       <c r="H4" t="n">
         <v>16.8</v>
       </c>
@@ -6134,17 +6931,23 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>223.55</v>
+      </c>
+      <c r="N4" t="n">
         <v>68.7</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>1.21</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>893.6</v>
       </c>
     </row>
@@ -6175,7 +6978,9 @@
       <c r="F5" t="n">
         <v>1794.62</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>61</v>
+      </c>
       <c r="H5" t="n">
         <v>26.5</v>
       </c>
@@ -6191,17 +6996,23 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1794.62</v>
+      </c>
+      <c r="N5" t="n">
         <v>52</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>1.27</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>15.1</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>6916.8</v>
       </c>
     </row>
@@ -6232,7 +7043,9 @@
       <c r="F6" t="n">
         <v>336.23</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>29.3</v>
+      </c>
       <c r="H6" t="n">
         <v>17.8</v>
       </c>
@@ -6248,17 +7061,23 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>336.23</v>
+      </c>
+      <c r="N6" t="n">
         <v>58.9</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>1.15</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>13.5</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>6444.9</v>
       </c>
     </row>
@@ -6289,7 +7108,9 @@
       <c r="F7" t="n">
         <v>283.65</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>38.1</v>
+      </c>
       <c r="H7" t="n">
         <v>26.3</v>
       </c>
@@ -6305,21 +7126,27 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>283.65</v>
+      </c>
+      <c r="N7" t="n">
         <v>21.7</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>1.42</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>6</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
         <v>798.3</v>
       </c>
     </row>
@@ -6350,7 +7177,9 @@
       <c r="F8" t="n">
         <v>70.53</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>34.1</v>
+      </c>
       <c r="H8" t="n">
         <v>19.9</v>
       </c>
@@ -6366,17 +7195,23 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="N8" t="n">
         <v>11.3</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>1.63</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>15.1</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6405,7 +7240,9 @@
       <c r="F9" t="n">
         <v>115.69</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>40.6</v>
+      </c>
       <c r="H9" t="n">
         <v>28.5</v>
       </c>
@@ -6421,17 +7258,23 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>115.69</v>
+      </c>
+      <c r="N9" t="n">
         <v>24.3</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>1.9</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>5.6</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6444,7 +7287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6505,30 +7348,40 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>漲跌%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>前次股價</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>ROE%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收CAGR%</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>市值(億美)</t>
         </is>
@@ -6561,7 +7414,9 @@
       <c r="F2" t="n">
         <v>106.34</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>23.3</v>
+      </c>
       <c r="H2" t="n">
         <v>16.9</v>
       </c>
@@ -6577,17 +7432,23 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>106.34</v>
+      </c>
+      <c r="N2" t="n">
         <v>21.3</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>1.23</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>18.5</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>30.5</v>
       </c>
     </row>
@@ -6618,7 +7479,9 @@
       <c r="F3" t="n">
         <v>113.32</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>28.6</v>
+      </c>
       <c r="H3" t="n">
         <v>21.8</v>
       </c>
@@ -6634,17 +7497,23 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>113.32</v>
+      </c>
+      <c r="N3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>1.29</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>18.3</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>514.6</v>
       </c>
     </row>
@@ -6675,7 +7544,9 @@
       <c r="F4" t="n">
         <v>550.25</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>19.7</v>
+      </c>
       <c r="H4" t="n">
         <v>9.800000000000001</v>
       </c>
@@ -6691,17 +7562,23 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>550.25</v>
+      </c>
+      <c r="N4" t="n">
         <v>33.2</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>1.92</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>14.3</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>13967.7</v>
       </c>
     </row>
@@ -6732,7 +7609,9 @@
       <c r="F5" t="n">
         <v>334.69</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>25.5</v>
+      </c>
       <c r="H5" t="n">
         <v>13.9</v>
       </c>
@@ -6748,17 +7627,23 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>334.69</v>
+      </c>
+      <c r="N5" t="n">
         <v>39</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>1.25</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>11.8</v>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="n">
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>40660.1</v>
       </c>
     </row>
@@ -6789,7 +7674,9 @@
       <c r="F6" t="n">
         <v>328.43</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>14.4</v>
+      </c>
       <c r="H6" t="n">
         <v>14.3</v>
       </c>
@@ -6805,17 +7692,23 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>328.43</v>
+      </c>
+      <c r="N6" t="n">
         <v>28</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>2.07</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>30.1</v>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="n">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>75.7</v>
       </c>
     </row>
@@ -6846,7 +7739,9 @@
       <c r="F7" t="n">
         <v>200.29</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>19.3</v>
+      </c>
       <c r="H7" t="n">
         <v>12.4</v>
       </c>
@@ -6862,17 +7757,23 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>200.29</v>
+      </c>
+      <c r="N7" t="n">
         <v>24.4</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>1.25</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>12.6</v>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
         <v>290.5</v>
       </c>
     </row>
@@ -6903,7 +7804,9 @@
       <c r="F8" t="n">
         <v>70.14</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>29.2</v>
+      </c>
       <c r="H8" t="n">
         <v>13.9</v>
       </c>
@@ -6919,17 +7822,23 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="N8" t="n">
         <v>33.8</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>1.72</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>17.5</v>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="n">
         <v>270.7</v>
       </c>
     </row>
@@ -6960,7 +7869,9 @@
       <c r="F9" t="n">
         <v>168.52</v>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>25.1</v>
+      </c>
       <c r="H9" t="n">
         <v>11.1</v>
       </c>
@@ -6976,17 +7887,23 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>168.52</v>
+      </c>
+      <c r="N9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>1.64</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>26</v>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="n">
         <v>169.4</v>
       </c>
     </row>
@@ -7017,7 +7934,9 @@
       <c r="F10" t="n">
         <v>372.97</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>22.1</v>
+      </c>
       <c r="H10" t="n">
         <v>11.2</v>
       </c>
@@ -7033,17 +7952,23 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="N10" t="n">
         <v>33.1</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>1.34</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>13.8</v>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="n">
         <v>27705.8</v>
       </c>
     </row>
@@ -7074,7 +7999,9 @@
       <c r="F11" t="n">
         <v>432.35</v>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>31.5</v>
+      </c>
       <c r="H11" t="n">
         <v>0.7</v>
       </c>
@@ -7090,17 +8017,23 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>432.35</v>
+      </c>
+      <c r="N11" t="n">
         <v>36.9</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>1.37</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>24.8</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
         <v>22423.7</v>
       </c>
     </row>
@@ -7131,7 +8064,9 @@
       <c r="F12" t="n">
         <v>157.6</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>53.2</v>
+      </c>
       <c r="H12" t="n">
         <v>22.2</v>
       </c>
@@ -7147,17 +8082,23 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>157.6</v>
+      </c>
+      <c r="N12" t="n">
         <v>30.6</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>1.25</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>32.2</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
         <v>1984.5</v>
       </c>
     </row>
@@ -7188,7 +8129,9 @@
       <c r="F13" t="n">
         <v>202.73</v>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H13" t="n">
         <v>5.8</v>
       </c>
@@ -7204,17 +8147,23 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>202.73</v>
+      </c>
+      <c r="N13" t="n">
         <v>62.4</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>1.41</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>10.8</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="n">
         <v>805.9</v>
       </c>
     </row>
@@ -7245,7 +8194,9 @@
       <c r="F14" t="n">
         <v>129.18</v>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>14.9</v>
+      </c>
       <c r="H14" t="n">
         <v>9.800000000000001</v>
       </c>
@@ -7261,17 +8212,23 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>129.18</v>
+      </c>
+      <c r="N14" t="n">
         <v>31</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>1.5</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>18.1</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
         <v>70.5</v>
       </c>
     </row>
@@ -7302,7 +8259,9 @@
       <c r="F15" t="n">
         <v>123.27</v>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>22</v>
+      </c>
       <c r="H15" t="n">
         <v>12.2</v>
       </c>
@@ -7318,17 +8277,23 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>123.27</v>
+      </c>
+      <c r="N15" t="n">
         <v>37.2</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>1.56</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>12.9</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
         <v>43.4</v>
       </c>
     </row>
@@ -7359,7 +8324,9 @@
       <c r="F16" t="n">
         <v>275.86</v>
       </c>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>19.4</v>
+      </c>
       <c r="H16" t="n">
         <v>18.7</v>
       </c>
@@ -7375,17 +8342,23 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>275.86</v>
+      </c>
+      <c r="N16" t="n">
         <v>33.4</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>1.34</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>18.3</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
         <v>71.3</v>
       </c>
     </row>
@@ -7416,7 +8389,9 @@
       <c r="F17" t="n">
         <v>196.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>28.4</v>
+      </c>
       <c r="H17" t="n">
         <v>10.8</v>
       </c>
@@ -7432,17 +8407,23 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>196.26</v>
+      </c>
+      <c r="N17" t="n">
         <v>49.4</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>2.18</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>13.2</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
         <v>414.4</v>
       </c>
     </row>
@@ -7473,7 +8454,9 @@
       <c r="F18" t="n">
         <v>44.29</v>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="H18" t="n">
         <v>5.8</v>
       </c>
@@ -7489,17 +8472,23 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="N18" t="n">
         <v>25.1</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>1.23</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>6.9</v>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
         <v>390.7</v>
       </c>
     </row>
@@ -7530,7 +8519,9 @@
       <c r="F19" t="n">
         <v>65.14</v>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>10</v>
+      </c>
       <c r="H19" t="n">
         <v>9.800000000000001</v>
       </c>
@@ -7546,17 +8537,23 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>65.14</v>
+      </c>
+      <c r="N19" t="n">
         <v>155.3</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>1.28</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>6.4</v>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>147.1</v>
       </c>
     </row>
@@ -7587,7 +8584,9 @@
       <c r="F20" t="n">
         <v>271.63</v>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>23.6</v>
+      </c>
       <c r="H20" t="n">
         <v>21.3</v>
       </c>
@@ -7603,21 +8602,27 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>271.63</v>
+      </c>
+      <c r="N20" t="n">
         <v>35.5</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>1.25</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>4.2</v>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>2553</v>
       </c>
     </row>
@@ -7648,7 +8653,9 @@
       <c r="F21" t="n">
         <v>123.71</v>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>15.2</v>
+      </c>
       <c r="H21" t="n">
         <v>1.4</v>
       </c>
@@ -7664,17 +8671,23 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>123.71</v>
+      </c>
+      <c r="N21" t="n">
         <v>21.6</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>1.46</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>6.5</v>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="n">
         <v>789.8</v>
       </c>
     </row>
@@ -7705,7 +8718,9 @@
       <c r="F22" t="n">
         <v>104.56</v>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>14.8</v>
+      </c>
       <c r="H22" t="n">
         <v>10.4</v>
       </c>
@@ -7721,17 +8736,23 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>104.56</v>
+      </c>
+      <c r="N22" t="n">
         <v>40.8</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>1.15</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>14.7</v>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
         <v>145.2</v>
       </c>
     </row>
@@ -7762,7 +8783,9 @@
       <c r="F23" t="n">
         <v>76.55</v>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>7.5</v>
+      </c>
       <c r="H23" t="n">
         <v>0.8</v>
       </c>
@@ -7778,21 +8801,27 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>76.55</v>
+      </c>
+      <c r="N23" t="n">
         <v>24</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>1.09</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>46.4</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="n">
         <v>1089.6</v>
       </c>
     </row>
@@ -7823,7 +8852,9 @@
       <c r="F24" t="n">
         <v>48.025</v>
       </c>
-      <c r="G24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>11.6</v>
+      </c>
       <c r="H24" t="n">
         <v>1.7</v>
       </c>
@@ -7839,17 +8870,23 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>48.025</v>
+      </c>
+      <c r="N24" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>1.16</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>21.7</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="n">
         <v>2134.1</v>
       </c>
     </row>
@@ -7880,7 +8917,9 @@
       <c r="F25" t="n">
         <v>54.77</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>17.6</v>
+      </c>
       <c r="H25" t="n">
         <v>15</v>
       </c>
@@ -7896,17 +8935,23 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>54.77</v>
+      </c>
+      <c r="N25" t="n">
         <v>40.2</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>1.13</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>12.8</v>
       </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="n">
         <v>137.7</v>
       </c>
     </row>
@@ -7937,7 +8982,9 @@
       <c r="F26" t="n">
         <v>268.87</v>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>61.8</v>
+      </c>
       <c r="H26" t="n">
         <v>30.5</v>
       </c>
@@ -7953,17 +9000,23 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>268.87</v>
+      </c>
+      <c r="N26" t="n">
         <v>33.1</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>1.25</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>13.5</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="n">
         <v>1075.8</v>
       </c>
     </row>
@@ -7994,7 +9047,9 @@
       <c r="F27" t="n">
         <v>21.76</v>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>21.8</v>
+      </c>
       <c r="H27" t="n">
         <v>3.7</v>
       </c>
@@ -8010,17 +9065,23 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="N27" t="n">
         <v>24.2</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>1.88</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>33.2</v>
       </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="n">
         <v>12286.6</v>
       </c>
     </row>
@@ -8051,7 +9112,9 @@
       <c r="F28" t="n">
         <v>88.56</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>22.4</v>
+      </c>
       <c r="H28" t="n">
         <v>15.9</v>
       </c>
@@ -8067,17 +9130,23 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="N28" t="n">
         <v>15.2</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>1.83</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>12.6</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="n">
         <v>1846.8</v>
       </c>
     </row>
@@ -8108,7 +9177,9 @@
       <c r="F29" t="n">
         <v>365.02</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>59</v>
+      </c>
       <c r="H29" t="n">
         <v>10.4</v>
       </c>
@@ -8124,17 +9195,23 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>365.02</v>
+      </c>
+      <c r="N29" t="n">
         <v>36.4</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>1.19</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>23.5</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="n">
         <v>17366.1</v>
       </c>
     </row>
@@ -8165,7 +9242,9 @@
       <c r="F30" t="n">
         <v>163.72</v>
       </c>
-      <c r="G30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>44.7</v>
+      </c>
       <c r="H30" t="n">
         <v>21.7</v>
       </c>
@@ -8181,17 +9260,23 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>163.72</v>
+      </c>
+      <c r="N30" t="n">
         <v>34.8</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>1.26</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>20.7</v>
       </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="n">
         <v>2014.1</v>
       </c>
     </row>
@@ -8222,7 +9307,9 @@
       <c r="F31" t="n">
         <v>267.72</v>
       </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>16.2</v>
+      </c>
       <c r="H31" t="n">
         <v>6.6</v>
       </c>
@@ -8238,17 +9325,23 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>267.72</v>
+      </c>
+      <c r="N31" t="n">
         <v>23.3</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>1.6</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>18.2</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
         <v>732.3</v>
       </c>
     </row>
@@ -8279,7 +9372,9 @@
       <c r="F32" t="n">
         <v>106.35</v>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>22.4</v>
+      </c>
       <c r="H32" t="n">
         <v>11.1</v>
       </c>
@@ -8295,17 +9390,23 @@
         </is>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="N32" t="n">
         <v>22.4</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>1.84</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>25.9</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="n">
         <v>56.9</v>
       </c>
     </row>
@@ -8336,7 +9437,9 @@
       <c r="F33" t="n">
         <v>499.02</v>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>28.8</v>
+      </c>
       <c r="H33" t="n">
         <v>14.5</v>
       </c>
@@ -8352,17 +9455,23 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>499.02</v>
+      </c>
+      <c r="N33" t="n">
         <v>206.1</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>1.16</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>14.8</v>
       </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="n">
         <v>4409.3</v>
       </c>
     </row>
@@ -8393,7 +9502,9 @@
       <c r="F34" t="n">
         <v>519.62</v>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>34.3</v>
+      </c>
       <c r="H34" t="n">
         <v>20.7</v>
       </c>
@@ -8409,17 +9520,23 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>519.62</v>
+      </c>
+      <c r="N34" t="n">
         <v>18.5</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>1.5</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>2.5</v>
       </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="n">
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="n">
         <v>2403.8</v>
       </c>
     </row>
@@ -8450,7 +9567,9 @@
       <c r="F35" t="n">
         <v>133.89</v>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="H35" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -8466,17 +9585,23 @@
         </is>
       </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>133.89</v>
+      </c>
+      <c r="N35" t="n">
         <v>22</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>1.54</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>6.9</v>
       </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="n">
         <v>367</v>
       </c>
     </row>
@@ -8507,7 +9632,9 @@
       <c r="F36" t="n">
         <v>33.33</v>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>12.5</v>
+      </c>
       <c r="H36" t="n">
         <v>10.6</v>
       </c>
@@ -8523,17 +9650,23 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="N36" t="n">
         <v>17.2</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>1.41</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>5.1</v>
       </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="n">
         <v>20.9</v>
       </c>
     </row>
@@ -8564,7 +9697,9 @@
       <c r="F37" t="n">
         <v>145.69</v>
       </c>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>6</v>
+      </c>
       <c r="H37" t="n">
         <v>4.9</v>
       </c>
@@ -8580,17 +9715,23 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>145.69</v>
+      </c>
+      <c r="N37" t="n">
         <v>20.9</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>1.25</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="n">
         <v>91.2</v>
       </c>
     </row>
@@ -8621,7 +9762,9 @@
       <c r="F38" t="n">
         <v>1675.1</v>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>44.2</v>
+      </c>
       <c r="H38" t="n">
         <v>9.6</v>
       </c>
@@ -8637,21 +9780,27 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1675.1</v>
+      </c>
+      <c r="N38" t="n">
         <v>29.6</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>6.07</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>42.2</v>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="n">
         <v>849.2</v>
       </c>
     </row>
@@ -8682,7 +9831,9 @@
       <c r="F39" t="n">
         <v>97.54000000000001</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>7.4</v>
+      </c>
       <c r="H39" t="n">
         <v>9.1</v>
       </c>
@@ -8698,17 +9849,23 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>97.54000000000001</v>
+      </c>
+      <c r="N39" t="n">
         <v>20.5</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>1.4</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>22.2</v>
       </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
         <v>340.8</v>
       </c>
     </row>
@@ -8739,7 +9896,9 @@
       <c r="F40" t="n">
         <v>340.36</v>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>21.2</v>
+      </c>
       <c r="H40" t="n">
         <v>12</v>
       </c>
@@ -8755,17 +9914,23 @@
         </is>
       </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>340.36</v>
+      </c>
+      <c r="N40" t="n">
         <v>33.9</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>1.7</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>16</v>
       </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="n">
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
         <v>2322.4</v>
       </c>
     </row>
@@ -8796,7 +9961,9 @@
       <c r="F41" t="n">
         <v>98.34</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>58.2</v>
+      </c>
       <c r="H41" t="n">
         <v>10.8</v>
       </c>
@@ -8812,17 +9979,23 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>98.34</v>
+      </c>
+      <c r="N41" t="n">
         <v>15</v>
       </c>
-      <c r="M41" t="n">
+      <c r="O41" t="n">
         <v>3.11</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>22.5</v>
       </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="n">
         <v>1014.2</v>
       </c>
     </row>
@@ -8853,7 +10026,9 @@
       <c r="F42" t="n">
         <v>158.37</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>18.3</v>
+      </c>
       <c r="H42" t="n">
         <v>8.699999999999999</v>
       </c>
@@ -8869,21 +10044,27 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>158.37</v>
+      </c>
+      <c r="N42" t="n">
         <v>14.9</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>2.01</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>11.9</v>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="n">
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="n">
         <v>1297.1</v>
       </c>
     </row>
@@ -8914,7 +10095,9 @@
       <c r="F43" t="n">
         <v>73.81</v>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>23.4</v>
+      </c>
       <c r="H43" t="n">
         <v>11.9</v>
       </c>
@@ -8930,17 +10113,23 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>73.81</v>
+      </c>
+      <c r="N43" t="n">
         <v>49.2</v>
       </c>
-      <c r="M43" t="n">
+      <c r="O43" t="n">
         <v>0.92</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>11.1</v>
       </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="n">
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="n">
         <v>3108</v>
       </c>
     </row>
@@ -8971,7 +10160,9 @@
       <c r="F44" t="n">
         <v>1206.505</v>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>42.8</v>
+      </c>
       <c r="H44" t="n">
         <v>19</v>
       </c>
@@ -8987,17 +10178,23 @@
         </is>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1206.505</v>
+      </c>
+      <c r="N44" t="n">
         <v>101.3</v>
       </c>
-      <c r="M44" t="n">
+      <c r="O44" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>23.2</v>
       </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="n">
         <v>11362.2</v>
       </c>
     </row>
@@ -9028,7 +10225,9 @@
       <c r="F45" t="n">
         <v>192.53</v>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>29.3</v>
+      </c>
       <c r="H45" t="n">
         <v>9.6</v>
       </c>
@@ -9044,17 +10243,23 @@
         </is>
       </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>192.53</v>
+      </c>
+      <c r="N45" t="n">
         <v>111.7</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>0.86</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>68.3</v>
       </c>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="n">
         <v>46632.7</v>
       </c>
     </row>
@@ -9085,7 +10290,9 @@
       <c r="F46" t="n">
         <v>182.68</v>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>19.4</v>
+      </c>
       <c r="H46" t="n">
         <v>9.199999999999999</v>
       </c>
@@ -9101,17 +10308,23 @@
         </is>
       </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>182.68</v>
+      </c>
+      <c r="N46" t="n">
         <v>17.8</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>2.54</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>2.5</v>
       </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -9140,7 +10353,9 @@
       <c r="F47" t="n">
         <v>137.93</v>
       </c>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>14.6</v>
+      </c>
       <c r="H47" t="n">
         <v>10</v>
       </c>
@@ -9156,17 +10371,23 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="N47" t="n">
         <v>40.1</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>1.4</v>
       </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
         <v>8.4</v>
       </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -9195,7 +10416,9 @@
       <c r="F48" t="n">
         <v>9.130000000000001</v>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>23.4</v>
+      </c>
       <c r="H48" t="n">
         <v>18.6</v>
       </c>
@@ -9211,17 +10434,23 @@
         </is>
       </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="N48" t="n">
         <v>14.6</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>1.21</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>1.9</v>
       </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -9250,7 +10479,9 @@
       <c r="F49" t="n">
         <v>107.09</v>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>17</v>
+      </c>
       <c r="H49" t="n">
         <v>0.6</v>
       </c>
@@ -9266,17 +10497,23 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>107.09</v>
+      </c>
+      <c r="N49" t="n">
         <v>16.4</v>
       </c>
-      <c r="M49" t="n">
+      <c r="O49" t="n">
         <v>1.09</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>10.6</v>
       </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -9305,7 +10542,9 @@
       <c r="F50" t="n">
         <v>91.98999999999999</v>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>10</v>
+      </c>
       <c r="H50" t="n">
         <v>3.7</v>
       </c>
@@ -9321,17 +10560,23 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="N50" t="n">
         <v>14</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>1.18</v>
       </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
         <v>11.3</v>
       </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -9360,7 +10605,9 @@
       <c r="F51" t="n">
         <v>52.5</v>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>13.7</v>
+      </c>
       <c r="H51" t="n">
         <v>11.8</v>
       </c>
@@ -9374,25 +10621,31 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N51" t="n">
         <v>35.8</v>
       </c>
-      <c r="M51" t="n">
+      <c r="O51" t="n">
         <v>1.25</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>7.2</v>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>🟡ROE弱化(36&lt;5年均49×80%)</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -9421,7 +10674,9 @@
       <c r="F52" t="n">
         <v>341.98</v>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>12.6</v>
+      </c>
       <c r="H52" t="n">
         <v>7.6</v>
       </c>
@@ -9435,21 +10690,27 @@
         </is>
       </c>
       <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>341.98</v>
+      </c>
+      <c r="N52" t="n">
         <v>23.4</v>
       </c>
-      <c r="M52" t="n">
+      <c r="O52" t="n">
         <v>1.41</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>0.3</v>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -9478,7 +10739,9 @@
       <c r="F53" t="n">
         <v>78.45</v>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>10.5</v>
+      </c>
       <c r="H53" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -9492,21 +10755,27 @@
         </is>
       </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="N53" t="n">
         <v>20.4</v>
       </c>
-      <c r="M53" t="n">
+      <c r="O53" t="n">
         <v>2.12</v>
       </c>
-      <c r="N53" t="n">
+      <c r="P53" t="n">
         <v>6.9</v>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9535,7 +10804,9 @@
       <c r="F54" t="n">
         <v>148.81</v>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>6.4</v>
+      </c>
       <c r="H54" t="n">
         <v>8.300000000000001</v>
       </c>
@@ -9547,21 +10818,27 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>148.81</v>
+      </c>
+      <c r="N54" t="n">
         <v>21.6</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>1.44</v>
       </c>
-      <c r="N54" t="n">
+      <c r="P54" t="n">
         <v>15.6</v>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9590,7 +10867,9 @@
       <c r="F55" t="n">
         <v>43.01</v>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>13.9</v>
+      </c>
       <c r="H55" t="n">
         <v>8.6</v>
       </c>
@@ -9604,21 +10883,27 @@
         </is>
       </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>43.01</v>
+      </c>
+      <c r="N55" t="n">
         <v>35</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>1.87</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>7.5</v>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9647,7 +10932,9 @@
       <c r="F56" t="n">
         <v>1132.33</v>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>25.3</v>
+      </c>
       <c r="H56" t="n">
         <v>4.3</v>
       </c>
@@ -9661,21 +10948,27 @@
         </is>
       </c>
       <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1132.33</v>
+      </c>
+      <c r="N56" t="n">
         <v>40.8</v>
       </c>
-      <c r="M56" t="n">
+      <c r="O56" t="n">
         <v>2.05</v>
       </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
         <v>7.8</v>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9704,7 +10997,9 @@
       <c r="F57" t="n">
         <v>239.07</v>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>15.4</v>
+      </c>
       <c r="H57" t="n">
         <v>8.800000000000001</v>
       </c>
@@ -9716,21 +11011,27 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>239.07</v>
+      </c>
+      <c r="N57" t="n">
         <v>18</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>1.35</v>
       </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
         <v>15.6</v>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9759,7 +11060,9 @@
       <c r="F58" t="n">
         <v>337.53</v>
       </c>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>40.5</v>
+      </c>
       <c r="H58" t="n">
         <v>18.5</v>
       </c>
@@ -9775,17 +11078,23 @@
         </is>
       </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>337.53</v>
+      </c>
+      <c r="N58" t="n">
         <v>47.7</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>0.79</v>
       </c>
-      <c r="N58" t="n">
+      <c r="P58" t="n">
         <v>22.3</v>
       </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9814,7 +11123,9 @@
       <c r="F59" t="n">
         <v>112.93</v>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>117.6</v>
+      </c>
       <c r="H59" t="n">
         <v>8.5</v>
       </c>
@@ -9826,21 +11137,27 @@
         </is>
       </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>112.93</v>
+      </c>
+      <c r="N59" t="n">
         <v>32.2</v>
       </c>
-      <c r="M59" t="n">
+      <c r="O59" t="n">
         <v>1.31</v>
       </c>
-      <c r="N59" t="n">
+      <c r="P59" t="n">
         <v>30.5</v>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9869,7 +11186,9 @@
       <c r="F60" t="n">
         <v>521.58</v>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>169.3</v>
+      </c>
       <c r="H60" t="n">
         <v>17.4</v>
       </c>
@@ -9885,21 +11204,27 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>521.58</v>
+      </c>
+      <c r="N60" t="n">
         <v>8.1</v>
       </c>
-      <c r="M60" t="n">
+      <c r="O60" t="n">
         <v>1.78</v>
       </c>
-      <c r="N60" t="n">
+      <c r="P60" t="n">
         <v>20.5</v>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -9928,7 +11253,9 @@
       <c r="F61" t="n">
         <v>94.83</v>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>13.7</v>
+      </c>
       <c r="H61" t="n">
         <v>1.3</v>
       </c>
@@ -9944,21 +11271,27 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>94.83</v>
+      </c>
+      <c r="N61" t="n">
         <v>10</v>
       </c>
-      <c r="M61" t="n">
+      <c r="O61" t="n">
         <v>0.74</v>
       </c>
-      <c r="N61" t="n">
+      <c r="P61" t="n">
         <v>4.7</v>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -9977,7 +11310,9 @@
       <c r="F62" t="n">
         <v>63.8</v>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>8.4</v>
+      </c>
       <c r="H62" t="n">
         <v>5</v>
       </c>
@@ -9988,12 +11323,18 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>63.8</v>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10006,7 +11347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10067,30 +11408,40 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>漲跌%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>前次股價</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>ROE%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收CAGR%</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>市值(億美)</t>
         </is>
@@ -10099,17 +11450,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CDNS</t>
+          <t>UAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cadence Design Systems, Inc.</t>
+          <t>CVR Partners, LP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -10118,553 +11469,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F2" t="n">
-        <v>377.27</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>33.8</v>
-      </c>
+        <v>109.48</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.63</v>
-      </c>
+        <v>-29.9</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>🔴未來過熱</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.56</v>
+        <v>109.48</v>
       </c>
       <c r="N2" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>75</v>
-      </c>
-      <c r="F3" t="n">
-        <v>283.78</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>146.7</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P2" t="n">
         <v>3.3</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LRCX</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Lam Research Corporation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>75</v>
-      </c>
-      <c r="F4" t="n">
-        <v>379.09</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AMAT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Applied Materials, Inc.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>75</v>
-      </c>
-      <c r="F5" t="n">
-        <v>626.84</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GLW</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Corning Inc</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>67</v>
-      </c>
-      <c r="F6" t="n">
-        <v>223</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>WDC</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Western Digital Corporation</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>56</v>
-      </c>
-      <c r="F7" t="n">
-        <v>586.45</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CIEN</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Ciena Corporation</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>47</v>
-      </c>
-      <c r="F8" t="n">
-        <v>479.5</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>33.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>-4.9</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="N8" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>COHR</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Coherent, Inc.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>36</v>
-      </c>
-      <c r="F9" t="n">
-        <v>380.56</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="N9" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SNDK</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Sandisk Corporation</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2090.71</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="n">
-        <v>154.5</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-9</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>⚠️現金流為負(含金量-0.05)</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>22</v>
-      </c>
-      <c r="F11" t="n">
-        <v>379.71</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-33.5</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>🔴未來過熱</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="N11" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>⚠️EPS落後營收(EPS3y -34&lt;營收CAGR 15×50%) | ⚠️ROE滑落(5&lt;5年均17×67%)</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10677,7 +11521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10738,30 +11582,40 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>漲跌%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>前次股價</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>ROE%</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>含金量</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>營收CAGR%</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>循環股</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>主要漏洞</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>市值(億美)</t>
         </is>
@@ -10770,6 +11624,767 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CDNS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cadence Design Systems, Inc.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>78</v>
+      </c>
+      <c r="F2" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="G2" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>377.27</v>
+      </c>
+      <c r="N2" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="P2" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Apple Inc.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>283.78</v>
+      </c>
+      <c r="G3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>283.78</v>
+      </c>
+      <c r="N3" t="n">
+        <v>146.7</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lam Research Corporation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="G4" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Applied Materials, Inc.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>75</v>
+      </c>
+      <c r="F5" t="n">
+        <v>626.84</v>
+      </c>
+      <c r="G5" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>626.84</v>
+      </c>
+      <c r="N5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Corning Inc</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>67</v>
+      </c>
+      <c r="F6" t="n">
+        <v>223</v>
+      </c>
+      <c r="G6" t="n">
+        <v>105.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>223</v>
+      </c>
+      <c r="N6" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>WDC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Western Digital Corporation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>586.45</v>
+      </c>
+      <c r="G7" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>586.45</v>
+      </c>
+      <c r="N7" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CIEN</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ciena Corporation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>47</v>
+      </c>
+      <c r="F8" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>155.2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>6.54</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>COHR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Coherent, Inc.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>36</v>
+      </c>
+      <c r="F9" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="G9" t="n">
+        <v>166.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>380.56</v>
+      </c>
+      <c r="N9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sandisk Corporation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>22</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2090.71</v>
+      </c>
+      <c r="G10" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2090.71</v>
+      </c>
+      <c r="N10" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-9</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>⚠️現金流為負(含金量-0.05)</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="G11" t="n">
+        <v>315.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-33.5</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>379.71</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="P11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>⚠️EPS落後營收(EPS3y -34&lt;營收CAGR 15×50%) | ⚠️ROE滑落(5&lt;5年均17×67%)</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>代號</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>名稱</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>產業</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>評等</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>品質總分</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>當前股價</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PER即時</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ForwardPE即時</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>EPS3y%</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>PEG即時</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>估值鬧鐘</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>漲跌%</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>前次股價</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ROE%</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>含金量</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>營收CAGR%</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>循環股</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>主要漏洞</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>市值(億美)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>KLAC</t>
         </is>
       </c>
@@ -10794,7 +12409,9 @@
       <c r="F2" t="n">
         <v>248.64</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>69.90000000000001</v>
+      </c>
       <c r="H2" t="n">
         <v>32.6</v>
       </c>
@@ -10810,21 +12427,27 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>248.64</v>
+      </c>
+      <c r="N2" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>15.1</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>🟡ROE弱化(89&lt;5年均117×80%)</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>3247.9</v>
       </c>
     </row>
@@ -10855,7 +12478,9 @@
       <c r="F3" t="n">
         <v>952.54</v>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>47.8</v>
+      </c>
       <c r="H3" t="n">
         <v>33.4</v>
       </c>
@@ -10871,17 +12496,23 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>952.54</v>
+      </c>
+      <c r="N3" t="n">
         <v>28.3</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>1.65</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>8.9</v>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10910,7 +12541,9 @@
       <c r="F4" t="n">
         <v>10.78</v>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>13.5</v>
+      </c>
       <c r="H4" t="n">
         <v>10.9</v>
       </c>
@@ -10926,17 +12559,23 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="N4" t="n">
         <v>31.8</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>1.22</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>5.4</v>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10965,7 +12604,9 @@
       <c r="F5" t="n">
         <v>303.95</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>74.5</v>
+      </c>
       <c r="H5" t="n">
         <v>19.1</v>
       </c>
@@ -10977,21 +12618,27 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>303.95</v>
+      </c>
+      <c r="N5" t="n">
         <v>42.1</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>1.59</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>19.6</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -11020,7 +12667,9 @@
       <c r="F6" t="n">
         <v>816.98</v>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>131.6</v>
+      </c>
       <c r="H6" t="n">
         <v>18.4</v>
       </c>
@@ -11034,21 +12683,27 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>816.98</v>
+      </c>
+      <c r="N6" t="n">
         <v>30.7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>4.88</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>-1</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11077,7 +12732,9 @@
       <c r="F7" t="n">
         <v>266.77</v>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>90.8</v>
+      </c>
       <c r="H7" t="n">
         <v>28.4</v>
       </c>
@@ -11089,21 +12746,27 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>266.77</v>
+      </c>
+      <c r="N7" t="n">
         <v>16.8</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.66</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>16.4</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -11132,7 +12795,9 @@
       <c r="F8" t="n">
         <v>498.66</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>14.8</v>
+      </c>
       <c r="H8" t="n">
         <v>23</v>
       </c>
@@ -11144,21 +12809,27 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>498.66</v>
+      </c>
+      <c r="N8" t="n">
         <v>10.3</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>7.7</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/美股PE監看表.xlsx
+++ b/data/美股PE監看表.xlsx
@@ -2486,7 +2486,7 @@
         <v>70.53</v>
       </c>
       <c r="G32" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="H32" t="n">
         <v>19.9</v>
@@ -4242,7 +4242,7 @@
         <v>86</v>
       </c>
       <c r="F59" t="n">
-        <v>21.76</v>
+        <v>21.75</v>
       </c>
       <c r="G59" t="n">
         <v>21.8</v>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="M59" t="n">
         <v>21.76</v>
@@ -5740,7 +5740,7 @@
         <v>91.98999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H82" t="n">
         <v>3.7</v>
@@ -6451,7 +6451,7 @@
         <v>94.83</v>
       </c>
       <c r="G93" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H93" t="n">
         <v>1.3</v>
@@ -7178,7 +7178,7 @@
         <v>70.53</v>
       </c>
       <c r="G8" t="n">
-        <v>34.1</v>
+        <v>34.2</v>
       </c>
       <c r="H8" t="n">
         <v>19.9</v>
@@ -9045,7 +9045,7 @@
         <v>86</v>
       </c>
       <c r="F27" t="n">
-        <v>21.76</v>
+        <v>21.75</v>
       </c>
       <c r="G27" t="n">
         <v>21.8</v>
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="M27" t="n">
         <v>21.76</v>
@@ -10543,7 +10543,7 @@
         <v>91.98999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H50" t="n">
         <v>3.7</v>
@@ -11254,7 +11254,7 @@
         <v>94.83</v>
       </c>
       <c r="G61" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H61" t="n">
         <v>1.3</v>

--- a/data/美股PE監看表.xlsx
+++ b/data/美股PE監看表.xlsx
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11.97</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>248.64</v>
+        <v>278.39</v>
       </c>
       <c r="N2" t="n">
         <v>89.09999999999999</v>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.21</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>377.27</v>
+        <v>372.72</v>
       </c>
       <c r="N3" t="n">
         <v>21.1</v>
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8.390000000000001</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>379.09</v>
+        <v>410.91</v>
       </c>
       <c r="N4" t="n">
         <v>65.8</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>10.82</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>626.84</v>
+        <v>694.64</v>
       </c>
       <c r="N5" t="n">
         <v>39.8</v>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>283.78</v>
+        <v>281.74</v>
       </c>
       <c r="N6" t="n">
         <v>146.7</v>
@@ -884,10 +884,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>223</v>
+        <v>255.79</v>
       </c>
       <c r="N7" t="n">
         <v>15.6</v>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.16</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>586.45</v>
+        <v>651.88</v>
       </c>
       <c r="N8" t="n">
         <v>91.90000000000001</v>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>479.5</v>
+        <v>478.93</v>
       </c>
       <c r="N9" t="n">
         <v>15.7</v>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>380.56</v>
+        <v>391.22</v>
       </c>
       <c r="N10" t="n">
         <v>5.3</v>
@@ -1143,8 +1143,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>411.84</v>
+      </c>
       <c r="N11" t="n">
         <v>4.8</v>
       </c>
@@ -1206,8 +1210,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2050.39</v>
+      </c>
       <c r="N12" t="n">
         <v>42.3</v>
       </c>
@@ -1274,10 +1282,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>-0.62</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>952.54</v>
+        <v>946.6799999999999</v>
       </c>
       <c r="N13" t="n">
         <v>28.3</v>
@@ -1320,7 +1328,7 @@
         <v>10.7</v>
       </c>
       <c r="G14" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
         <v>10.8</v>
@@ -1336,8 +1344,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10.7</v>
+      </c>
       <c r="N14" t="n">
         <v>31.8</v>
       </c>
@@ -1392,10 +1404,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>303.95</v>
+        <v>306.97</v>
       </c>
       <c r="N15" t="n">
         <v>42.1</v>
@@ -1457,10 +1469,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>816.98</v>
+        <v>851.4</v>
       </c>
       <c r="N16" t="n">
         <v>30.7</v>
@@ -1520,10 +1532,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>266.77</v>
+        <v>277.75</v>
       </c>
       <c r="N17" t="n">
         <v>16.8</v>
@@ -1583,10 +1595,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>498.66</v>
+        <v>495.95</v>
       </c>
       <c r="N18" t="n">
         <v>10.3</v>
@@ -1650,10 +1662,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>151.35</v>
+        <v>155.42</v>
       </c>
       <c r="N19" t="n">
         <v>155.7</v>
@@ -1698,7 +1710,7 @@
         <v>31.29</v>
       </c>
       <c r="G20" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="H20" t="n">
         <v>16.8</v>
@@ -1714,8 +1726,12 @@
           <t>🟡未來合理</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>31.29</v>
+      </c>
       <c r="N20" t="n">
         <v>90.8</v>
       </c>
@@ -1759,7 +1775,7 @@
         <v>520.39</v>
       </c>
       <c r="G21" t="n">
-        <v>56.2</v>
+        <v>60.3</v>
       </c>
       <c r="H21" t="n">
         <v>40</v>
@@ -1776,10 +1792,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.51</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>488.58</v>
+        <v>520.39</v>
       </c>
       <c r="N21" t="n">
         <v>21.2</v>
@@ -1841,10 +1857,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>997.47</v>
+        <v>1033.19</v>
       </c>
       <c r="N22" t="n">
         <v>47.5</v>
@@ -1887,7 +1903,7 @@
         <v>101.38</v>
       </c>
       <c r="G23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="H23" t="n">
         <v>14.5</v>
@@ -1904,10 +1920,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.21</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>101.59</v>
+        <v>101.38</v>
       </c>
       <c r="N23" t="n">
         <v>24.5</v>
@@ -1965,10 +1981,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>105.73</v>
+        <v>105.4</v>
       </c>
       <c r="N24" t="n">
         <v>35.2</v>
@@ -2031,8 +2047,12 @@
           <t>🟡未來合理</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>124.74</v>
+      </c>
       <c r="N25" t="n">
         <v>25</v>
       </c>
@@ -2087,10 +2107,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>232.69</v>
+        <v>240.14</v>
       </c>
       <c r="N26" t="n">
         <v>23.3</v>
@@ -2137,7 +2157,7 @@
         <v>368.34</v>
       </c>
       <c r="G27" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="H27" t="n">
         <v>26.8</v>
@@ -2153,8 +2173,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>368.34</v>
+      </c>
       <c r="N27" t="n">
         <v>41.9</v>
       </c>
@@ -2214,8 +2238,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>224.97</v>
+      </c>
       <c r="N28" t="n">
         <v>68.7</v>
       </c>
@@ -2259,7 +2287,7 @@
         <v>1883.11</v>
       </c>
       <c r="G29" t="n">
-        <v>62.3</v>
+        <v>64.7</v>
       </c>
       <c r="H29" t="n">
         <v>27.9</v>
@@ -2276,10 +2304,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1794.62</v>
+        <v>1883.11</v>
       </c>
       <c r="N29" t="n">
         <v>52</v>
@@ -2340,8 +2368,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>341.65</v>
+      </c>
       <c r="N30" t="n">
         <v>58.9</v>
       </c>
@@ -2402,10 +2434,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>283.65</v>
+        <v>278.6</v>
       </c>
       <c r="N31" t="n">
         <v>21.7</v>
@@ -2454,7 +2486,7 @@
         <v>69.52</v>
       </c>
       <c r="G32" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="H32" t="n">
         <v>19.7</v>
@@ -2470,8 +2502,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>69.52</v>
+      </c>
       <c r="N32" t="n">
         <v>11.3</v>
       </c>
@@ -2530,10 +2566,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>115.69</v>
+        <v>114.6</v>
       </c>
       <c r="N33" t="n">
         <v>24.3</v>
@@ -2593,10 +2629,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>157.6</v>
+        <v>164.1</v>
       </c>
       <c r="N34" t="n">
         <v>30.6</v>
@@ -2641,7 +2677,7 @@
         <v>455.1</v>
       </c>
       <c r="G35" t="n">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="H35" t="n">
         <v>0.7</v>
@@ -2658,10 +2694,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>432.35</v>
+        <v>455.1</v>
       </c>
       <c r="N35" t="n">
         <v>36.9</v>
@@ -2723,10 +2759,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>334.69</v>
+        <v>351.28</v>
       </c>
       <c r="N36" t="n">
         <v>39</v>
@@ -2787,8 +2823,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>101.76</v>
+      </c>
       <c r="N37" t="n">
         <v>21.3</v>
       </c>
@@ -2849,10 +2889,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>372.97</v>
+        <v>368.57</v>
       </c>
       <c r="N38" t="n">
         <v>33.1</v>
@@ -2914,10 +2954,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>113.32</v>
+        <v>110.93</v>
       </c>
       <c r="N39" t="n">
         <v>21.3</v>
@@ -2979,10 +3019,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>275.86</v>
+        <v>277.07</v>
       </c>
       <c r="N40" t="n">
         <v>33.4</v>
@@ -3044,10 +3084,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>550.25</v>
+        <v>562.6</v>
       </c>
       <c r="N41" t="n">
         <v>33.2</v>
@@ -3108,8 +3148,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>128.32</v>
+      </c>
       <c r="N42" t="n">
         <v>37.2</v>
       </c>
@@ -3170,10 +3214,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>168.52</v>
+        <v>170</v>
       </c>
       <c r="N43" t="n">
         <v>21.6</v>
@@ -3234,8 +3278,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>195.24</v>
+      </c>
       <c r="N44" t="n">
         <v>49.4</v>
       </c>
@@ -3295,8 +3343,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>69.98</v>
+      </c>
       <c r="N45" t="n">
         <v>33.8</v>
       </c>
@@ -3356,8 +3408,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>198.43</v>
+      </c>
       <c r="N46" t="n">
         <v>24.4</v>
       </c>
@@ -3417,8 +3473,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>127.18</v>
+      </c>
       <c r="N47" t="n">
         <v>31</v>
       </c>
@@ -3478,8 +3538,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>206.43</v>
+      </c>
       <c r="N48" t="n">
         <v>62.4</v>
       </c>
@@ -3539,8 +3603,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>332.02</v>
+      </c>
       <c r="N49" t="n">
         <v>28</v>
       </c>
@@ -3584,7 +3652,7 @@
         <v>129.16</v>
       </c>
       <c r="G50" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="H50" t="n">
         <v>1.5</v>
@@ -3600,8 +3668,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>129.16</v>
+      </c>
       <c r="N50" t="n">
         <v>21.6</v>
       </c>
@@ -3661,8 +3733,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>278</v>
+      </c>
       <c r="N51" t="n">
         <v>35.5</v>
       </c>
@@ -3710,7 +3786,7 @@
         <v>64.95</v>
       </c>
       <c r="G52" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="H52" t="n">
         <v>9.800000000000001</v>
@@ -3726,8 +3802,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>64.95</v>
+      </c>
       <c r="N52" t="n">
         <v>155.3</v>
       </c>
@@ -3787,8 +3867,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>44.38</v>
+      </c>
       <c r="N53" t="n">
         <v>25.1</v>
       </c>
@@ -3849,10 +3933,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>365.02</v>
+        <v>372.45</v>
       </c>
       <c r="N54" t="n">
         <v>36.4</v>
@@ -3914,10 +3998,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>268.87</v>
+        <v>268.57</v>
       </c>
       <c r="N55" t="n">
         <v>33.1</v>
@@ -3979,10 +4063,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>163.72</v>
+        <v>166.42</v>
       </c>
       <c r="N56" t="n">
         <v>34.8</v>
@@ -4043,8 +4127,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>101.28</v>
+      </c>
       <c r="N57" t="n">
         <v>40.8</v>
       </c>
@@ -4105,10 +4193,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>54.77</v>
+        <v>54.28</v>
       </c>
       <c r="N58" t="n">
         <v>40.2</v>
@@ -4169,8 +4257,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>509.64</v>
+      </c>
       <c r="N59" t="n">
         <v>206.1</v>
       </c>
@@ -4230,8 +4322,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>88.66</v>
+      </c>
       <c r="N60" t="n">
         <v>15.2</v>
       </c>
@@ -4291,8 +4387,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>105.73</v>
+      </c>
       <c r="N61" t="n">
         <v>22.4</v>
       </c>
@@ -4352,8 +4452,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>266.4</v>
+      </c>
       <c r="N62" t="n">
         <v>23.3</v>
       </c>
@@ -4397,7 +4501,7 @@
         <v>48.34</v>
       </c>
       <c r="G63" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H63" t="n">
         <v>1.7</v>
@@ -4413,8 +4517,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>48.34</v>
+      </c>
       <c r="N63" t="n">
         <v>66.40000000000001</v>
       </c>
@@ -4474,8 +4582,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>76.54000000000001</v>
+      </c>
       <c r="N64" t="n">
         <v>24</v>
       </c>
@@ -4520,7 +4632,7 @@
         <v>86</v>
       </c>
       <c r="F65" t="n">
-        <v>22.24</v>
+        <v>22.25</v>
       </c>
       <c r="G65" t="n">
         <v>22.4</v>
@@ -4539,8 +4651,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M65" t="n">
+        <v>22.24</v>
+      </c>
       <c r="N65" t="n">
         <v>24.2</v>
       </c>
@@ -4600,8 +4716,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>32.19</v>
+      </c>
       <c r="N66" t="n">
         <v>17.2</v>
       </c>
@@ -4662,10 +4782,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-1.65</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>519.62</v>
+        <v>511.06</v>
       </c>
       <c r="N67" t="n">
         <v>18.5</v>
@@ -4726,8 +4846,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>133.49</v>
+      </c>
       <c r="N68" t="n">
         <v>22</v>
       </c>
@@ -4787,8 +4911,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>147.02</v>
+      </c>
       <c r="N69" t="n">
         <v>20.9</v>
       </c>
@@ -4848,8 +4976,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1683.13</v>
+      </c>
       <c r="N70" t="n">
         <v>29.6</v>
       </c>
@@ -4913,8 +5045,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>99.97</v>
+      </c>
       <c r="N71" t="n">
         <v>15</v>
       </c>
@@ -4975,10 +5111,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>340.36</v>
+        <v>340.88</v>
       </c>
       <c r="N72" t="n">
         <v>33.9</v>
@@ -5039,8 +5175,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>98.06</v>
+      </c>
       <c r="N73" t="n">
         <v>20.5</v>
       </c>
@@ -5100,8 +5240,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>157.93</v>
+      </c>
       <c r="N74" t="n">
         <v>14.9</v>
       </c>
@@ -5166,10 +5310,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>192.53</v>
+        <v>194.97</v>
       </c>
       <c r="N75" t="n">
         <v>111.7</v>
@@ -5217,13 +5361,13 @@
         <v>43.6</v>
       </c>
       <c r="H76" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="I76" t="n">
         <v>51.8</v>
       </c>
       <c r="J76" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5231,10 +5375,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1206.505</v>
+        <v>1229.93</v>
       </c>
       <c r="N76" t="n">
         <v>101.3</v>
@@ -5296,10 +5440,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>73.81</v>
+        <v>73.78</v>
       </c>
       <c r="N77" t="n">
         <v>49.2</v>
@@ -5360,8 +5504,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>173.97</v>
+      </c>
       <c r="N78" t="n">
         <v>17.8</v>
       </c>
@@ -5419,8 +5567,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>135.44</v>
+      </c>
       <c r="N79" t="n">
         <v>40.1</v>
       </c>
@@ -5478,8 +5630,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>9.210000000000001</v>
+      </c>
       <c r="N80" t="n">
         <v>14.6</v>
       </c>
@@ -5521,7 +5677,7 @@
         <v>91.8</v>
       </c>
       <c r="G81" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H81" t="n">
         <v>3.7</v>
@@ -5537,8 +5693,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>91.8</v>
+      </c>
       <c r="N81" t="n">
         <v>14</v>
       </c>
@@ -5596,8 +5756,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>107.37</v>
+      </c>
       <c r="N82" t="n">
         <v>16.4</v>
       </c>
@@ -5654,10 +5818,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>341.98</v>
+        <v>342.46</v>
       </c>
       <c r="N83" t="n">
         <v>23.4</v>
@@ -5718,8 +5882,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>78.58</v>
+      </c>
       <c r="N84" t="n">
         <v>20.4</v>
       </c>
@@ -5765,7 +5933,7 @@
         <v>52.81</v>
       </c>
       <c r="G85" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H85" t="n">
         <v>11.8</v>
@@ -5779,8 +5947,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>52.81</v>
+      </c>
       <c r="N85" t="n">
         <v>35.8</v>
       </c>
@@ -5843,10 +6015,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>148.81</v>
+        <v>147.54</v>
       </c>
       <c r="N86" t="n">
         <v>21.6</v>
@@ -5908,10 +6080,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>1132.33</v>
+        <v>1145.28</v>
       </c>
       <c r="N87" t="n">
         <v>40.8</v>
@@ -5972,8 +6144,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>43.39</v>
+      </c>
       <c r="N88" t="n">
         <v>35</v>
       </c>
@@ -6032,10 +6208,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-2.62</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>239.07</v>
+        <v>232.8</v>
       </c>
       <c r="N89" t="n">
         <v>18</v>
@@ -6099,10 +6275,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>337.53</v>
+        <v>343.25</v>
       </c>
       <c r="N90" t="n">
         <v>47.7</v>
@@ -6158,10 +6334,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>112.93</v>
+        <v>115.7</v>
       </c>
       <c r="N91" t="n">
         <v>32.2</v>
@@ -6225,10 +6401,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>521.58</v>
+        <v>539.49</v>
       </c>
       <c r="N92" t="n">
         <v>8.1</v>
@@ -6275,7 +6451,7 @@
         <v>95.5</v>
       </c>
       <c r="G93" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H93" t="n">
         <v>1.3</v>
@@ -6291,8 +6467,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>95.5</v>
+      </c>
       <c r="N93" t="n">
         <v>10</v>
       </c>
@@ -6340,8 +6520,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>63.8</v>
+      </c>
       <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
@@ -6389,8 +6573,12 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>112.41</v>
+      </c>
       <c r="N95" t="n">
         <v>40.1</v>
       </c>
@@ -6445,10 +6633,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>-1.35</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>373.63</v>
+        <v>368.58</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
@@ -6596,7 +6784,7 @@
         <v>368.34</v>
       </c>
       <c r="G2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="H2" t="n">
         <v>26.8</v>
@@ -6612,8 +6800,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>368.34</v>
+      </c>
       <c r="N2" t="n">
         <v>41.9</v>
       </c>
@@ -6673,8 +6865,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>224.97</v>
+      </c>
       <c r="N3" t="n">
         <v>68.7</v>
       </c>
@@ -6718,7 +6914,7 @@
         <v>1883.11</v>
       </c>
       <c r="G4" t="n">
-        <v>62.3</v>
+        <v>64.7</v>
       </c>
       <c r="H4" t="n">
         <v>27.9</v>
@@ -6735,10 +6931,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.93</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1794.62</v>
+        <v>1883.11</v>
       </c>
       <c r="N4" t="n">
         <v>52</v>
@@ -6799,8 +6995,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>341.65</v>
+      </c>
       <c r="N5" t="n">
         <v>58.9</v>
       </c>
@@ -6861,10 +7061,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.78</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>283.65</v>
+        <v>278.6</v>
       </c>
       <c r="N6" t="n">
         <v>21.7</v>
@@ -6913,7 +7113,7 @@
         <v>69.52</v>
       </c>
       <c r="G7" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="H7" t="n">
         <v>19.7</v>
@@ -6929,8 +7129,12 @@
           <t>🟢成長未反映</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>69.52</v>
+      </c>
       <c r="N7" t="n">
         <v>11.3</v>
       </c>
@@ -6989,10 +7193,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>115.69</v>
+        <v>114.6</v>
       </c>
       <c r="N8" t="n">
         <v>24.3</v>
@@ -7163,10 +7367,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>157.6</v>
+        <v>164.1</v>
       </c>
       <c r="N2" t="n">
         <v>30.6</v>
@@ -7211,7 +7415,7 @@
         <v>455.1</v>
       </c>
       <c r="G3" t="n">
-        <v>31.9</v>
+        <v>32.4</v>
       </c>
       <c r="H3" t="n">
         <v>0.7</v>
@@ -7228,10 +7432,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>432.35</v>
+        <v>455.1</v>
       </c>
       <c r="N3" t="n">
         <v>36.9</v>
@@ -7293,10 +7497,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>334.69</v>
+        <v>351.28</v>
       </c>
       <c r="N4" t="n">
         <v>39</v>
@@ -7357,8 +7561,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>101.76</v>
+      </c>
       <c r="N5" t="n">
         <v>21.3</v>
       </c>
@@ -7419,10 +7627,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-1.18</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>372.97</v>
+        <v>368.57</v>
       </c>
       <c r="N6" t="n">
         <v>33.1</v>
@@ -7484,10 +7692,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-2.11</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>113.32</v>
+        <v>110.93</v>
       </c>
       <c r="N7" t="n">
         <v>21.3</v>
@@ -7549,10 +7757,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>275.86</v>
+        <v>277.07</v>
       </c>
       <c r="N8" t="n">
         <v>33.4</v>
@@ -7614,10 +7822,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>550.25</v>
+        <v>562.6</v>
       </c>
       <c r="N9" t="n">
         <v>33.2</v>
@@ -7678,8 +7886,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>128.32</v>
+      </c>
       <c r="N10" t="n">
         <v>37.2</v>
       </c>
@@ -7740,10 +7952,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>168.52</v>
+        <v>170</v>
       </c>
       <c r="N11" t="n">
         <v>21.6</v>
@@ -7804,8 +8016,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>195.24</v>
+      </c>
       <c r="N12" t="n">
         <v>49.4</v>
       </c>
@@ -7865,8 +8081,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>69.98</v>
+      </c>
       <c r="N13" t="n">
         <v>33.8</v>
       </c>
@@ -7926,8 +8146,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>198.43</v>
+      </c>
       <c r="N14" t="n">
         <v>24.4</v>
       </c>
@@ -7987,8 +8211,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>127.18</v>
+      </c>
       <c r="N15" t="n">
         <v>31</v>
       </c>
@@ -8048,8 +8276,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>206.43</v>
+      </c>
       <c r="N16" t="n">
         <v>62.4</v>
       </c>
@@ -8109,8 +8341,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>332.02</v>
+      </c>
       <c r="N17" t="n">
         <v>28</v>
       </c>
@@ -8154,7 +8390,7 @@
         <v>129.16</v>
       </c>
       <c r="G18" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="H18" t="n">
         <v>1.5</v>
@@ -8170,8 +8406,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>129.16</v>
+      </c>
       <c r="N18" t="n">
         <v>21.6</v>
       </c>
@@ -8231,8 +8471,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>278</v>
+      </c>
       <c r="N19" t="n">
         <v>35.5</v>
       </c>
@@ -8280,7 +8524,7 @@
         <v>64.95</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="H20" t="n">
         <v>9.800000000000001</v>
@@ -8296,8 +8540,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>64.95</v>
+      </c>
       <c r="N20" t="n">
         <v>155.3</v>
       </c>
@@ -8357,8 +8605,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>44.38</v>
+      </c>
       <c r="N21" t="n">
         <v>25.1</v>
       </c>
@@ -8419,10 +8671,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>365.02</v>
+        <v>372.45</v>
       </c>
       <c r="N22" t="n">
         <v>36.4</v>
@@ -8484,10 +8736,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>268.87</v>
+        <v>268.57</v>
       </c>
       <c r="N23" t="n">
         <v>33.1</v>
@@ -8549,10 +8801,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>163.72</v>
+        <v>166.42</v>
       </c>
       <c r="N24" t="n">
         <v>34.8</v>
@@ -8613,8 +8865,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>101.28</v>
+      </c>
       <c r="N25" t="n">
         <v>40.8</v>
       </c>
@@ -8675,10 +8931,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>54.77</v>
+        <v>54.28</v>
       </c>
       <c r="N26" t="n">
         <v>40.2</v>
@@ -8739,8 +8995,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>509.64</v>
+      </c>
       <c r="N27" t="n">
         <v>206.1</v>
       </c>
@@ -8800,8 +9060,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.66</v>
+      </c>
       <c r="N28" t="n">
         <v>15.2</v>
       </c>
@@ -8861,8 +9125,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>105.73</v>
+      </c>
       <c r="N29" t="n">
         <v>22.4</v>
       </c>
@@ -8922,8 +9190,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>266.4</v>
+      </c>
       <c r="N30" t="n">
         <v>23.3</v>
       </c>
@@ -8967,7 +9239,7 @@
         <v>48.34</v>
       </c>
       <c r="G31" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="H31" t="n">
         <v>1.7</v>
@@ -8983,8 +9255,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>48.34</v>
+      </c>
       <c r="N31" t="n">
         <v>66.40000000000001</v>
       </c>
@@ -9044,8 +9320,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>76.54000000000001</v>
+      </c>
       <c r="N32" t="n">
         <v>24</v>
       </c>
@@ -9090,7 +9370,7 @@
         <v>86</v>
       </c>
       <c r="F33" t="n">
-        <v>22.24</v>
+        <v>22.25</v>
       </c>
       <c r="G33" t="n">
         <v>22.4</v>
@@ -9109,8 +9389,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M33" t="n">
+        <v>22.24</v>
+      </c>
       <c r="N33" t="n">
         <v>24.2</v>
       </c>
@@ -9170,8 +9454,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>32.19</v>
+      </c>
       <c r="N34" t="n">
         <v>17.2</v>
       </c>
@@ -9232,10 +9520,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>-1.65</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>519.62</v>
+        <v>511.06</v>
       </c>
       <c r="N35" t="n">
         <v>18.5</v>
@@ -9296,8 +9584,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>133.49</v>
+      </c>
       <c r="N36" t="n">
         <v>22</v>
       </c>
@@ -9357,8 +9649,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>147.02</v>
+      </c>
       <c r="N37" t="n">
         <v>20.9</v>
       </c>
@@ -9418,8 +9714,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1683.13</v>
+      </c>
       <c r="N38" t="n">
         <v>29.6</v>
       </c>
@@ -9483,8 +9783,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>99.97</v>
+      </c>
       <c r="N39" t="n">
         <v>15</v>
       </c>
@@ -9545,10 +9849,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>340.36</v>
+        <v>340.88</v>
       </c>
       <c r="N40" t="n">
         <v>33.9</v>
@@ -9609,8 +9913,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>98.06</v>
+      </c>
       <c r="N41" t="n">
         <v>20.5</v>
       </c>
@@ -9670,8 +9978,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>157.93</v>
+      </c>
       <c r="N42" t="n">
         <v>14.9</v>
       </c>
@@ -9736,10 +10048,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>192.53</v>
+        <v>194.97</v>
       </c>
       <c r="N43" t="n">
         <v>111.7</v>
@@ -9787,13 +10099,13 @@
         <v>43.6</v>
       </c>
       <c r="H44" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="I44" t="n">
         <v>51.8</v>
       </c>
       <c r="J44" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -9801,10 +10113,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1206.505</v>
+        <v>1229.93</v>
       </c>
       <c r="N44" t="n">
         <v>101.3</v>
@@ -9866,10 +10178,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>73.81</v>
+        <v>73.78</v>
       </c>
       <c r="N45" t="n">
         <v>49.2</v>
@@ -9930,8 +10242,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>173.97</v>
+      </c>
       <c r="N46" t="n">
         <v>17.8</v>
       </c>
@@ -9989,8 +10305,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>135.44</v>
+      </c>
       <c r="N47" t="n">
         <v>40.1</v>
       </c>
@@ -10048,8 +10368,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>9.210000000000001</v>
+      </c>
       <c r="N48" t="n">
         <v>14.6</v>
       </c>
@@ -10091,7 +10415,7 @@
         <v>91.8</v>
       </c>
       <c r="G49" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H49" t="n">
         <v>3.7</v>
@@ -10107,8 +10431,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>91.8</v>
+      </c>
       <c r="N49" t="n">
         <v>14</v>
       </c>
@@ -10166,8 +10494,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>107.37</v>
+      </c>
       <c r="N50" t="n">
         <v>16.4</v>
       </c>
@@ -10224,10 +10556,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>341.98</v>
+        <v>342.46</v>
       </c>
       <c r="N51" t="n">
         <v>23.4</v>
@@ -10288,8 +10620,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>78.58</v>
+      </c>
       <c r="N52" t="n">
         <v>20.4</v>
       </c>
@@ -10335,7 +10671,7 @@
         <v>52.81</v>
       </c>
       <c r="G53" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H53" t="n">
         <v>11.8</v>
@@ -10349,8 +10685,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>52.81</v>
+      </c>
       <c r="N53" t="n">
         <v>35.8</v>
       </c>
@@ -10413,10 +10753,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>148.81</v>
+        <v>147.54</v>
       </c>
       <c r="N54" t="n">
         <v>21.6</v>
@@ -10478,10 +10818,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1132.33</v>
+        <v>1145.28</v>
       </c>
       <c r="N55" t="n">
         <v>40.8</v>
@@ -10542,8 +10882,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>43.39</v>
+      </c>
       <c r="N56" t="n">
         <v>35</v>
       </c>
@@ -10602,10 +10946,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>-2.62</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>239.07</v>
+        <v>232.8</v>
       </c>
       <c r="N57" t="n">
         <v>18</v>
@@ -10669,10 +11013,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>337.53</v>
+        <v>343.25</v>
       </c>
       <c r="N58" t="n">
         <v>47.7</v>
@@ -10728,10 +11072,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>112.93</v>
+        <v>115.7</v>
       </c>
       <c r="N59" t="n">
         <v>32.2</v>
@@ -10795,10 +11139,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>521.58</v>
+        <v>539.49</v>
       </c>
       <c r="N60" t="n">
         <v>8.1</v>
@@ -10845,7 +11189,7 @@
         <v>95.5</v>
       </c>
       <c r="G61" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H61" t="n">
         <v>1.3</v>
@@ -10861,8 +11205,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>95.5</v>
+      </c>
       <c r="N61" t="n">
         <v>10</v>
       </c>
@@ -10910,8 +11258,12 @@
           <t>🟢未來便宜</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>63.8</v>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
@@ -11070,8 +11422,12 @@
           <t>🟢便宜</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>112.41</v>
+      </c>
       <c r="N2" t="n">
         <v>40.1</v>
       </c>
@@ -11245,10 +11601,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>11.97</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>248.64</v>
+        <v>278.39</v>
       </c>
       <c r="N2" t="n">
         <v>89.09999999999999</v>
@@ -11314,10 +11670,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-1.21</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>377.27</v>
+        <v>372.72</v>
       </c>
       <c r="N3" t="n">
         <v>21.1</v>
@@ -11377,10 +11733,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8.390000000000001</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>379.09</v>
+        <v>410.91</v>
       </c>
       <c r="N4" t="n">
         <v>65.8</v>
@@ -11440,10 +11796,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>10.82</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>626.84</v>
+        <v>694.64</v>
       </c>
       <c r="N5" t="n">
         <v>39.8</v>
@@ -11503,10 +11859,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-0.72</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>283.78</v>
+        <v>281.74</v>
       </c>
       <c r="N6" t="n">
         <v>146.7</v>
@@ -11566,10 +11922,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>223</v>
+        <v>255.79</v>
       </c>
       <c r="N7" t="n">
         <v>15.6</v>
@@ -11633,10 +11989,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.16</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>586.45</v>
+        <v>651.88</v>
       </c>
       <c r="N8" t="n">
         <v>91.90000000000001</v>
@@ -11698,10 +12054,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>479.5</v>
+        <v>478.93</v>
       </c>
       <c r="N9" t="n">
         <v>15.7</v>
@@ -11761,10 +12117,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>380.56</v>
+        <v>391.22</v>
       </c>
       <c r="N10" t="n">
         <v>5.3</v>
@@ -11825,8 +12181,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>411.84</v>
+      </c>
       <c r="N11" t="n">
         <v>4.8</v>
       </c>
@@ -11888,8 +12248,12 @@
           <t>🔴未來過熱</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2050.39</v>
+      </c>
       <c r="N12" t="n">
         <v>42.3</v>
       </c>
@@ -12067,10 +12431,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-0.62</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>952.54</v>
+        <v>946.6799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>28.3</v>
@@ -12113,7 +12477,7 @@
         <v>10.7</v>
       </c>
       <c r="G3" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="H3" t="n">
         <v>10.8</v>
@@ -12129,8 +12493,12 @@
           <t>🟠未來偏貴</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10.7</v>
+      </c>
       <c r="N3" t="n">
         <v>31.8</v>
       </c>
@@ -12185,10 +12553,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>303.95</v>
+        <v>306.97</v>
       </c>
       <c r="N4" t="n">
         <v>42.1</v>
@@ -12250,10 +12618,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>816.98</v>
+        <v>851.4</v>
       </c>
       <c r="N5" t="n">
         <v>30.7</v>
@@ -12313,10 +12681,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>266.77</v>
+        <v>277.75</v>
       </c>
       <c r="N6" t="n">
         <v>16.8</v>
@@ -12376,10 +12744,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>498.66</v>
+        <v>495.95</v>
       </c>
       <c r="N7" t="n">
         <v>10.3</v>

--- a/data/美股PE監看表.xlsx
+++ b/data/美股PE監看表.xlsx
@@ -543,19 +543,19 @@
         <v>86</v>
       </c>
       <c r="F2" t="n">
-        <v>278.39</v>
+        <v>301.71</v>
       </c>
       <c r="G2" t="n">
-        <v>78.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>36.5</v>
+        <v>39.6</v>
       </c>
       <c r="I2" t="n">
         <v>11.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>278.39</v>
@@ -612,19 +612,19 @@
         <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>372.72</v>
+        <v>375.32</v>
       </c>
       <c r="G3" t="n">
-        <v>86.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>33.4</v>
+        <v>33.7</v>
       </c>
       <c r="I3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
         <v>372.72</v>
@@ -675,19 +675,19 @@
         <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>410.91</v>
+        <v>433.33</v>
       </c>
       <c r="G4" t="n">
-        <v>77.2</v>
+        <v>81.5</v>
       </c>
       <c r="H4" t="n">
-        <v>31.1</v>
+        <v>32.8</v>
       </c>
       <c r="I4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="M4" t="n">
         <v>410.91</v>
@@ -738,19 +738,19 @@
         <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>694.64</v>
+        <v>723</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>30.6</v>
+        <v>31.9</v>
       </c>
       <c r="I5" t="n">
         <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>5.88</v>
+        <v>6.13</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="M5" t="n">
         <v>694.64</v>
@@ -801,19 +801,19 @@
         <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>281.74</v>
+        <v>289.36</v>
       </c>
       <c r="G6" t="n">
-        <v>34</v>
+        <v>34.9</v>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="I6" t="n">
         <v>6.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
         <v>281.74</v>
@@ -864,19 +864,19 @@
         <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>255.79</v>
+        <v>255.54</v>
       </c>
       <c r="G7" t="n">
-        <v>121.2</v>
+        <v>121.1</v>
       </c>
       <c r="H7" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>6.67</v>
+        <v>6.65</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="M7" t="n">
         <v>255.79</v>
@@ -931,19 +931,19 @@
         <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>651.88</v>
+        <v>638.72</v>
       </c>
       <c r="G8" t="n">
-        <v>34.9</v>
+        <v>34.2</v>
       </c>
       <c r="H8" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="I8" t="n">
         <v>3.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.02</v>
       </c>
       <c r="M8" t="n">
         <v>651.88</v>
@@ -998,13 +998,13 @@
         <v>47</v>
       </c>
       <c r="F9" t="n">
-        <v>478.93</v>
+        <v>490.56</v>
       </c>
       <c r="G9" t="n">
-        <v>155</v>
+        <v>158.8</v>
       </c>
       <c r="H9" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="I9" t="n">
         <v>-4.9</v>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
         <v>478.93</v>
@@ -1041,12 +1041,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coherent, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>391.22</v>
+        <v>297.89</v>
       </c>
       <c r="G10" t="n">
-        <v>170.8</v>
+        <v>101.4</v>
       </c>
       <c r="H10" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="M10" t="n">
-        <v>391.22</v>
+        <v>277.75</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>16.8</v>
       </c>
       <c r="O10" t="n">
-        <v>12.84</v>
+        <v>0.66</v>
       </c>
       <c r="P10" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1104,17 +1104,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Coherent, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1123,20 +1123,18 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>411.84</v>
+        <v>394.47</v>
       </c>
       <c r="G11" t="n">
-        <v>342.2</v>
+        <v>172.3</v>
       </c>
       <c r="H11" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-33.5</v>
-      </c>
+        <v>31.8</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -1144,46 +1142,42 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="M11" t="n">
-        <v>411.84</v>
+        <v>391.22</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.89</v>
+        <v>12.84</v>
       </c>
       <c r="P11" t="n">
-        <v>15.2</v>
+        <v>16.9</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>⚠️EPS落後營收(EPS3y -34&lt;營收CAGR 15×50%) | ⚠️ROE滑落(5&lt;5年均17×67%)</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1195,15 +1189,17 @@
         <v>22</v>
       </c>
       <c r="F12" t="n">
-        <v>2050.39</v>
+        <v>420.6</v>
       </c>
       <c r="G12" t="n">
-        <v>67.2</v>
+        <v>349.5</v>
       </c>
       <c r="H12" t="n">
-        <v>151.5</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>46.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-33.5</v>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -1211,19 +1207,19 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M12" t="n">
-        <v>2050.39</v>
+        <v>411.84</v>
       </c>
       <c r="N12" t="n">
-        <v>42.3</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.05</v>
+        <v>3.89</v>
       </c>
       <c r="P12" t="n">
-        <v>-9</v>
+        <v>15.2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1232,7 +1228,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>⚠️現金流為負(含金量-0.05)</t>
+          <t>⚠️EPS落後營收(EPS3y -34&lt;營收CAGR 15×50%) | ⚠️ROE滑落(5&lt;5年均17×67%)</t>
         </is>
       </c>
       <c r="S12" t="inlineStr"/>
@@ -1240,75 +1236,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Sandisk Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
-        <v>946.6799999999999</v>
+        <v>2273.73</v>
       </c>
       <c r="G13" t="n">
-        <v>47.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.89</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>🟠未來偏貴</t>
+          <t>🔴未來過熱</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>10.89</v>
       </c>
       <c r="M13" t="n">
-        <v>946.6799999999999</v>
+        <v>2050.39</v>
       </c>
       <c r="N13" t="n">
-        <v>28.3</v>
+        <v>42.3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.65</v>
+        <v>-0.05</v>
       </c>
       <c r="P13" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+        <v>-9</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>⚠️現金流為負(含金量-0.05)</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>NVMI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Nova Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1318,26 +1318,26 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F14" t="n">
-        <v>10.7</v>
+        <v>542.9400000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="H14" t="n">
-        <v>10.8</v>
+        <v>41.8</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3</v>
+        <v>20.8</v>
       </c>
       <c r="J14" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1345,96 +1345,98 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M14" t="n">
-        <v>10.7</v>
+        <v>520.39</v>
       </c>
       <c r="N14" t="n">
-        <v>31.8</v>
+        <v>21.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.22</v>
+        <v>0.95</v>
       </c>
       <c r="P14" t="n">
-        <v>5.4</v>
+        <v>20.6</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>155.3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
-        <v>306.97</v>
+        <v>935.47</v>
       </c>
       <c r="G15" t="n">
-        <v>75.2</v>
+        <v>47</v>
       </c>
       <c r="H15" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>32.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.85</v>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="M15" t="n">
-        <v>306.97</v>
+        <v>946.6799999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>42.1</v>
+        <v>28.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="P15" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>8.9</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1444,85 +1446,83 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
-        <v>851.4</v>
+        <v>10.49</v>
       </c>
       <c r="G16" t="n">
-        <v>137.1</v>
+        <v>12.6</v>
       </c>
       <c r="H16" t="n">
-        <v>19.1</v>
+        <v>10.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-48.5</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>5.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="M16" t="n">
-        <v>851.4</v>
+        <v>10.7</v>
       </c>
       <c r="N16" t="n">
-        <v>30.7</v>
+        <v>31.8</v>
       </c>
       <c r="O16" t="n">
-        <v>4.88</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>5.4</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F17" t="n">
-        <v>277.75</v>
+        <v>334.82</v>
       </c>
       <c r="G17" t="n">
-        <v>94.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>29.5</v>
+        <v>21.1</v>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
@@ -1532,19 +1532,19 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="M17" t="n">
-        <v>277.75</v>
+        <v>306.97</v>
       </c>
       <c r="N17" t="n">
-        <v>16.8</v>
+        <v>42.1</v>
       </c>
       <c r="O17" t="n">
-        <v>0.66</v>
+        <v>1.59</v>
       </c>
       <c r="P17" t="n">
-        <v>16.4</v>
+        <v>19.6</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1557,17 +1557,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BRK-B</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1576,18 +1576,20 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F18" t="n">
-        <v>495.95</v>
+        <v>858.0599999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>14.8</v>
+        <v>138.2</v>
       </c>
       <c r="H18" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>19.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-48.5</v>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
@@ -1595,19 +1597,19 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="M18" t="n">
-        <v>495.95</v>
+        <v>851.4</v>
       </c>
       <c r="N18" t="n">
-        <v>10.3</v>
+        <v>30.7</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6899999999999999</v>
+        <v>4.88</v>
       </c>
       <c r="P18" t="n">
-        <v>7.7</v>
+        <v>-1</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1620,67 +1622,65 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>BRK-B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fortinet, Inc.</t>
+          <t>Berkshire Hathaway Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
-        <v>155.42</v>
+        <v>499.99</v>
       </c>
       <c r="G19" t="n">
-        <v>59.8</v>
+        <v>14.9</v>
       </c>
       <c r="H19" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.51</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>155.42</v>
+        <v>495.95</v>
       </c>
       <c r="N19" t="n">
-        <v>155.7</v>
+        <v>10.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>7.7</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>1108.9</v>
-      </c>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1707,19 +1707,19 @@
         <v>87</v>
       </c>
       <c r="F20" t="n">
-        <v>31.29</v>
+        <v>31.67</v>
       </c>
       <c r="G20" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="H20" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
         <v>10</v>
       </c>
       <c r="J20" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
         <v>31.29</v>
@@ -1750,41 +1750,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NVMI</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nova Ltd.</t>
+          <t>Caterpillar Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F21" t="n">
-        <v>520.39</v>
+        <v>1064.9</v>
       </c>
       <c r="G21" t="n">
-        <v>60.3</v>
+        <v>52.8</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>28.1</v>
       </c>
       <c r="I21" t="n">
-        <v>20.8</v>
+        <v>14.1</v>
       </c>
       <c r="J21" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1792,40 +1792,38 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="M21" t="n">
-        <v>520.39</v>
+        <v>1033.19</v>
       </c>
       <c r="N21" t="n">
-        <v>21.2</v>
+        <v>47.5</v>
       </c>
       <c r="O21" t="n">
-        <v>0.95</v>
+        <v>1.32</v>
       </c>
       <c r="P21" t="n">
-        <v>20.6</v>
+        <v>7.3</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
-      <c r="S21" t="n">
-        <v>155.3</v>
-      </c>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>CCEP</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Caterpillar Inc.</t>
+          <t>Coca-Cola Europacific Partners PLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1834,19 +1832,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
-        <v>1033.19</v>
+        <v>100.07</v>
       </c>
       <c r="G22" t="n">
-        <v>51.2</v>
+        <v>20.6</v>
       </c>
       <c r="H22" t="n">
-        <v>27.2</v>
+        <v>14.3</v>
       </c>
       <c r="I22" t="n">
-        <v>14.1</v>
+        <v>7.4</v>
       </c>
       <c r="J22" t="n">
         <v>1.93</v>
@@ -1857,19 +1855,19 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>-1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>1033.19</v>
+        <v>101.38</v>
       </c>
       <c r="N22" t="n">
-        <v>47.5</v>
+        <v>24.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="P22" t="n">
-        <v>7.3</v>
+        <v>11</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -1878,17 +1876,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CCEP</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Coca-Cola Europacific Partners PLC</t>
+          <t>CF Industries Holdings, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1897,61 +1895,63 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
-        <v>101.38</v>
+        <v>108.18</v>
       </c>
       <c r="G23" t="n">
-        <v>20.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="I23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.96</v>
-      </c>
+        <v>-18.3</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M23" t="n">
-        <v>101.38</v>
+        <v>105.4</v>
       </c>
       <c r="N23" t="n">
-        <v>24.5</v>
+        <v>35.2</v>
       </c>
       <c r="O23" t="n">
-        <v>1.52</v>
+        <v>1.89</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CF Industries Holdings, Inc.</t>
+          <t>Accenture plc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1963,60 +1963,58 @@
         <v>67</v>
       </c>
       <c r="F24" t="n">
-        <v>105.4</v>
+        <v>124.44</v>
       </c>
       <c r="G24" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="H24" t="n">
-        <v>14.3</v>
+        <v>6.6</v>
       </c>
       <c r="I24" t="n">
-        <v>-18.3</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>4.2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.57</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="M24" t="n">
-        <v>105.4</v>
+        <v>124.74</v>
       </c>
       <c r="N24" t="n">
-        <v>35.2</v>
+        <v>25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.89</v>
+        <v>1.49</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>8.4</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Accenture plc</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2025,109 +2023,111 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F25" t="n">
-        <v>124.74</v>
+        <v>238.34</v>
       </c>
       <c r="G25" t="n">
-        <v>9.9</v>
+        <v>28.1</v>
       </c>
       <c r="H25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.57</v>
-      </c>
+        <v>12.2</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>🟡未來合理</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="M25" t="n">
-        <v>124.74</v>
+        <v>240.14</v>
       </c>
       <c r="N25" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.49</v>
+        <v>1.8</v>
       </c>
       <c r="P25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+        <v>11.1</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F26" t="n">
-        <v>240.14</v>
+        <v>153.62</v>
       </c>
       <c r="G26" t="n">
-        <v>28.3</v>
+        <v>59.1</v>
       </c>
       <c r="H26" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+        <v>46.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.49</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>🟡未來合理</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="M26" t="n">
-        <v>240.14</v>
+        <v>155.42</v>
       </c>
       <c r="N26" t="n">
-        <v>23.3</v>
+        <v>155.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>19.4</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>1108.9</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2154,19 +2154,19 @@
         <v>90</v>
       </c>
       <c r="F27" t="n">
-        <v>368.34</v>
+        <v>372.29</v>
       </c>
       <c r="G27" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="H27" t="n">
-        <v>26.8</v>
+        <v>27.1</v>
       </c>
       <c r="I27" t="n">
         <v>20.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="M27" t="n">
         <v>368.34</v>
@@ -2219,19 +2219,19 @@
         <v>87</v>
       </c>
       <c r="F28" t="n">
-        <v>224.97</v>
+        <v>223.95</v>
       </c>
       <c r="G28" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="H28" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="I28" t="n">
         <v>12.5</v>
       </c>
       <c r="J28" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="M28" t="n">
         <v>224.97</v>
@@ -2284,19 +2284,19 @@
         <v>86</v>
       </c>
       <c r="F29" t="n">
-        <v>1883.11</v>
+        <v>1989.44</v>
       </c>
       <c r="G29" t="n">
-        <v>64.7</v>
+        <v>66.8</v>
       </c>
       <c r="H29" t="n">
-        <v>27.9</v>
+        <v>29.5</v>
       </c>
       <c r="I29" t="n">
         <v>21.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="M29" t="n">
         <v>1883.11</v>
@@ -2349,19 +2349,19 @@
         <v>86</v>
       </c>
       <c r="F30" t="n">
-        <v>341.65</v>
+        <v>343.09</v>
       </c>
       <c r="G30" t="n">
-        <v>29.7</v>
+        <v>29.9</v>
       </c>
       <c r="H30" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="I30" t="n">
         <v>13.4</v>
       </c>
       <c r="J30" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M30" t="n">
         <v>341.65</v>
@@ -2414,7 +2414,7 @@
         <v>83</v>
       </c>
       <c r="F31" t="n">
-        <v>278.6</v>
+        <v>278.61</v>
       </c>
       <c r="G31" t="n">
         <v>37.4</v>
@@ -2483,19 +2483,19 @@
         <v>79</v>
       </c>
       <c r="F32" t="n">
-        <v>69.52</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="H32" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="I32" t="n">
         <v>17.2</v>
       </c>
       <c r="J32" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="M32" t="n">
         <v>69.52</v>
@@ -2546,19 +2546,19 @@
         <v>71</v>
       </c>
       <c r="F33" t="n">
-        <v>114.6</v>
+        <v>113.26</v>
       </c>
       <c r="G33" t="n">
-        <v>40.2</v>
+        <v>39.7</v>
       </c>
       <c r="H33" t="n">
-        <v>28.3</v>
+        <v>27.9</v>
       </c>
       <c r="I33" t="n">
         <v>24.2</v>
       </c>
       <c r="J33" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="M33" t="n">
         <v>114.6</v>
@@ -2609,19 +2609,19 @@
         <v>90</v>
       </c>
       <c r="F34" t="n">
-        <v>164.1</v>
+        <v>169.88</v>
       </c>
       <c r="G34" t="n">
-        <v>55.4</v>
+        <v>57.4</v>
       </c>
       <c r="H34" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="I34" t="n">
         <v>36.4</v>
       </c>
       <c r="J34" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="M34" t="n">
         <v>164.1</v>
@@ -2674,10 +2674,10 @@
         <v>90</v>
       </c>
       <c r="F35" t="n">
-        <v>455.1</v>
+        <v>477.57</v>
       </c>
       <c r="G35" t="n">
-        <v>32.4</v>
+        <v>33.7</v>
       </c>
       <c r="H35" t="n">
         <v>0.7</v>
@@ -2694,7 +2694,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="M35" t="n">
         <v>455.1</v>
@@ -2739,10 +2739,10 @@
         <v>90</v>
       </c>
       <c r="F36" t="n">
-        <v>351.28</v>
+        <v>353.33</v>
       </c>
       <c r="G36" t="n">
-        <v>26.7</v>
+        <v>27</v>
       </c>
       <c r="H36" t="n">
         <v>14.6</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="M36" t="n">
         <v>351.28</v>
@@ -2804,19 +2804,19 @@
         <v>90</v>
       </c>
       <c r="F37" t="n">
-        <v>101.76</v>
+        <v>104.67</v>
       </c>
       <c r="G37" t="n">
-        <v>22.3</v>
+        <v>22.9</v>
       </c>
       <c r="H37" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="I37" t="n">
         <v>43.1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M37" t="n">
         <v>101.76</v>
@@ -2869,19 +2869,19 @@
         <v>90</v>
       </c>
       <c r="F38" t="n">
-        <v>368.57</v>
+        <v>373.02</v>
       </c>
       <c r="G38" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="H38" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="I38" t="n">
         <v>12.2</v>
       </c>
       <c r="J38" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M38" t="n">
         <v>368.57</v>
@@ -2934,13 +2934,13 @@
         <v>90</v>
       </c>
       <c r="F39" t="n">
-        <v>110.93</v>
+        <v>112.32</v>
       </c>
       <c r="G39" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="H39" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="I39" t="n">
         <v>32.5</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M39" t="n">
         <v>110.93</v>
@@ -2999,19 +2999,19 @@
         <v>90</v>
       </c>
       <c r="F40" t="n">
-        <v>277.07</v>
+        <v>283.13</v>
       </c>
       <c r="G40" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="I40" t="n">
         <v>71.8</v>
       </c>
       <c r="J40" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M40" t="n">
         <v>277.07</v>
@@ -3064,7 +3064,7 @@
         <v>90</v>
       </c>
       <c r="F41" t="n">
-        <v>562.6</v>
+        <v>563.29</v>
       </c>
       <c r="G41" t="n">
         <v>20.1</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M41" t="n">
         <v>562.6</v>
@@ -3129,19 +3129,19 @@
         <v>90</v>
       </c>
       <c r="F42" t="n">
-        <v>128.32</v>
+        <v>137.49</v>
       </c>
       <c r="G42" t="n">
-        <v>22.9</v>
+        <v>24.6</v>
       </c>
       <c r="H42" t="n">
-        <v>12.7</v>
+        <v>13.6</v>
       </c>
       <c r="I42" t="n">
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="M42" t="n">
         <v>128.32</v>
@@ -3194,13 +3194,13 @@
         <v>90</v>
       </c>
       <c r="F43" t="n">
-        <v>170</v>
+        <v>168.535</v>
       </c>
       <c r="G43" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="H43" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="I43" t="n">
         <v>44</v>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="M43" t="n">
         <v>170</v>
@@ -3259,19 +3259,19 @@
         <v>90</v>
       </c>
       <c r="F44" t="n">
-        <v>195.24</v>
+        <v>194.42</v>
       </c>
       <c r="G44" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="H44" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="I44" t="n">
         <v>11.5</v>
       </c>
       <c r="J44" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M44" t="n">
         <v>195.24</v>
@@ -3324,19 +3324,19 @@
         <v>90</v>
       </c>
       <c r="F45" t="n">
-        <v>69.98</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="H45" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="I45" t="n">
         <v>34.5</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>-3.76</v>
       </c>
       <c r="M45" t="n">
         <v>69.98</v>
@@ -3389,13 +3389,13 @@
         <v>90</v>
       </c>
       <c r="F46" t="n">
-        <v>198.43</v>
+        <v>194.88</v>
       </c>
       <c r="G46" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="H46" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="I46" t="n">
         <v>21.4</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
       <c r="M46" t="n">
         <v>198.43</v>
@@ -3454,19 +3454,19 @@
         <v>90</v>
       </c>
       <c r="F47" t="n">
-        <v>127.18</v>
+        <v>125.68</v>
       </c>
       <c r="G47" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="H47" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I47" t="n">
         <v>18.7</v>
       </c>
       <c r="J47" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="M47" t="n">
         <v>127.18</v>
@@ -3519,10 +3519,10 @@
         <v>90</v>
       </c>
       <c r="F48" t="n">
-        <v>206.43</v>
+        <v>205.02</v>
       </c>
       <c r="G48" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="H48" t="n">
         <v>5.9</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
       <c r="M48" t="n">
         <v>206.43</v>
@@ -3584,19 +3584,19 @@
         <v>90</v>
       </c>
       <c r="F49" t="n">
-        <v>332.02</v>
+        <v>329.81</v>
       </c>
       <c r="G49" t="n">
         <v>14.5</v>
       </c>
       <c r="H49" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="I49" t="n">
         <v>46.2</v>
       </c>
       <c r="J49" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
       <c r="M49" t="n">
         <v>332.02</v>
@@ -3649,7 +3649,7 @@
         <v>87</v>
       </c>
       <c r="F50" t="n">
-        <v>129.16</v>
+        <v>128.14</v>
       </c>
       <c r="G50" t="n">
         <v>16.4</v>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="M50" t="n">
         <v>129.16</v>
@@ -3714,13 +3714,13 @@
         <v>87</v>
       </c>
       <c r="F51" t="n">
-        <v>278</v>
+        <v>281.21</v>
       </c>
       <c r="G51" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="H51" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="I51" t="n">
         <v>84.09999999999999</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M51" t="n">
         <v>278</v>
@@ -3783,10 +3783,10 @@
         <v>87</v>
       </c>
       <c r="F52" t="n">
-        <v>64.95</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="H52" t="n">
         <v>9.800000000000001</v>
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="M52" t="n">
         <v>64.95</v>
@@ -3848,13 +3848,13 @@
         <v>87</v>
       </c>
       <c r="F53" t="n">
-        <v>44.38</v>
+        <v>43.18</v>
       </c>
       <c r="G53" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="H53" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I53" t="n">
         <v>37.5</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="M53" t="n">
         <v>44.38</v>
@@ -3913,19 +3913,19 @@
         <v>86</v>
       </c>
       <c r="F54" t="n">
-        <v>372.45</v>
+        <v>377.75</v>
       </c>
       <c r="G54" t="n">
-        <v>60.2</v>
+        <v>61</v>
       </c>
       <c r="H54" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="I54" t="n">
         <v>21.5</v>
       </c>
       <c r="J54" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M54" t="n">
         <v>372.45</v>
@@ -3978,10 +3978,10 @@
         <v>86</v>
       </c>
       <c r="F55" t="n">
-        <v>268.57</v>
+        <v>268.86</v>
       </c>
       <c r="G55" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="H55" t="n">
         <v>30.5</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M55" t="n">
         <v>268.57</v>
@@ -4043,19 +4043,19 @@
         <v>86</v>
       </c>
       <c r="F56" t="n">
-        <v>166.42</v>
+        <v>176.32</v>
       </c>
       <c r="G56" t="n">
-        <v>45.5</v>
+        <v>48.2</v>
       </c>
       <c r="H56" t="n">
-        <v>22.1</v>
+        <v>23.4</v>
       </c>
       <c r="I56" t="n">
         <v>29.9</v>
       </c>
       <c r="J56" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="M56" t="n">
         <v>166.42</v>
@@ -4108,13 +4108,13 @@
         <v>86</v>
       </c>
       <c r="F57" t="n">
-        <v>101.28</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="H57" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="I57" t="n">
         <v>29.4</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="M57" t="n">
         <v>101.28</v>
@@ -4173,7 +4173,7 @@
         <v>86</v>
       </c>
       <c r="F58" t="n">
-        <v>54.28</v>
+        <v>54.41</v>
       </c>
       <c r="G58" t="n">
         <v>17.4</v>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="M58" t="n">
         <v>54.28</v>
@@ -4238,13 +4238,13 @@
         <v>86</v>
       </c>
       <c r="F59" t="n">
-        <v>509.64</v>
+        <v>513.6</v>
       </c>
       <c r="G59" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="H59" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="I59" t="n">
         <v>17.3</v>
@@ -4258,7 +4258,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="M59" t="n">
         <v>509.64</v>
@@ -4303,19 +4303,19 @@
         <v>86</v>
       </c>
       <c r="F60" t="n">
-        <v>88.66</v>
+        <v>87.77</v>
       </c>
       <c r="G60" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="H60" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="I60" t="n">
         <v>16.3</v>
       </c>
       <c r="J60" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M60" t="n">
         <v>88.66</v>
@@ -4368,13 +4368,13 @@
         <v>86</v>
       </c>
       <c r="F61" t="n">
-        <v>105.73</v>
+        <v>104.53</v>
       </c>
       <c r="G61" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="H61" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="I61" t="n">
         <v>35.2</v>
@@ -4388,7 +4388,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="M61" t="n">
         <v>105.73</v>
@@ -4433,13 +4433,13 @@
         <v>86</v>
       </c>
       <c r="F62" t="n">
-        <v>266.4</v>
+        <v>261</v>
       </c>
       <c r="G62" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="H62" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I62" t="n">
         <v>23.3</v>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="M62" t="n">
         <v>266.4</v>
@@ -4498,7 +4498,7 @@
         <v>86</v>
       </c>
       <c r="F63" t="n">
-        <v>48.34</v>
+        <v>47.93</v>
       </c>
       <c r="G63" t="n">
         <v>11.6</v>
@@ -4518,7 +4518,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="M63" t="n">
         <v>48.34</v>
@@ -4563,7 +4563,7 @@
         <v>86</v>
       </c>
       <c r="F64" t="n">
-        <v>76.54000000000001</v>
+        <v>76.28</v>
       </c>
       <c r="G64" t="n">
         <v>7.5</v>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="M64" t="n">
         <v>76.54000000000001</v>
@@ -4632,13 +4632,13 @@
         <v>86</v>
       </c>
       <c r="F65" t="n">
-        <v>22.25</v>
+        <v>22.46</v>
       </c>
       <c r="G65" t="n">
-        <v>22.4</v>
+        <v>21.9</v>
       </c>
       <c r="H65" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I65" t="n">
         <v>105.8</v>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>22.24</v>
+        <v>22.25</v>
       </c>
       <c r="N65" t="n">
         <v>24.2</v>
@@ -4697,10 +4697,10 @@
         <v>83</v>
       </c>
       <c r="F66" t="n">
-        <v>32.19</v>
+        <v>32</v>
       </c>
       <c r="G66" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="H66" t="n">
         <v>10.2</v>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="M66" t="n">
         <v>32.19</v>
@@ -4762,19 +4762,19 @@
         <v>83</v>
       </c>
       <c r="F67" t="n">
-        <v>511.06</v>
+        <v>518.9400000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>33.8</v>
+        <v>34.3</v>
       </c>
       <c r="H67" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="I67" t="n">
         <v>20.9</v>
       </c>
       <c r="J67" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M67" t="n">
         <v>511.06</v>
@@ -4827,13 +4827,13 @@
         <v>83</v>
       </c>
       <c r="F68" t="n">
-        <v>133.49</v>
+        <v>132.52</v>
       </c>
       <c r="G68" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I68" t="n">
         <v>34.8</v>
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="M68" t="n">
         <v>133.49</v>
@@ -4892,19 +4892,19 @@
         <v>83</v>
       </c>
       <c r="F69" t="n">
-        <v>147.02</v>
+        <v>148.69</v>
       </c>
       <c r="G69" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H69" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I69" t="n">
         <v>36.4</v>
       </c>
       <c r="J69" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M69" t="n">
         <v>147.02</v>
@@ -4957,13 +4957,13 @@
         <v>82</v>
       </c>
       <c r="F70" t="n">
-        <v>1683.13</v>
+        <v>1697.39</v>
       </c>
       <c r="G70" t="n">
-        <v>44.4</v>
+        <v>44.8</v>
       </c>
       <c r="H70" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I70" t="n">
         <v>60.3</v>
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M70" t="n">
         <v>1683.13</v>
@@ -5026,13 +5026,13 @@
         <v>82</v>
       </c>
       <c r="F71" t="n">
-        <v>99.97</v>
+        <v>99.28</v>
       </c>
       <c r="G71" t="n">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
       <c r="H71" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="I71" t="n">
         <v>74.09999999999999</v>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M71" t="n">
         <v>99.97</v>
@@ -5091,13 +5091,13 @@
         <v>82</v>
       </c>
       <c r="F72" t="n">
-        <v>340.88</v>
+        <v>338.25</v>
       </c>
       <c r="G72" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="H72" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="I72" t="n">
         <v>16.1</v>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="M72" t="n">
         <v>340.88</v>
@@ -5156,19 +5156,19 @@
         <v>82</v>
       </c>
       <c r="F73" t="n">
-        <v>98.06</v>
+        <v>97.06</v>
       </c>
       <c r="G73" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H73" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I73" t="n">
         <v>44.8</v>
       </c>
       <c r="J73" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="M73" t="n">
         <v>98.06</v>
@@ -5221,13 +5221,13 @@
         <v>82</v>
       </c>
       <c r="F74" t="n">
-        <v>157.93</v>
+        <v>156.66</v>
       </c>
       <c r="G74" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="H74" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I74" t="n">
         <v>234.4</v>
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="M74" t="n">
         <v>157.93</v>
@@ -5290,13 +5290,13 @@
         <v>80</v>
       </c>
       <c r="F75" t="n">
-        <v>194.97</v>
+        <v>200.09</v>
       </c>
       <c r="G75" t="n">
-        <v>29.7</v>
+        <v>30.5</v>
       </c>
       <c r="H75" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I75" t="n">
         <v>201.4</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M75" t="n">
         <v>194.97</v>
@@ -5355,19 +5355,19 @@
         <v>80</v>
       </c>
       <c r="F76" t="n">
-        <v>1229.93</v>
+        <v>1199.3</v>
       </c>
       <c r="G76" t="n">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
       <c r="H76" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="I76" t="n">
         <v>51.8</v>
       </c>
       <c r="J76" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>-2.49</v>
       </c>
       <c r="M76" t="n">
         <v>1229.93</v>
@@ -5420,19 +5420,19 @@
         <v>80</v>
       </c>
       <c r="F77" t="n">
-        <v>73.78</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="H77" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="I77" t="n">
         <v>36.7</v>
       </c>
       <c r="J77" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>-3.23</v>
       </c>
       <c r="M77" t="n">
         <v>73.78</v>
@@ -5485,19 +5485,19 @@
         <v>79</v>
       </c>
       <c r="F78" t="n">
-        <v>173.97</v>
+        <v>167.73</v>
       </c>
       <c r="G78" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="H78" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I78" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>-3.59</v>
       </c>
       <c r="M78" t="n">
         <v>173.97</v>
@@ -5548,19 +5548,19 @@
         <v>79</v>
       </c>
       <c r="F79" t="n">
-        <v>135.44</v>
+        <v>136.95</v>
       </c>
       <c r="G79" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="H79" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I79" t="n">
         <v>15.8</v>
       </c>
       <c r="J79" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M79" t="n">
         <v>135.44</v>
@@ -5611,19 +5611,19 @@
         <v>79</v>
       </c>
       <c r="F80" t="n">
-        <v>9.210000000000001</v>
+        <v>9</v>
       </c>
       <c r="G80" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="H80" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="I80" t="n">
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>-2.28</v>
       </c>
       <c r="M80" t="n">
         <v>9.210000000000001</v>
@@ -5674,13 +5674,13 @@
         <v>78</v>
       </c>
       <c r="F81" t="n">
-        <v>91.8</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H81" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I81" t="n">
         <v>33</v>
@@ -5694,7 +5694,7 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="M81" t="n">
         <v>91.8</v>
@@ -5737,10 +5737,10 @@
         <v>78</v>
       </c>
       <c r="F82" t="n">
-        <v>107.37</v>
+        <v>106.25</v>
       </c>
       <c r="G82" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="H82" t="n">
         <v>0.6</v>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="M82" t="n">
         <v>107.37</v>
@@ -5800,13 +5800,13 @@
         <v>71</v>
       </c>
       <c r="F83" t="n">
-        <v>342.46</v>
+        <v>338.4</v>
       </c>
       <c r="G83" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="H83" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I83" t="n">
         <v>-5.4</v>
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>-1.19</v>
       </c>
       <c r="M83" t="n">
         <v>342.46</v>
@@ -5865,13 +5865,13 @@
         <v>71</v>
       </c>
       <c r="F84" t="n">
-        <v>78.58</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H84" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I84" t="n">
         <v>-2.5</v>
@@ -5883,7 +5883,7 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>-1.74</v>
       </c>
       <c r="M84" t="n">
         <v>78.58</v>
@@ -5930,13 +5930,13 @@
         <v>71</v>
       </c>
       <c r="F85" t="n">
-        <v>52.81</v>
+        <v>52.42</v>
       </c>
       <c r="G85" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H85" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="I85" t="n">
         <v>-8.800000000000001</v>
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="M85" t="n">
         <v>52.81</v>
@@ -5999,13 +5999,13 @@
         <v>70</v>
       </c>
       <c r="F86" t="n">
-        <v>147.54</v>
+        <v>145.78</v>
       </c>
       <c r="G86" t="n">
         <v>6.3</v>
       </c>
       <c r="H86" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
@@ -6015,7 +6015,7 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>-1.19</v>
       </c>
       <c r="M86" t="n">
         <v>147.54</v>
@@ -6062,13 +6062,13 @@
         <v>67</v>
       </c>
       <c r="F87" t="n">
-        <v>1145.28</v>
+        <v>1154.29</v>
       </c>
       <c r="G87" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="H87" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I87" t="n">
         <v>-0.7</v>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="M87" t="n">
         <v>1145.28</v>
@@ -6127,13 +6127,13 @@
         <v>67</v>
       </c>
       <c r="F88" t="n">
-        <v>43.39</v>
+        <v>43.76</v>
       </c>
       <c r="G88" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H88" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M88" t="n">
         <v>43.39</v>
@@ -6192,13 +6192,13 @@
         <v>66</v>
       </c>
       <c r="F89" t="n">
-        <v>232.8</v>
+        <v>235.96</v>
       </c>
       <c r="G89" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="H89" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
@@ -6208,7 +6208,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M89" t="n">
         <v>232.8</v>
@@ -6255,19 +6255,19 @@
         <v>64</v>
       </c>
       <c r="F90" t="n">
-        <v>343.25</v>
+        <v>364.8</v>
       </c>
       <c r="G90" t="n">
-        <v>41.2</v>
+        <v>43.7</v>
       </c>
       <c r="H90" t="n">
-        <v>18.8</v>
+        <v>19.9</v>
       </c>
       <c r="I90" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="J90" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6275,7 +6275,7 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="M90" t="n">
         <v>343.25</v>
@@ -6318,13 +6318,13 @@
         <v>62</v>
       </c>
       <c r="F91" t="n">
-        <v>115.7</v>
+        <v>116.67</v>
       </c>
       <c r="G91" t="n">
-        <v>120.5</v>
+        <v>121.5</v>
       </c>
       <c r="H91" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="M91" t="n">
         <v>115.7</v>
@@ -6381,19 +6381,19 @@
         <v>59</v>
       </c>
       <c r="F92" t="n">
-        <v>539.49</v>
+        <v>580.91</v>
       </c>
       <c r="G92" t="n">
-        <v>175.2</v>
+        <v>188.6</v>
       </c>
       <c r="H92" t="n">
-        <v>18</v>
+        <v>19.4</v>
       </c>
       <c r="I92" t="n">
         <v>46.5</v>
       </c>
       <c r="J92" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>7.68</v>
       </c>
       <c r="M92" t="n">
         <v>539.49</v>
@@ -6448,10 +6448,10 @@
         <v>58</v>
       </c>
       <c r="F93" t="n">
-        <v>95.5</v>
+        <v>96</v>
       </c>
       <c r="G93" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H93" t="n">
         <v>1.3</v>
@@ -6468,7 +6468,7 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M93" t="n">
         <v>95.5</v>
@@ -6558,10 +6558,10 @@
         <v>67</v>
       </c>
       <c r="F95" t="n">
-        <v>112.41</v>
+        <v>111.48</v>
       </c>
       <c r="G95" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="M95" t="n">
         <v>112.41</v>
@@ -6621,7 +6621,7 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>368.58</v>
+        <v>368.38</v>
       </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="M96" t="n">
         <v>368.58</v>
@@ -6656,7 +6656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S8"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6759,17 +6759,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RACE</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Fortinet, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -6781,19 +6781,19 @@
         <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>368.34</v>
+        <v>153.62</v>
       </c>
       <c r="G2" t="n">
-        <v>35.9</v>
+        <v>59.1</v>
       </c>
       <c r="H2" t="n">
-        <v>26.8</v>
+        <v>46.5</v>
       </c>
       <c r="I2" t="n">
-        <v>20.7</v>
+        <v>31.2</v>
       </c>
       <c r="J2" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -6801,40 +6801,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="M2" t="n">
-        <v>368.34</v>
+        <v>155.42</v>
       </c>
       <c r="N2" t="n">
-        <v>41.9</v>
+        <v>155.7</v>
       </c>
       <c r="O2" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>13.7</v>
+        <v>19.4</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>650.2</v>
+        <v>1108.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>RACE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Automatic Data Processing, Inc.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -6843,22 +6843,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>224.97</v>
+        <v>372.29</v>
       </c>
       <c r="G3" t="n">
-        <v>20.9</v>
+        <v>36</v>
       </c>
       <c r="H3" t="n">
-        <v>16.9</v>
+        <v>27.1</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5</v>
+        <v>20.7</v>
       </c>
       <c r="J3" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -6866,40 +6866,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="M3" t="n">
-        <v>224.97</v>
+        <v>368.34</v>
       </c>
       <c r="N3" t="n">
-        <v>68.7</v>
+        <v>41.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>2.62</v>
       </c>
       <c r="P3" t="n">
-        <v>8.199999999999999</v>
+        <v>13.7</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>893.6</v>
+        <v>650.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Automatic Data Processing, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" t="n">
-        <v>1883.11</v>
+        <v>223.95</v>
       </c>
       <c r="G4" t="n">
-        <v>64.7</v>
+        <v>20.8</v>
       </c>
       <c r="H4" t="n">
-        <v>27.9</v>
+        <v>16.8</v>
       </c>
       <c r="I4" t="n">
-        <v>21.4</v>
+        <v>12.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6931,40 +6931,40 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="M4" t="n">
-        <v>1883.11</v>
+        <v>224.97</v>
       </c>
       <c r="N4" t="n">
-        <v>52</v>
+        <v>68.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>15.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>6916.8</v>
+        <v>893.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa Inc.</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -6976,19 +6976,19 @@
         <v>86</v>
       </c>
       <c r="F5" t="n">
-        <v>341.65</v>
+        <v>1989.44</v>
       </c>
       <c r="G5" t="n">
-        <v>29.7</v>
+        <v>66.8</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>29.5</v>
       </c>
       <c r="I5" t="n">
-        <v>13.4</v>
+        <v>21.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -6996,40 +6996,40 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="M5" t="n">
-        <v>341.65</v>
+        <v>1883.11</v>
       </c>
       <c r="N5" t="n">
-        <v>58.9</v>
+        <v>52</v>
       </c>
       <c r="O5" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>13.5</v>
+        <v>15.1</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>6444.9</v>
+        <v>6916.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ecolab Inc.</t>
+          <t>Visa Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7038,22 +7038,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F6" t="n">
-        <v>278.6</v>
+        <v>343.09</v>
       </c>
       <c r="G6" t="n">
-        <v>37.4</v>
+        <v>29.9</v>
       </c>
       <c r="H6" t="n">
-        <v>25.8</v>
+        <v>18.1</v>
       </c>
       <c r="I6" t="n">
-        <v>24.2</v>
+        <v>13.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.07</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -7061,68 +7061,64 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>278.6</v>
+        <v>341.65</v>
       </c>
       <c r="N6" t="n">
-        <v>21.7</v>
+        <v>58.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>13.5</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>798.3</v>
+        <v>6444.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSGX</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Descartes Systems Group Inc.</t>
+          <t>Ecolab Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F7" t="n">
-        <v>69.52</v>
+        <v>278.61</v>
       </c>
       <c r="G7" t="n">
-        <v>33.6</v>
+        <v>37.4</v>
       </c>
       <c r="H7" t="n">
-        <v>19.7</v>
+        <v>25.8</v>
       </c>
       <c r="I7" t="n">
-        <v>17.2</v>
+        <v>24.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7133,35 +7129,41 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>69.52</v>
+        <v>278.6</v>
       </c>
       <c r="N7" t="n">
-        <v>11.3</v>
+        <v>21.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>798.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WMT</t>
+          <t>DSGX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Walmart Inc.</t>
+          <t>The Descartes Systems Group Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7170,22 +7172,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>114.6</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>40.2</v>
+        <v>33.5</v>
       </c>
       <c r="H8" t="n">
-        <v>28.3</v>
+        <v>19.6</v>
       </c>
       <c r="I8" t="n">
-        <v>24.2</v>
+        <v>17.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -7193,23 +7195,86 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>114.6</v>
+        <v>69.52</v>
       </c>
       <c r="N8" t="n">
-        <v>24.3</v>
+        <v>11.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="P8" t="n">
-        <v>5.6</v>
+        <v>15.1</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Walmart Inc.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Consumer Defensive</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>71</v>
+      </c>
+      <c r="F9" t="n">
+        <v>113.26</v>
+      </c>
+      <c r="G9" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="M9" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7347,19 +7412,19 @@
         <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>164.1</v>
+        <v>169.88</v>
       </c>
       <c r="G2" t="n">
-        <v>55.4</v>
+        <v>57.4</v>
       </c>
       <c r="H2" t="n">
-        <v>23.2</v>
+        <v>24</v>
       </c>
       <c r="I2" t="n">
         <v>36.4</v>
       </c>
       <c r="J2" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -7367,7 +7432,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="M2" t="n">
         <v>164.1</v>
@@ -7412,10 +7477,10 @@
         <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>455.1</v>
+        <v>477.57</v>
       </c>
       <c r="G3" t="n">
-        <v>32.4</v>
+        <v>33.7</v>
       </c>
       <c r="H3" t="n">
         <v>0.7</v>
@@ -7432,7 +7497,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="M3" t="n">
         <v>455.1</v>
@@ -7477,10 +7542,10 @@
         <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>351.28</v>
+        <v>353.33</v>
       </c>
       <c r="G4" t="n">
-        <v>26.7</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
         <v>14.6</v>
@@ -7497,7 +7562,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="M4" t="n">
         <v>351.28</v>
@@ -7542,19 +7607,19 @@
         <v>90</v>
       </c>
       <c r="F5" t="n">
-        <v>101.76</v>
+        <v>104.67</v>
       </c>
       <c r="G5" t="n">
-        <v>22.3</v>
+        <v>22.9</v>
       </c>
       <c r="H5" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="I5" t="n">
         <v>43.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -7562,7 +7627,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="M5" t="n">
         <v>101.76</v>
@@ -7607,19 +7672,19 @@
         <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>368.57</v>
+        <v>373.02</v>
       </c>
       <c r="G6" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="H6" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="I6" t="n">
         <v>12.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -7627,7 +7692,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M6" t="n">
         <v>368.57</v>
@@ -7672,13 +7737,13 @@
         <v>90</v>
       </c>
       <c r="F7" t="n">
-        <v>110.93</v>
+        <v>112.32</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="H7" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="I7" t="n">
         <v>32.5</v>
@@ -7692,7 +7757,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M7" t="n">
         <v>110.93</v>
@@ -7737,19 +7802,19 @@
         <v>90</v>
       </c>
       <c r="F8" t="n">
-        <v>277.07</v>
+        <v>283.13</v>
       </c>
       <c r="G8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="I8" t="n">
         <v>71.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -7757,7 +7822,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M8" t="n">
         <v>277.07</v>
@@ -7802,7 +7867,7 @@
         <v>90</v>
       </c>
       <c r="F9" t="n">
-        <v>562.6</v>
+        <v>563.29</v>
       </c>
       <c r="G9" t="n">
         <v>20.1</v>
@@ -7822,7 +7887,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M9" t="n">
         <v>562.6</v>
@@ -7867,19 +7932,19 @@
         <v>90</v>
       </c>
       <c r="F10" t="n">
-        <v>128.32</v>
+        <v>137.49</v>
       </c>
       <c r="G10" t="n">
-        <v>22.9</v>
+        <v>24.6</v>
       </c>
       <c r="H10" t="n">
-        <v>12.7</v>
+        <v>13.6</v>
       </c>
       <c r="I10" t="n">
         <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -7887,7 +7952,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.15</v>
       </c>
       <c r="M10" t="n">
         <v>128.32</v>
@@ -7932,13 +7997,13 @@
         <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>170</v>
+        <v>168.535</v>
       </c>
       <c r="G11" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="H11" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="I11" t="n">
         <v>44</v>
@@ -7952,7 +8017,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.86</v>
       </c>
       <c r="M11" t="n">
         <v>170</v>
@@ -7997,19 +8062,19 @@
         <v>90</v>
       </c>
       <c r="F12" t="n">
-        <v>195.24</v>
+        <v>194.42</v>
       </c>
       <c r="G12" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="H12" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="I12" t="n">
         <v>11.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -8017,7 +8082,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-0.42</v>
       </c>
       <c r="M12" t="n">
         <v>195.24</v>
@@ -8062,19 +8127,19 @@
         <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>69.98</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="H13" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="I13" t="n">
         <v>34.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -8082,7 +8147,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-3.76</v>
       </c>
       <c r="M13" t="n">
         <v>69.98</v>
@@ -8127,13 +8192,13 @@
         <v>90</v>
       </c>
       <c r="F14" t="n">
-        <v>198.43</v>
+        <v>194.88</v>
       </c>
       <c r="G14" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="H14" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="I14" t="n">
         <v>21.4</v>
@@ -8147,7 +8212,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
       <c r="M14" t="n">
         <v>198.43</v>
@@ -8192,19 +8257,19 @@
         <v>90</v>
       </c>
       <c r="F15" t="n">
-        <v>127.18</v>
+        <v>125.68</v>
       </c>
       <c r="G15" t="n">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="H15" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I15" t="n">
         <v>18.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -8212,7 +8277,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="M15" t="n">
         <v>127.18</v>
@@ -8257,10 +8322,10 @@
         <v>90</v>
       </c>
       <c r="F16" t="n">
-        <v>206.43</v>
+        <v>205.02</v>
       </c>
       <c r="G16" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="H16" t="n">
         <v>5.9</v>
@@ -8277,7 +8342,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.68</v>
       </c>
       <c r="M16" t="n">
         <v>206.43</v>
@@ -8322,19 +8387,19 @@
         <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>332.02</v>
+        <v>329.81</v>
       </c>
       <c r="G17" t="n">
         <v>14.5</v>
       </c>
       <c r="H17" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="I17" t="n">
         <v>46.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -8342,7 +8407,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.67</v>
       </c>
       <c r="M17" t="n">
         <v>332.02</v>
@@ -8387,7 +8452,7 @@
         <v>87</v>
       </c>
       <c r="F18" t="n">
-        <v>129.16</v>
+        <v>128.14</v>
       </c>
       <c r="G18" t="n">
         <v>16.4</v>
@@ -8407,7 +8472,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0.79</v>
       </c>
       <c r="M18" t="n">
         <v>129.16</v>
@@ -8452,13 +8517,13 @@
         <v>87</v>
       </c>
       <c r="F19" t="n">
-        <v>278</v>
+        <v>281.21</v>
       </c>
       <c r="G19" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="H19" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="I19" t="n">
         <v>84.09999999999999</v>
@@ -8472,7 +8537,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="M19" t="n">
         <v>278</v>
@@ -8521,10 +8586,10 @@
         <v>87</v>
       </c>
       <c r="F20" t="n">
-        <v>64.95</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="H20" t="n">
         <v>9.800000000000001</v>
@@ -8541,7 +8606,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
       <c r="M20" t="n">
         <v>64.95</v>
@@ -8586,13 +8651,13 @@
         <v>87</v>
       </c>
       <c r="F21" t="n">
-        <v>44.38</v>
+        <v>43.18</v>
       </c>
       <c r="G21" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I21" t="n">
         <v>37.5</v>
@@ -8606,7 +8671,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-2.7</v>
       </c>
       <c r="M21" t="n">
         <v>44.38</v>
@@ -8651,19 +8716,19 @@
         <v>86</v>
       </c>
       <c r="F22" t="n">
-        <v>372.45</v>
+        <v>377.75</v>
       </c>
       <c r="G22" t="n">
-        <v>60.2</v>
+        <v>61</v>
       </c>
       <c r="H22" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="I22" t="n">
         <v>21.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -8671,7 +8736,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M22" t="n">
         <v>372.45</v>
@@ -8716,10 +8781,10 @@
         <v>86</v>
       </c>
       <c r="F23" t="n">
-        <v>268.57</v>
+        <v>268.86</v>
       </c>
       <c r="G23" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="H23" t="n">
         <v>30.5</v>
@@ -8736,7 +8801,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="M23" t="n">
         <v>268.57</v>
@@ -8781,19 +8846,19 @@
         <v>86</v>
       </c>
       <c r="F24" t="n">
-        <v>166.42</v>
+        <v>176.32</v>
       </c>
       <c r="G24" t="n">
-        <v>45.5</v>
+        <v>48.2</v>
       </c>
       <c r="H24" t="n">
-        <v>22.1</v>
+        <v>23.4</v>
       </c>
       <c r="I24" t="n">
         <v>29.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -8801,7 +8866,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="M24" t="n">
         <v>166.42</v>
@@ -8846,13 +8911,13 @@
         <v>86</v>
       </c>
       <c r="F25" t="n">
-        <v>101.28</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="H25" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="I25" t="n">
         <v>29.4</v>
@@ -8866,7 +8931,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="M25" t="n">
         <v>101.28</v>
@@ -8911,7 +8976,7 @@
         <v>86</v>
       </c>
       <c r="F26" t="n">
-        <v>54.28</v>
+        <v>54.41</v>
       </c>
       <c r="G26" t="n">
         <v>17.4</v>
@@ -8931,7 +8996,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="M26" t="n">
         <v>54.28</v>
@@ -8976,13 +9041,13 @@
         <v>86</v>
       </c>
       <c r="F27" t="n">
-        <v>509.64</v>
+        <v>513.6</v>
       </c>
       <c r="G27" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="H27" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="I27" t="n">
         <v>17.3</v>
@@ -8996,7 +9061,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="M27" t="n">
         <v>509.64</v>
@@ -9041,19 +9106,19 @@
         <v>86</v>
       </c>
       <c r="F28" t="n">
-        <v>88.66</v>
+        <v>87.77</v>
       </c>
       <c r="G28" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="H28" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="I28" t="n">
         <v>16.3</v>
       </c>
       <c r="J28" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -9061,7 +9126,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M28" t="n">
         <v>88.66</v>
@@ -9106,13 +9171,13 @@
         <v>86</v>
       </c>
       <c r="F29" t="n">
-        <v>105.73</v>
+        <v>104.53</v>
       </c>
       <c r="G29" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="H29" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="I29" t="n">
         <v>35.2</v>
@@ -9126,7 +9191,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="M29" t="n">
         <v>105.73</v>
@@ -9171,13 +9236,13 @@
         <v>86</v>
       </c>
       <c r="F30" t="n">
-        <v>266.4</v>
+        <v>261</v>
       </c>
       <c r="G30" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="H30" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="I30" t="n">
         <v>23.3</v>
@@ -9191,7 +9256,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>-2.03</v>
       </c>
       <c r="M30" t="n">
         <v>266.4</v>
@@ -9236,7 +9301,7 @@
         <v>86</v>
       </c>
       <c r="F31" t="n">
-        <v>48.34</v>
+        <v>47.93</v>
       </c>
       <c r="G31" t="n">
         <v>11.6</v>
@@ -9256,7 +9321,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>-0.85</v>
       </c>
       <c r="M31" t="n">
         <v>48.34</v>
@@ -9301,7 +9366,7 @@
         <v>86</v>
       </c>
       <c r="F32" t="n">
-        <v>76.54000000000001</v>
+        <v>76.28</v>
       </c>
       <c r="G32" t="n">
         <v>7.5</v>
@@ -9321,7 +9386,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="M32" t="n">
         <v>76.54000000000001</v>
@@ -9370,13 +9435,13 @@
         <v>86</v>
       </c>
       <c r="F33" t="n">
-        <v>22.25</v>
+        <v>22.46</v>
       </c>
       <c r="G33" t="n">
-        <v>22.4</v>
+        <v>21.9</v>
       </c>
       <c r="H33" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I33" t="n">
         <v>105.8</v>
@@ -9390,10 +9455,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0.04</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>22.24</v>
+        <v>22.25</v>
       </c>
       <c r="N33" t="n">
         <v>24.2</v>
@@ -9435,10 +9500,10 @@
         <v>83</v>
       </c>
       <c r="F34" t="n">
-        <v>32.19</v>
+        <v>32</v>
       </c>
       <c r="G34" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="H34" t="n">
         <v>10.2</v>
@@ -9455,7 +9520,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="M34" t="n">
         <v>32.19</v>
@@ -9500,19 +9565,19 @@
         <v>83</v>
       </c>
       <c r="F35" t="n">
-        <v>511.06</v>
+        <v>518.9400000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>33.8</v>
+        <v>34.3</v>
       </c>
       <c r="H35" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="I35" t="n">
         <v>20.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -9520,7 +9585,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M35" t="n">
         <v>511.06</v>
@@ -9565,13 +9630,13 @@
         <v>83</v>
       </c>
       <c r="F36" t="n">
-        <v>133.49</v>
+        <v>132.52</v>
       </c>
       <c r="G36" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I36" t="n">
         <v>34.8</v>
@@ -9585,7 +9650,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-0.73</v>
       </c>
       <c r="M36" t="n">
         <v>133.49</v>
@@ -9630,19 +9695,19 @@
         <v>83</v>
       </c>
       <c r="F37" t="n">
-        <v>147.02</v>
+        <v>148.69</v>
       </c>
       <c r="G37" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I37" t="n">
         <v>36.4</v>
       </c>
       <c r="J37" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -9650,7 +9715,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M37" t="n">
         <v>147.02</v>
@@ -9695,13 +9760,13 @@
         <v>82</v>
       </c>
       <c r="F38" t="n">
-        <v>1683.13</v>
+        <v>1697.39</v>
       </c>
       <c r="G38" t="n">
-        <v>44.4</v>
+        <v>44.8</v>
       </c>
       <c r="H38" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I38" t="n">
         <v>60.3</v>
@@ -9715,7 +9780,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M38" t="n">
         <v>1683.13</v>
@@ -9764,13 +9829,13 @@
         <v>82</v>
       </c>
       <c r="F39" t="n">
-        <v>99.97</v>
+        <v>99.28</v>
       </c>
       <c r="G39" t="n">
-        <v>59.2</v>
+        <v>58.7</v>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="I39" t="n">
         <v>74.09999999999999</v>
@@ -9784,7 +9849,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M39" t="n">
         <v>99.97</v>
@@ -9829,13 +9894,13 @@
         <v>82</v>
       </c>
       <c r="F40" t="n">
-        <v>340.88</v>
+        <v>338.25</v>
       </c>
       <c r="G40" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="H40" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="I40" t="n">
         <v>16.1</v>
@@ -9849,7 +9914,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="M40" t="n">
         <v>340.88</v>
@@ -9894,19 +9959,19 @@
         <v>82</v>
       </c>
       <c r="F41" t="n">
-        <v>98.06</v>
+        <v>97.06</v>
       </c>
       <c r="G41" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I41" t="n">
         <v>44.8</v>
       </c>
       <c r="J41" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -9914,7 +9979,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>-1.02</v>
       </c>
       <c r="M41" t="n">
         <v>98.06</v>
@@ -9959,13 +10024,13 @@
         <v>82</v>
       </c>
       <c r="F42" t="n">
-        <v>157.93</v>
+        <v>156.66</v>
       </c>
       <c r="G42" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="H42" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I42" t="n">
         <v>234.4</v>
@@ -9979,7 +10044,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="M42" t="n">
         <v>157.93</v>
@@ -10028,13 +10093,13 @@
         <v>80</v>
       </c>
       <c r="F43" t="n">
-        <v>194.97</v>
+        <v>200.09</v>
       </c>
       <c r="G43" t="n">
-        <v>29.7</v>
+        <v>30.5</v>
       </c>
       <c r="H43" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I43" t="n">
         <v>201.4</v>
@@ -10048,7 +10113,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M43" t="n">
         <v>194.97</v>
@@ -10093,19 +10158,19 @@
         <v>80</v>
       </c>
       <c r="F44" t="n">
-        <v>1229.93</v>
+        <v>1199.3</v>
       </c>
       <c r="G44" t="n">
-        <v>43.6</v>
+        <v>42.5</v>
       </c>
       <c r="H44" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="I44" t="n">
         <v>51.8</v>
       </c>
       <c r="J44" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -10113,7 +10178,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-2.49</v>
       </c>
       <c r="M44" t="n">
         <v>1229.93</v>
@@ -10158,19 +10223,19 @@
         <v>80</v>
       </c>
       <c r="F45" t="n">
-        <v>73.78</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G45" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="H45" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="I45" t="n">
         <v>36.7</v>
       </c>
       <c r="J45" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -10178,7 +10243,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>-3.23</v>
       </c>
       <c r="M45" t="n">
         <v>73.78</v>
@@ -10223,19 +10288,19 @@
         <v>79</v>
       </c>
       <c r="F46" t="n">
-        <v>173.97</v>
+        <v>167.73</v>
       </c>
       <c r="G46" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="H46" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I46" t="n">
         <v>67.59999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -10243,7 +10308,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-3.59</v>
       </c>
       <c r="M46" t="n">
         <v>173.97</v>
@@ -10286,19 +10351,19 @@
         <v>79</v>
       </c>
       <c r="F47" t="n">
-        <v>135.44</v>
+        <v>136.95</v>
       </c>
       <c r="G47" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="H47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I47" t="n">
         <v>15.8</v>
       </c>
       <c r="J47" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -10306,7 +10371,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M47" t="n">
         <v>135.44</v>
@@ -10349,19 +10414,19 @@
         <v>79</v>
       </c>
       <c r="F48" t="n">
-        <v>9.210000000000001</v>
+        <v>9</v>
       </c>
       <c r="G48" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="H48" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="I48" t="n">
         <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -10369,7 +10434,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-2.28</v>
       </c>
       <c r="M48" t="n">
         <v>9.210000000000001</v>
@@ -10412,13 +10477,13 @@
         <v>78</v>
       </c>
       <c r="F49" t="n">
-        <v>91.8</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H49" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I49" t="n">
         <v>33</v>
@@ -10432,7 +10497,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-1.03</v>
       </c>
       <c r="M49" t="n">
         <v>91.8</v>
@@ -10475,10 +10540,10 @@
         <v>78</v>
       </c>
       <c r="F50" t="n">
-        <v>107.37</v>
+        <v>106.25</v>
       </c>
       <c r="G50" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="H50" t="n">
         <v>0.6</v>
@@ -10495,7 +10560,7 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="M50" t="n">
         <v>107.37</v>
@@ -10538,13 +10603,13 @@
         <v>71</v>
       </c>
       <c r="F51" t="n">
-        <v>342.46</v>
+        <v>338.4</v>
       </c>
       <c r="G51" t="n">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="H51" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="I51" t="n">
         <v>-5.4</v>
@@ -10556,7 +10621,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-1.19</v>
       </c>
       <c r="M51" t="n">
         <v>342.46</v>
@@ -10603,13 +10668,13 @@
         <v>71</v>
       </c>
       <c r="F52" t="n">
-        <v>78.58</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H52" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I52" t="n">
         <v>-2.5</v>
@@ -10621,7 +10686,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-1.74</v>
       </c>
       <c r="M52" t="n">
         <v>78.58</v>
@@ -10668,13 +10733,13 @@
         <v>71</v>
       </c>
       <c r="F53" t="n">
-        <v>52.81</v>
+        <v>52.42</v>
       </c>
       <c r="G53" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H53" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="I53" t="n">
         <v>-8.800000000000001</v>
@@ -10686,7 +10751,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>-0.74</v>
       </c>
       <c r="M53" t="n">
         <v>52.81</v>
@@ -10737,13 +10802,13 @@
         <v>70</v>
       </c>
       <c r="F54" t="n">
-        <v>147.54</v>
+        <v>145.78</v>
       </c>
       <c r="G54" t="n">
         <v>6.3</v>
       </c>
       <c r="H54" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
@@ -10753,7 +10818,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-1.19</v>
       </c>
       <c r="M54" t="n">
         <v>147.54</v>
@@ -10800,13 +10865,13 @@
         <v>67</v>
       </c>
       <c r="F55" t="n">
-        <v>1145.28</v>
+        <v>1154.29</v>
       </c>
       <c r="G55" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="H55" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I55" t="n">
         <v>-0.7</v>
@@ -10818,7 +10883,7 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="M55" t="n">
         <v>1145.28</v>
@@ -10865,13 +10930,13 @@
         <v>67</v>
       </c>
       <c r="F56" t="n">
-        <v>43.39</v>
+        <v>43.76</v>
       </c>
       <c r="G56" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H56" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -10883,7 +10948,7 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="M56" t="n">
         <v>43.39</v>
@@ -10930,13 +10995,13 @@
         <v>66</v>
       </c>
       <c r="F57" t="n">
-        <v>232.8</v>
+        <v>235.96</v>
       </c>
       <c r="G57" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="H57" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
@@ -10946,7 +11011,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M57" t="n">
         <v>232.8</v>
@@ -10993,19 +11058,19 @@
         <v>64</v>
       </c>
       <c r="F58" t="n">
-        <v>343.25</v>
+        <v>364.8</v>
       </c>
       <c r="G58" t="n">
-        <v>41.2</v>
+        <v>43.7</v>
       </c>
       <c r="H58" t="n">
-        <v>18.8</v>
+        <v>19.9</v>
       </c>
       <c r="I58" t="n">
         <v>71.40000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -11013,7 +11078,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="M58" t="n">
         <v>343.25</v>
@@ -11056,13 +11121,13 @@
         <v>62</v>
       </c>
       <c r="F59" t="n">
-        <v>115.7</v>
+        <v>116.67</v>
       </c>
       <c r="G59" t="n">
-        <v>120.5</v>
+        <v>121.5</v>
       </c>
       <c r="H59" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
@@ -11072,7 +11137,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="M59" t="n">
         <v>115.7</v>
@@ -11119,19 +11184,19 @@
         <v>59</v>
       </c>
       <c r="F60" t="n">
-        <v>539.49</v>
+        <v>580.91</v>
       </c>
       <c r="G60" t="n">
-        <v>175.2</v>
+        <v>188.6</v>
       </c>
       <c r="H60" t="n">
-        <v>18</v>
+        <v>19.4</v>
       </c>
       <c r="I60" t="n">
         <v>46.5</v>
       </c>
       <c r="J60" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -11139,7 +11204,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>7.68</v>
       </c>
       <c r="M60" t="n">
         <v>539.49</v>
@@ -11186,10 +11251,10 @@
         <v>58</v>
       </c>
       <c r="F61" t="n">
-        <v>95.5</v>
+        <v>96</v>
       </c>
       <c r="G61" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H61" t="n">
         <v>1.3</v>
@@ -11206,7 +11271,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M61" t="n">
         <v>95.5</v>
@@ -11407,10 +11472,10 @@
         <v>67</v>
       </c>
       <c r="F2" t="n">
-        <v>112.41</v>
+        <v>111.48</v>
       </c>
       <c r="G2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
@@ -11423,7 +11488,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0.83</v>
       </c>
       <c r="M2" t="n">
         <v>112.41</v>
@@ -11456,7 +11521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11581,19 +11646,19 @@
         <v>86</v>
       </c>
       <c r="F2" t="n">
-        <v>278.39</v>
+        <v>301.71</v>
       </c>
       <c r="G2" t="n">
-        <v>78.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>36.5</v>
+        <v>39.6</v>
       </c>
       <c r="I2" t="n">
         <v>11.4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -11601,7 +11666,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>278.39</v>
@@ -11650,19 +11715,19 @@
         <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>372.72</v>
+        <v>375.32</v>
       </c>
       <c r="G3" t="n">
-        <v>86.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>33.4</v>
+        <v>33.7</v>
       </c>
       <c r="I3" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>3.59</v>
+        <v>3.62</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -11670,7 +11735,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
         <v>372.72</v>
@@ -11713,19 +11778,19 @@
         <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>410.91</v>
+        <v>433.33</v>
       </c>
       <c r="G4" t="n">
-        <v>77.2</v>
+        <v>81.5</v>
       </c>
       <c r="H4" t="n">
-        <v>31.1</v>
+        <v>32.8</v>
       </c>
       <c r="I4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>3.79</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -11733,7 +11798,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="M4" t="n">
         <v>410.91</v>
@@ -11776,19 +11841,19 @@
         <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>694.64</v>
+        <v>723</v>
       </c>
       <c r="G5" t="n">
-        <v>65</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>30.6</v>
+        <v>31.9</v>
       </c>
       <c r="I5" t="n">
         <v>5.2</v>
       </c>
       <c r="J5" t="n">
-        <v>5.88</v>
+        <v>6.13</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -11796,7 +11861,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="M5" t="n">
         <v>694.64</v>
@@ -11839,19 +11904,19 @@
         <v>75</v>
       </c>
       <c r="F6" t="n">
-        <v>281.74</v>
+        <v>289.36</v>
       </c>
       <c r="G6" t="n">
-        <v>34</v>
+        <v>34.9</v>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>22.6</v>
       </c>
       <c r="I6" t="n">
         <v>6.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.24</v>
+        <v>3.32</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -11859,7 +11924,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
         <v>281.74</v>
@@ -11902,19 +11967,19 @@
         <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>255.79</v>
+        <v>255.54</v>
       </c>
       <c r="G7" t="n">
-        <v>121.2</v>
+        <v>121.1</v>
       </c>
       <c r="H7" t="n">
-        <v>40</v>
+        <v>39.9</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>6.67</v>
+        <v>6.65</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -11922,7 +11987,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="M7" t="n">
         <v>255.79</v>
@@ -11969,19 +12034,19 @@
         <v>56</v>
       </c>
       <c r="F8" t="n">
-        <v>651.88</v>
+        <v>638.72</v>
       </c>
       <c r="G8" t="n">
-        <v>34.9</v>
+        <v>34.2</v>
       </c>
       <c r="H8" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="I8" t="n">
         <v>3.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.76</v>
+        <v>3.68</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -11989,7 +12054,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.02</v>
       </c>
       <c r="M8" t="n">
         <v>651.88</v>
@@ -12036,13 +12101,13 @@
         <v>47</v>
       </c>
       <c r="F9" t="n">
-        <v>478.93</v>
+        <v>490.56</v>
       </c>
       <c r="G9" t="n">
-        <v>155</v>
+        <v>158.8</v>
       </c>
       <c r="H9" t="n">
-        <v>33.5</v>
+        <v>34.3</v>
       </c>
       <c r="I9" t="n">
         <v>-4.9</v>
@@ -12054,7 +12119,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M9" t="n">
         <v>478.93</v>
@@ -12079,12 +12144,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coherent, Inc.</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -12098,16 +12163,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F10" t="n">
-        <v>391.22</v>
+        <v>297.89</v>
       </c>
       <c r="G10" t="n">
-        <v>170.8</v>
+        <v>101.4</v>
       </c>
       <c r="H10" t="n">
-        <v>31.5</v>
+        <v>31.7</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
@@ -12117,19 +12182,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="M10" t="n">
-        <v>391.22</v>
+        <v>277.75</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3</v>
+        <v>16.8</v>
       </c>
       <c r="O10" t="n">
-        <v>12.84</v>
+        <v>0.66</v>
       </c>
       <c r="P10" t="n">
-        <v>16.9</v>
+        <v>16.4</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -12142,17 +12207,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Coherent, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -12161,20 +12226,18 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>411.84</v>
+        <v>394.47</v>
       </c>
       <c r="G11" t="n">
-        <v>342.2</v>
+        <v>172.3</v>
       </c>
       <c r="H11" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-33.5</v>
-      </c>
+        <v>31.8</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -12182,46 +12245,42 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="M11" t="n">
-        <v>411.84</v>
+        <v>391.22</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O11" t="n">
-        <v>3.89</v>
+        <v>12.84</v>
       </c>
       <c r="P11" t="n">
-        <v>15.2</v>
+        <v>16.9</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>⚠️EPS落後營收(EPS3y -34&lt;營收CAGR 15×50%) | ⚠️ROE滑落(5&lt;5年均17×67%)</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sandisk Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -12233,15 +12292,17 @@
         <v>22</v>
       </c>
       <c r="F12" t="n">
-        <v>2050.39</v>
+        <v>420.6</v>
       </c>
       <c r="G12" t="n">
-        <v>67.2</v>
+        <v>349.5</v>
       </c>
       <c r="H12" t="n">
-        <v>151.5</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+        <v>46.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-33.5</v>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
@@ -12249,31 +12310,98 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M12" t="n">
+        <v>411.84</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>⚠️循環(看PBR)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>⚠️EPS落後營收(EPS3y -34&lt;營收CAGR 15×50%) | ⚠️ROE滑落(5&lt;5年均17×67%)</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SNDK</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sandisk Corporation</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>22</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2273.73</v>
+      </c>
+      <c r="G13" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>168</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>🔴未來過熱</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="M13" t="n">
         <v>2050.39</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N13" t="n">
         <v>42.3</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P13" t="n">
         <v>-9</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>⚠️循環(看PBR)</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>⚠️現金流為負(含金量-0.05)</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12389,41 +12517,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COST</t>
+          <t>NVMI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Costco Wholesale Corporation</t>
+          <t>Nova Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>946.6799999999999</v>
+        <v>542.9400000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>47.5</v>
+        <v>62</v>
       </c>
       <c r="H2" t="n">
-        <v>33.2</v>
+        <v>41.8</v>
       </c>
       <c r="I2" t="n">
-        <v>11.5</v>
+        <v>20.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.89</v>
+        <v>2.01</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -12431,38 +12559,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M2" t="n">
-        <v>946.6799999999999</v>
+        <v>520.39</v>
       </c>
       <c r="N2" t="n">
-        <v>28.3</v>
+        <v>21.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.65</v>
+        <v>0.95</v>
       </c>
       <c r="P2" t="n">
-        <v>8.9</v>
+        <v>20.6</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>155.3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>COST</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Infosys Limited</t>
+          <t>Costco Wholesale Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Consumer Defensive</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -12474,19 +12604,19 @@
         <v>71</v>
       </c>
       <c r="F3" t="n">
-        <v>10.7</v>
+        <v>935.47</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="H3" t="n">
-        <v>10.8</v>
+        <v>32.8</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="J3" t="n">
-        <v>2.04</v>
+        <v>2.85</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -12494,19 +12624,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>10.7</v>
+        <v>946.6799999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>31.8</v>
+        <v>28.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="P3" t="n">
-        <v>5.4</v>
+        <v>8.9</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -12515,102 +12645,100 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Infosys Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>306.97</v>
+        <v>10.49</v>
       </c>
       <c r="G4" t="n">
-        <v>75.2</v>
+        <v>12.6</v>
       </c>
       <c r="H4" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+        <v>10.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>🟠未來偏貴</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-1.96</v>
       </c>
       <c r="M4" t="n">
-        <v>306.97</v>
+        <v>10.7</v>
       </c>
       <c r="N4" t="n">
-        <v>42.1</v>
+        <v>31.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.59</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>⚠️循環(看PBR)</t>
-        </is>
-      </c>
+        <v>5.4</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Vertiv Holdings Co</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F5" t="n">
-        <v>851.4</v>
+        <v>334.82</v>
       </c>
       <c r="G5" t="n">
-        <v>137.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-48.5</v>
-      </c>
+        <v>21.1</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
@@ -12618,19 +12746,19 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>9.07</v>
       </c>
       <c r="M5" t="n">
-        <v>851.4</v>
+        <v>306.97</v>
       </c>
       <c r="N5" t="n">
-        <v>30.7</v>
+        <v>42.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4.88</v>
+        <v>1.59</v>
       </c>
       <c r="P5" t="n">
-        <v>-1</v>
+        <v>19.6</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -12643,12 +12771,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -12665,15 +12793,17 @@
         <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>277.75</v>
+        <v>858.0599999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>94.5</v>
+        <v>138.2</v>
       </c>
       <c r="H6" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>19.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-48.5</v>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
@@ -12681,19 +12811,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="M6" t="n">
-        <v>277.75</v>
+        <v>851.4</v>
       </c>
       <c r="N6" t="n">
-        <v>16.8</v>
+        <v>30.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0.66</v>
+        <v>4.88</v>
       </c>
       <c r="P6" t="n">
-        <v>16.4</v>
+        <v>-1</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -12728,13 +12858,13 @@
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>495.95</v>
+        <v>499.99</v>
       </c>
       <c r="G7" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H7" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
@@ -12744,7 +12874,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>495.95</v>

--- a/data/美股PE監看表.xlsx
+++ b/data/美股PE監看表.xlsx
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>377.73</v>
+        <v>373.14</v>
       </c>
       <c r="N2" t="n">
         <v>21.1</v>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-10.19</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>391.26</v>
+        <v>351.41</v>
       </c>
       <c r="N3" t="n">
         <v>65.8</v>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-7.35</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>650.91</v>
+        <v>603.04</v>
       </c>
       <c r="N4" t="n">
         <v>39.8</v>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>294.38</v>
+        <v>308.63</v>
       </c>
       <c r="N5" t="n">
         <v>146.7</v>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-10.87</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>220.695</v>
+        <v>196.695</v>
       </c>
       <c r="N6" t="n">
         <v>15.6</v>
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-9.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>598.37</v>
+        <v>539</v>
       </c>
       <c r="N7" t="n">
         <v>91.90000000000001</v>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-7.49</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>425.3</v>
+        <v>393.45</v>
       </c>
       <c r="N8" t="n">
         <v>4.8</v>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-14.13</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2032.22</v>
+        <v>1745</v>
       </c>
       <c r="N9" t="n">
         <v>42.3</v>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>-11.51</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>266.19</v>
+        <v>235.55</v>
       </c>
       <c r="N10" t="n">
         <v>89.09999999999999</v>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>106.1</v>
+        <v>106.61</v>
       </c>
       <c r="N11" t="n">
         <v>24.5</v>
@@ -1217,10 +1217,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>924.67</v>
+        <v>951.67</v>
       </c>
       <c r="N12" t="n">
         <v>28.3</v>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>10.65</v>
+        <v>11.16</v>
       </c>
       <c r="N13" t="n">
         <v>31.8</v>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>311.42</v>
+        <v>300.53</v>
       </c>
       <c r="N14" t="n">
         <v>42.1</v>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>-8.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>462.44</v>
+        <v>422.46</v>
       </c>
       <c r="N15" t="n">
         <v>15.7</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>-9.84</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>272.05</v>
+        <v>245.29</v>
       </c>
       <c r="N16" t="n">
         <v>16.8</v>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>-9.57</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>368.65</v>
+        <v>333.36</v>
       </c>
       <c r="N17" t="n">
         <v>5.3</v>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>499.99</v>
+        <v>507.78</v>
       </c>
       <c r="N18" t="n">
         <v>10.3</v>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>-1.72</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>158.98</v>
+        <v>156.25</v>
       </c>
       <c r="N19" t="n">
         <v>155.7</v>
@@ -1708,7 +1708,7 @@
         <v>31.93</v>
       </c>
       <c r="G20" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="H20" t="n">
         <v>17.7</v>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>31.38</v>
+        <v>31.93</v>
       </c>
       <c r="N20" t="n">
         <v>90.8</v>
@@ -1773,7 +1773,7 @@
         <v>470.14</v>
       </c>
       <c r="G21" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="H21" t="n">
         <v>36.2</v>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>-6.46</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>502.6</v>
+        <v>470.14</v>
       </c>
       <c r="N21" t="n">
         <v>21.2</v>
@@ -1855,10 +1855,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.81</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>991.41</v>
+        <v>963.53</v>
       </c>
       <c r="N22" t="n">
         <v>47.5</v>
@@ -1901,7 +1901,7 @@
         <v>53.66</v>
       </c>
       <c r="G23" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="H23" t="n">
         <v>12.1</v>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>51.3</v>
+        <v>53.66</v>
       </c>
       <c r="N23" t="n">
         <v>35.8</v>
@@ -1985,10 +1985,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>108.16</v>
+        <v>110.54</v>
       </c>
       <c r="N24" t="n">
         <v>35.2</v>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>131.13</v>
+        <v>137.35</v>
       </c>
       <c r="N25" t="n">
         <v>25</v>
@@ -2111,10 +2111,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>241.7</v>
+        <v>242.67</v>
       </c>
       <c r="N26" t="n">
         <v>23.3</v>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>-9.09</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>801.16</v>
+        <v>728.3200000000001</v>
       </c>
       <c r="N27" t="n">
         <v>30.7</v>
@@ -2226,16 +2226,16 @@
         <v>384.97</v>
       </c>
       <c r="G28" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="H28" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="I28" t="n">
         <v>20.7</v>
       </c>
       <c r="J28" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2243,10 +2243,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>374.66</v>
+        <v>384.97</v>
       </c>
       <c r="N28" t="n">
         <v>41.9</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>235.73</v>
+        <v>242.27</v>
       </c>
       <c r="N29" t="n">
         <v>68.7</v>
@@ -2356,16 +2356,16 @@
         <v>1769.32</v>
       </c>
       <c r="G30" t="n">
-        <v>62.9</v>
+        <v>63.1</v>
       </c>
       <c r="H30" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="I30" t="n">
         <v>21.4</v>
       </c>
       <c r="J30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1843.04</v>
+        <v>1769.32</v>
       </c>
       <c r="N30" t="n">
         <v>52</v>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>351.08</v>
+        <v>362.13</v>
       </c>
       <c r="N31" t="n">
         <v>58.9</v>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>533.55</v>
+        <v>546.64</v>
       </c>
       <c r="N32" t="n">
         <v>18.5</v>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>278.37</v>
+        <v>283.36</v>
       </c>
       <c r="N33" t="n">
         <v>21.7</v>
@@ -2620,10 +2620,10 @@
         <v>72.795</v>
       </c>
       <c r="G34" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="H34" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="I34" t="n">
         <v>17.2</v>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>70.94</v>
+        <v>72.795</v>
       </c>
       <c r="N34" t="n">
         <v>11.3</v>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>108.82</v>
+        <v>111.84</v>
       </c>
       <c r="N35" t="n">
         <v>24.3</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>-3.98</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>166.62</v>
+        <v>159.99</v>
       </c>
       <c r="N36" t="n">
         <v>30.6</v>
@@ -2828,10 +2828,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>444.23</v>
+        <v>434.16</v>
       </c>
       <c r="N37" t="n">
         <v>36.9</v>
@@ -2893,10 +2893,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>357.89</v>
+        <v>356.18</v>
       </c>
       <c r="N38" t="n">
         <v>39</v>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>106.03</v>
+        <v>107.5</v>
       </c>
       <c r="N39" t="n">
         <v>21.3</v>
@@ -3023,10 +3023,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>384.28</v>
+        <v>390.49</v>
       </c>
       <c r="N40" t="n">
         <v>33.1</v>
@@ -3074,13 +3074,13 @@
         <v>29.2</v>
       </c>
       <c r="H41" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="I41" t="n">
         <v>32.5</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>111.44</v>
+        <v>115.73</v>
       </c>
       <c r="N41" t="n">
         <v>21.3</v>
@@ -3153,10 +3153,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>282.26</v>
+        <v>281.4</v>
       </c>
       <c r="N42" t="n">
         <v>33.4</v>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>-4.9</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>612.91</v>
+        <v>582.9</v>
       </c>
       <c r="N43" t="n">
         <v>33.2</v>
@@ -3283,10 +3283,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>143.44</v>
+        <v>148.12</v>
       </c>
       <c r="N44" t="n">
         <v>37.2</v>
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>167.77</v>
+        <v>174.26</v>
       </c>
       <c r="N45" t="n">
         <v>21.6</v>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>199.76</v>
+        <v>207.48</v>
       </c>
       <c r="N46" t="n">
         <v>49.4</v>
@@ -3478,10 +3478,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>68.86</v>
+        <v>71.25</v>
       </c>
       <c r="N47" t="n">
         <v>33.8</v>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>201.1</v>
+        <v>209.63</v>
       </c>
       <c r="N48" t="n">
         <v>24.4</v>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>133.96</v>
+        <v>139.21</v>
       </c>
       <c r="N49" t="n">
         <v>31</v>
@@ -3673,10 +3673,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>210.98</v>
+        <v>219.72</v>
       </c>
       <c r="N50" t="n">
         <v>62.4</v>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>345.27</v>
+        <v>354.85</v>
       </c>
       <c r="N51" t="n">
         <v>28</v>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>129.7</v>
+        <v>127.24</v>
       </c>
       <c r="N52" t="n">
         <v>21.6</v>
@@ -3868,10 +3868,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>286.25</v>
+        <v>289.52</v>
       </c>
       <c r="N53" t="n">
         <v>35.5</v>
@@ -3937,10 +3937,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>65.09</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="N54" t="n">
         <v>155.3</v>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>44.07</v>
+        <v>45.47</v>
       </c>
       <c r="N55" t="n">
         <v>25.1</v>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-2.41</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>369.34</v>
+        <v>360.45</v>
       </c>
       <c r="N56" t="n">
         <v>36.4</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>267.41</v>
+        <v>270.41</v>
       </c>
       <c r="N57" t="n">
         <v>33.1</v>
@@ -4197,10 +4197,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-4.43</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>172.22</v>
+        <v>164.59</v>
       </c>
       <c r="N58" t="n">
         <v>34.8</v>
@@ -4262,10 +4262,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>100.33</v>
+        <v>104.69</v>
       </c>
       <c r="N59" t="n">
         <v>40.8</v>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>53.96</v>
+        <v>55.85</v>
       </c>
       <c r="N60" t="n">
         <v>40.2</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>522.4400000000001</v>
+        <v>539.39</v>
       </c>
       <c r="N61" t="n">
         <v>206.1</v>
@@ -4457,10 +4457,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>86.37</v>
+        <v>88.34</v>
       </c>
       <c r="N62" t="n">
         <v>15.2</v>
@@ -4522,10 +4522,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>111.33</v>
+        <v>115.1</v>
       </c>
       <c r="N63" t="n">
         <v>22.4</v>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>267.08</v>
+        <v>275.35</v>
       </c>
       <c r="N64" t="n">
         <v>23.3</v>
@@ -4652,10 +4652,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>48.77</v>
+        <v>50.43</v>
       </c>
       <c r="N65" t="n">
         <v>66.40000000000001</v>
@@ -4700,7 +4700,7 @@
         <v>82.39</v>
       </c>
       <c r="G66" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H66" t="n">
         <v>0.9</v>
@@ -4717,10 +4717,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>82.52</v>
+        <v>82.39</v>
       </c>
       <c r="N66" t="n">
         <v>24</v>
@@ -4769,7 +4769,7 @@
         <v>21.58</v>
       </c>
       <c r="G67" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="H67" t="n">
         <v>3.7</v>
@@ -4786,10 +4786,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-4.72</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>22.65</v>
+        <v>21.58</v>
       </c>
       <c r="N67" t="n">
         <v>24.2</v>
@@ -4851,10 +4851,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>33.25</v>
+        <v>34.43</v>
       </c>
       <c r="N68" t="n">
         <v>17.2</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>133.89</v>
+        <v>137.85</v>
       </c>
       <c r="N69" t="n">
         <v>22</v>
@@ -4981,10 +4981,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>150.58</v>
+        <v>158.33</v>
       </c>
       <c r="N70" t="n">
         <v>20.9</v>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>1742.19</v>
+        <v>1763.36</v>
       </c>
       <c r="N71" t="n">
         <v>29.6</v>
@@ -5115,10 +5115,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>105.8</v>
+        <v>106.32</v>
       </c>
       <c r="N72" t="n">
         <v>15</v>
@@ -5180,10 +5180,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>348</v>
+        <v>351.96</v>
       </c>
       <c r="N73" t="n">
         <v>33.9</v>
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>98.55</v>
+        <v>102.2</v>
       </c>
       <c r="N74" t="n">
         <v>20.5</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>163.23</v>
+        <v>166.11</v>
       </c>
       <c r="N75" t="n">
         <v>14.9</v>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-1.39</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>197.58</v>
+        <v>194.83</v>
       </c>
       <c r="N76" t="n">
         <v>111.7</v>
@@ -5444,10 +5444,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>1191.71</v>
+        <v>1210.5</v>
       </c>
       <c r="N77" t="n">
         <v>101.3</v>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>74.19</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="N78" t="n">
         <v>49.2</v>
@@ -5574,10 +5574,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>173.06</v>
+        <v>177.52</v>
       </c>
       <c r="N79" t="n">
         <v>17.8</v>
@@ -5637,10 +5637,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>140.93</v>
+        <v>143.95</v>
       </c>
       <c r="N80" t="n">
         <v>40.1</v>
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>9.56</v>
+        <v>9.77</v>
       </c>
       <c r="N81" t="n">
         <v>14.6</v>
@@ -5763,10 +5763,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>94.83</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="N82" t="n">
         <v>14</v>
@@ -5809,7 +5809,7 @@
         <v>107.38</v>
       </c>
       <c r="G83" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="H83" t="n">
         <v>0.6</v>
@@ -5826,10 +5826,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>105.8</v>
+        <v>107.38</v>
       </c>
       <c r="N83" t="n">
         <v>16.4</v>
@@ -5887,10 +5887,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>336.91</v>
+        <v>344.6</v>
       </c>
       <c r="N84" t="n">
         <v>23.4</v>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>77.5</v>
+        <v>79.34</v>
       </c>
       <c r="N85" t="n">
         <v>20.4</v>
@@ -6015,10 +6015,10 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>141.92</v>
+        <v>147.84</v>
       </c>
       <c r="N86" t="n">
         <v>21.6</v>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-5.49</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>1032.28</v>
+        <v>975.5599999999999</v>
       </c>
       <c r="N87" t="n">
         <v>40.8</v>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>43.13</v>
+        <v>43.67</v>
       </c>
       <c r="N88" t="n">
         <v>35</v>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-3.24</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>232.08</v>
+        <v>224.57</v>
       </c>
       <c r="N89" t="n">
         <v>18</v>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>-7.03</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>361.62</v>
+        <v>336.21</v>
       </c>
       <c r="N90" t="n">
         <v>47.7</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>125.73</v>
+        <v>129.3</v>
       </c>
       <c r="N91" t="n">
         <v>32.2</v>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-4.26</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>540.88</v>
+        <v>517.8200000000001</v>
       </c>
       <c r="N92" t="n">
         <v>8.1</v>
@@ -6451,7 +6451,7 @@
         <v>96.14</v>
       </c>
       <c r="G93" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="H93" t="n">
         <v>1.3</v>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>98.005</v>
+        <v>96.14</v>
       </c>
       <c r="N93" t="n">
         <v>10</v>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>111.65</v>
+        <v>114</v>
       </c>
       <c r="N95" t="n">
         <v>40.1</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>370.6</v>
+        <v>378.13</v>
       </c>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
@@ -6784,16 +6784,16 @@
         <v>384.97</v>
       </c>
       <c r="G2" t="n">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="H2" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="I2" t="n">
         <v>20.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -6801,10 +6801,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>374.66</v>
+        <v>384.97</v>
       </c>
       <c r="N2" t="n">
         <v>41.9</v>
@@ -6866,10 +6866,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>235.73</v>
+        <v>242.27</v>
       </c>
       <c r="N3" t="n">
         <v>68.7</v>
@@ -6914,16 +6914,16 @@
         <v>1769.32</v>
       </c>
       <c r="G4" t="n">
-        <v>62.9</v>
+        <v>63.1</v>
       </c>
       <c r="H4" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="I4" t="n">
         <v>21.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1843.04</v>
+        <v>1769.32</v>
       </c>
       <c r="N4" t="n">
         <v>52</v>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>351.08</v>
+        <v>362.13</v>
       </c>
       <c r="N5" t="n">
         <v>58.9</v>
@@ -7061,10 +7061,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>533.55</v>
+        <v>546.64</v>
       </c>
       <c r="N6" t="n">
         <v>18.5</v>
@@ -7126,10 +7126,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>278.37</v>
+        <v>283.36</v>
       </c>
       <c r="N7" t="n">
         <v>21.7</v>
@@ -7178,10 +7178,10 @@
         <v>72.795</v>
       </c>
       <c r="G8" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="H8" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="I8" t="n">
         <v>17.2</v>
@@ -7195,10 +7195,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>70.94</v>
+        <v>72.795</v>
       </c>
       <c r="N8" t="n">
         <v>11.3</v>
@@ -7258,10 +7258,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>108.82</v>
+        <v>111.84</v>
       </c>
       <c r="N9" t="n">
         <v>24.3</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-3.98</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>166.62</v>
+        <v>159.99</v>
       </c>
       <c r="N2" t="n">
         <v>30.6</v>
@@ -7497,10 +7497,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>444.23</v>
+        <v>434.16</v>
       </c>
       <c r="N3" t="n">
         <v>36.9</v>
@@ -7562,10 +7562,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-0.48</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>357.89</v>
+        <v>356.18</v>
       </c>
       <c r="N4" t="n">
         <v>39</v>
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>106.03</v>
+        <v>107.5</v>
       </c>
       <c r="N5" t="n">
         <v>21.3</v>
@@ -7692,10 +7692,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>384.28</v>
+        <v>390.49</v>
       </c>
       <c r="N6" t="n">
         <v>33.1</v>
@@ -7743,13 +7743,13 @@
         <v>29.2</v>
       </c>
       <c r="H7" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="I7" t="n">
         <v>32.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -7757,10 +7757,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>111.44</v>
+        <v>115.73</v>
       </c>
       <c r="N7" t="n">
         <v>21.3</v>
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>282.26</v>
+        <v>281.4</v>
       </c>
       <c r="N8" t="n">
         <v>33.4</v>
@@ -7887,10 +7887,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-4.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>612.91</v>
+        <v>582.9</v>
       </c>
       <c r="N9" t="n">
         <v>33.2</v>
@@ -7952,10 +7952,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>143.44</v>
+        <v>148.12</v>
       </c>
       <c r="N10" t="n">
         <v>37.2</v>
@@ -8017,10 +8017,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>167.77</v>
+        <v>174.26</v>
       </c>
       <c r="N11" t="n">
         <v>21.6</v>
@@ -8082,10 +8082,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>199.76</v>
+        <v>207.48</v>
       </c>
       <c r="N12" t="n">
         <v>49.4</v>
@@ -8147,10 +8147,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>68.86</v>
+        <v>71.25</v>
       </c>
       <c r="N13" t="n">
         <v>33.8</v>
@@ -8212,10 +8212,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>201.1</v>
+        <v>209.63</v>
       </c>
       <c r="N14" t="n">
         <v>24.4</v>
@@ -8277,10 +8277,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>133.96</v>
+        <v>139.21</v>
       </c>
       <c r="N15" t="n">
         <v>31</v>
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>210.98</v>
+        <v>219.72</v>
       </c>
       <c r="N16" t="n">
         <v>62.4</v>
@@ -8407,10 +8407,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>345.27</v>
+        <v>354.85</v>
       </c>
       <c r="N17" t="n">
         <v>28</v>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>129.7</v>
+        <v>127.24</v>
       </c>
       <c r="N18" t="n">
         <v>21.6</v>
@@ -8537,10 +8537,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>286.25</v>
+        <v>289.52</v>
       </c>
       <c r="N19" t="n">
         <v>35.5</v>
@@ -8606,10 +8606,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>65.09</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>155.3</v>
@@ -8671,10 +8671,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>44.07</v>
+        <v>45.47</v>
       </c>
       <c r="N21" t="n">
         <v>25.1</v>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>-2.41</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>369.34</v>
+        <v>360.45</v>
       </c>
       <c r="N22" t="n">
         <v>36.4</v>
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>267.41</v>
+        <v>270.41</v>
       </c>
       <c r="N23" t="n">
         <v>33.1</v>
@@ -8866,10 +8866,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>-4.43</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>172.22</v>
+        <v>164.59</v>
       </c>
       <c r="N24" t="n">
         <v>34.8</v>
@@ -8931,10 +8931,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>100.33</v>
+        <v>104.69</v>
       </c>
       <c r="N25" t="n">
         <v>40.8</v>
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>53.96</v>
+        <v>55.85</v>
       </c>
       <c r="N26" t="n">
         <v>40.2</v>
@@ -9061,10 +9061,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>522.4400000000001</v>
+        <v>539.39</v>
       </c>
       <c r="N27" t="n">
         <v>206.1</v>
@@ -9126,10 +9126,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>86.37</v>
+        <v>88.34</v>
       </c>
       <c r="N28" t="n">
         <v>15.2</v>
@@ -9191,10 +9191,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>111.33</v>
+        <v>115.1</v>
       </c>
       <c r="N29" t="n">
         <v>22.4</v>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>267.08</v>
+        <v>275.35</v>
       </c>
       <c r="N30" t="n">
         <v>23.3</v>
@@ -9321,10 +9321,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>48.77</v>
+        <v>50.43</v>
       </c>
       <c r="N31" t="n">
         <v>66.40000000000001</v>
@@ -9369,7 +9369,7 @@
         <v>82.39</v>
       </c>
       <c r="G32" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
         <v>0.9</v>
@@ -9386,10 +9386,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>-0.16</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>82.52</v>
+        <v>82.39</v>
       </c>
       <c r="N32" t="n">
         <v>24</v>
@@ -9438,7 +9438,7 @@
         <v>21.58</v>
       </c>
       <c r="G33" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="H33" t="n">
         <v>3.7</v>
@@ -9455,10 +9455,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>-4.72</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>22.65</v>
+        <v>21.58</v>
       </c>
       <c r="N33" t="n">
         <v>24.2</v>
@@ -9520,10 +9520,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>33.25</v>
+        <v>34.43</v>
       </c>
       <c r="N34" t="n">
         <v>17.2</v>
@@ -9585,10 +9585,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>133.89</v>
+        <v>137.85</v>
       </c>
       <c r="N35" t="n">
         <v>22</v>
@@ -9650,10 +9650,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>150.58</v>
+        <v>158.33</v>
       </c>
       <c r="N36" t="n">
         <v>20.9</v>
@@ -9715,10 +9715,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1742.19</v>
+        <v>1763.36</v>
       </c>
       <c r="N37" t="n">
         <v>29.6</v>
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>105.8</v>
+        <v>106.32</v>
       </c>
       <c r="N38" t="n">
         <v>15</v>
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>348</v>
+        <v>351.96</v>
       </c>
       <c r="N39" t="n">
         <v>33.9</v>
@@ -9914,10 +9914,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>98.55</v>
+        <v>102.2</v>
       </c>
       <c r="N40" t="n">
         <v>20.5</v>
@@ -9979,10 +9979,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>163.23</v>
+        <v>166.11</v>
       </c>
       <c r="N41" t="n">
         <v>14.9</v>
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>-1.39</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>197.58</v>
+        <v>194.83</v>
       </c>
       <c r="N42" t="n">
         <v>111.7</v>
@@ -10113,10 +10113,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1191.71</v>
+        <v>1210.5</v>
       </c>
       <c r="N43" t="n">
         <v>101.3</v>
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.66</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>74.19</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="N44" t="n">
         <v>49.2</v>
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>173.06</v>
+        <v>177.52</v>
       </c>
       <c r="N45" t="n">
         <v>17.8</v>
@@ -10306,10 +10306,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>140.93</v>
+        <v>143.95</v>
       </c>
       <c r="N46" t="n">
         <v>40.1</v>
@@ -10369,10 +10369,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>9.56</v>
+        <v>9.77</v>
       </c>
       <c r="N47" t="n">
         <v>14.6</v>
@@ -10432,10 +10432,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>94.83</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="N48" t="n">
         <v>14</v>
@@ -10478,7 +10478,7 @@
         <v>107.38</v>
       </c>
       <c r="G49" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="H49" t="n">
         <v>0.6</v>
@@ -10495,10 +10495,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>105.8</v>
+        <v>107.38</v>
       </c>
       <c r="N49" t="n">
         <v>16.4</v>
@@ -10556,10 +10556,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>336.91</v>
+        <v>344.6</v>
       </c>
       <c r="N50" t="n">
         <v>23.4</v>
@@ -10621,10 +10621,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>77.5</v>
+        <v>79.34</v>
       </c>
       <c r="N51" t="n">
         <v>20.4</v>
@@ -10684,10 +10684,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>141.92</v>
+        <v>147.84</v>
       </c>
       <c r="N52" t="n">
         <v>21.6</v>
@@ -10749,10 +10749,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>-5.49</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>1032.28</v>
+        <v>975.5599999999999</v>
       </c>
       <c r="N53" t="n">
         <v>40.8</v>
@@ -10814,10 +10814,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>43.13</v>
+        <v>43.67</v>
       </c>
       <c r="N54" t="n">
         <v>35</v>
@@ -10877,10 +10877,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>-3.24</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>232.08</v>
+        <v>224.57</v>
       </c>
       <c r="N55" t="n">
         <v>18</v>
@@ -10944,10 +10944,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>-7.03</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>361.62</v>
+        <v>336.21</v>
       </c>
       <c r="N56" t="n">
         <v>47.7</v>
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>125.73</v>
+        <v>129.3</v>
       </c>
       <c r="N57" t="n">
         <v>32.2</v>
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>-4.26</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>540.88</v>
+        <v>517.8200000000001</v>
       </c>
       <c r="N58" t="n">
         <v>8.1</v>
@@ -11120,7 +11120,7 @@
         <v>96.14</v>
       </c>
       <c r="G59" t="n">
-        <v>14.3</v>
+        <v>15.5</v>
       </c>
       <c r="H59" t="n">
         <v>1.3</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>98.005</v>
+        <v>96.14</v>
       </c>
       <c r="N59" t="n">
         <v>10</v>
@@ -11354,10 +11354,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>111.65</v>
+        <v>114</v>
       </c>
       <c r="N2" t="n">
         <v>40.1</v>
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-1.22</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>377.73</v>
+        <v>373.14</v>
       </c>
       <c r="N2" t="n">
         <v>21.1</v>
@@ -11595,10 +11595,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>-10.19</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>391.26</v>
+        <v>351.41</v>
       </c>
       <c r="N3" t="n">
         <v>65.8</v>
@@ -11658,10 +11658,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>-7.35</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>650.91</v>
+        <v>603.04</v>
       </c>
       <c r="N4" t="n">
         <v>39.8</v>
@@ -11721,10 +11721,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>294.38</v>
+        <v>308.63</v>
       </c>
       <c r="N5" t="n">
         <v>146.7</v>
@@ -11784,10 +11784,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-10.87</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>220.695</v>
+        <v>196.695</v>
       </c>
       <c r="N6" t="n">
         <v>15.6</v>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-9.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>598.37</v>
+        <v>539</v>
       </c>
       <c r="N7" t="n">
         <v>91.90000000000001</v>
@@ -11916,10 +11916,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-7.49</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>425.3</v>
+        <v>393.45</v>
       </c>
       <c r="N8" t="n">
         <v>4.8</v>
@@ -11983,10 +11983,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-14.13</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2032.22</v>
+        <v>1745</v>
       </c>
       <c r="N9" t="n">
         <v>42.3</v>
@@ -12165,10 +12165,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>-11.51</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>266.19</v>
+        <v>235.55</v>
       </c>
       <c r="N2" t="n">
         <v>89.09999999999999</v>
@@ -12234,10 +12234,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>106.1</v>
+        <v>106.61</v>
       </c>
       <c r="N3" t="n">
         <v>24.5</v>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>924.67</v>
+        <v>951.67</v>
       </c>
       <c r="N4" t="n">
         <v>28.3</v>
@@ -12360,10 +12360,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>10.65</v>
+        <v>11.16</v>
       </c>
       <c r="N5" t="n">
         <v>31.8</v>
@@ -12419,10 +12419,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>-3.5</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>311.42</v>
+        <v>300.53</v>
       </c>
       <c r="N6" t="n">
         <v>42.1</v>
@@ -12484,10 +12484,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>-8.65</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>462.44</v>
+        <v>422.46</v>
       </c>
       <c r="N7" t="n">
         <v>15.7</v>
@@ -12547,10 +12547,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>-9.84</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>272.05</v>
+        <v>245.29</v>
       </c>
       <c r="N8" t="n">
         <v>16.8</v>
@@ -12610,10 +12610,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>-9.57</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>368.65</v>
+        <v>333.36</v>
       </c>
       <c r="N9" t="n">
         <v>5.3</v>
@@ -12673,10 +12673,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>499.99</v>
+        <v>507.78</v>
       </c>
       <c r="N10" t="n">
         <v>10.3</v>

--- a/data/美股PE監看表.xlsx
+++ b/data/美股PE監看表.xlsx
@@ -550,9 +550,7 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>159.99</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>30.6</v>
       </c>
@@ -605,9 +603,7 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>156.25</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>155.7</v>
       </c>
@@ -660,9 +656,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>434.16</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>36.9</v>
       </c>
@@ -715,9 +709,7 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>356.18</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>39</v>
       </c>
@@ -770,9 +762,7 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>107.5</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>21.3</v>
       </c>
@@ -825,9 +815,7 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>384.97</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>41.9</v>
       </c>
@@ -880,9 +868,7 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>390.49</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
         <v>33.1</v>
       </c>
@@ -935,9 +921,7 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>115.73</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>21.3</v>
       </c>
@@ -990,9 +974,7 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>281.4</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>33.4</v>
       </c>
@@ -1045,9 +1027,7 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>582.9</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>33.2</v>
       </c>
@@ -1100,9 +1080,7 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>148.12</v>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>37.2</v>
       </c>
@@ -1155,9 +1133,7 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>174.26</v>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>21.6</v>
       </c>
@@ -1210,9 +1186,7 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>207.48</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>49.4</v>
       </c>
@@ -1265,9 +1239,7 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>71.25</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>33.8</v>
       </c>
@@ -1320,9 +1292,7 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>209.63</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>24.4</v>
       </c>
@@ -1375,9 +1345,7 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>139.21</v>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>31</v>
       </c>
@@ -1430,9 +1398,7 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>219.72</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>62.4</v>
       </c>
@@ -1485,9 +1451,7 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>354.85</v>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>28</v>
       </c>
@@ -1540,9 +1504,7 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
-        <v>127.24</v>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>21.6</v>
       </c>
@@ -1595,9 +1557,7 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>242.27</v>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
         <v>68.7</v>
       </c>
@@ -1650,9 +1610,7 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>289.52</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>35.5</v>
       </c>
@@ -1709,9 +1667,7 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
-        <v>31.93</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
         <v>90.8</v>
       </c>
@@ -1764,9 +1720,7 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
-        <v>65.93000000000001</v>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
         <v>155.3</v>
       </c>
@@ -1819,9 +1773,7 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
-        <v>45.47</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
         <v>25.1</v>
       </c>
@@ -1874,9 +1826,7 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
-        <v>235.55</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
         <v>89.09999999999999</v>
       </c>
@@ -1933,9 +1883,7 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
-        <v>360.45</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>36.4</v>
       </c>
@@ -1988,9 +1936,7 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
-        <v>1769.32</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
         <v>52</v>
       </c>
@@ -2043,9 +1989,7 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
-        <v>270.41</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
         <v>33.1</v>
       </c>
@@ -2098,9 +2042,7 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>164.59</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>34.8</v>
       </c>
@@ -2153,9 +2095,7 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>104.69</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
         <v>40.8</v>
       </c>
@@ -2208,9 +2148,7 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
-        <v>55.85</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
         <v>40.2</v>
       </c>
@@ -2263,9 +2201,7 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
-        <v>539.39</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
         <v>206.1</v>
       </c>
@@ -2318,9 +2254,7 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
-        <v>362.13</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>58.9</v>
       </c>
@@ -2373,9 +2307,7 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
-        <v>88.34</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>15.2</v>
       </c>
@@ -2428,9 +2360,7 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
-        <v>115.1</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
         <v>22.4</v>
       </c>
@@ -2483,9 +2413,7 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
-        <v>275.35</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
         <v>23.3</v>
       </c>
@@ -2538,9 +2466,7 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>50.43</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
         <v>66.40000000000001</v>
       </c>
@@ -2593,9 +2519,7 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="n">
-        <v>82.39</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
         <v>24</v>
       </c>
@@ -2652,9 +2576,7 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
-        <v>21.58</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
         <v>24.2</v>
       </c>
@@ -2707,9 +2629,7 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="n">
-        <v>34.43</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
         <v>17.2</v>
       </c>
@@ -2762,9 +2682,7 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="n">
-        <v>546.64</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
         <v>18.5</v>
       </c>
@@ -2817,9 +2735,7 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="n">
-        <v>137.85</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>22</v>
       </c>
@@ -2872,9 +2788,7 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="n">
-        <v>283.36</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>21.7</v>
       </c>
@@ -2931,9 +2845,7 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="n">
-        <v>158.33</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
         <v>20.9</v>
       </c>
@@ -2986,9 +2898,7 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="n">
-        <v>1763.36</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
         <v>29.6</v>
       </c>
@@ -3045,9 +2955,7 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="n">
-        <v>106.32</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
         <v>15</v>
       </c>
@@ -3100,9 +3008,7 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="n">
-        <v>351.96</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
         <v>33.9</v>
       </c>
@@ -3155,9 +3061,7 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="n">
-        <v>102.2</v>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
         <v>20.5</v>
       </c>
@@ -3210,9 +3114,7 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="n">
-        <v>166.11</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
         <v>14.9</v>
       </c>
@@ -3269,9 +3171,7 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="n">
-        <v>194.83</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
         <v>111.7</v>
       </c>
@@ -3324,9 +3224,7 @@
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="n">
-        <v>470.14</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
         <v>21.2</v>
       </c>
@@ -3379,9 +3277,7 @@
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="n">
-        <v>1210.5</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
         <v>101.3</v>
       </c>
@@ -3434,9 +3330,7 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="n">
-        <v>77.65000000000001</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
         <v>49.2</v>
       </c>
@@ -3489,9 +3383,7 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="n">
-        <v>963.53</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
         <v>47.5</v>
       </c>
@@ -3542,9 +3434,7 @@
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="n">
-        <v>177.52</v>
-      </c>
+      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
         <v>17.8</v>
       </c>
@@ -3595,9 +3485,7 @@
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="n">
-        <v>72.795</v>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
         <v>11.3</v>
       </c>
@@ -3648,9 +3536,7 @@
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="n">
-        <v>143.95</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
         <v>40.1</v>
       </c>
@@ -3701,9 +3587,7 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="n">
-        <v>9.77</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
         <v>14.6</v>
       </c>
@@ -3754,9 +3638,7 @@
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="n">
-        <v>373.14</v>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
         <v>21.1</v>
       </c>
@@ -3807,9 +3689,7 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="n">
-        <v>96.73999999999999</v>
-      </c>
+      <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
         <v>14</v>
       </c>
@@ -3860,9 +3740,7 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="n">
-        <v>107.38</v>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
         <v>16.4</v>
       </c>
@@ -3913,9 +3791,7 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="n">
-        <v>351.41</v>
-      </c>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
         <v>65.8</v>
       </c>
@@ -3966,9 +3842,7 @@
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="n">
-        <v>603.04</v>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
         <v>39.8</v>
       </c>
@@ -4019,9 +3893,7 @@
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="n">
-        <v>308.63</v>
-      </c>
+      <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
         <v>146.7</v>
       </c>
@@ -4072,9 +3944,7 @@
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="n">
-        <v>106.61</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
         <v>24.5</v>
       </c>
@@ -4125,9 +3995,7 @@
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="n">
-        <v>951.67</v>
-      </c>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
         <v>28.3</v>
       </c>
@@ -4178,9 +4046,7 @@
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="n">
-        <v>111.84</v>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
         <v>24.3</v>
       </c>
@@ -4231,9 +4097,7 @@
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="n">
-        <v>344.6</v>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
         <v>23.4</v>
       </c>
@@ -4288,9 +4152,7 @@
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="n">
-        <v>79.34</v>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
         <v>20.4</v>
       </c>
@@ -4345,9 +4207,7 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="n">
-        <v>53.66</v>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
         <v>35.8</v>
       </c>
@@ -4406,9 +4266,7 @@
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="n">
-        <v>11.16</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
         <v>31.8</v>
       </c>
@@ -4457,9 +4315,7 @@
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="n">
-        <v>147.84</v>
-      </c>
+      <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
         <v>21.6</v>
       </c>
@@ -4514,9 +4370,7 @@
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="n">
-        <v>975.5599999999999</v>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
         <v>40.8</v>
       </c>
@@ -4571,9 +4425,7 @@
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="n">
-        <v>196.695</v>
-      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
         <v>15.6</v>
       </c>
@@ -4628,9 +4480,7 @@
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="n">
-        <v>110.54</v>
-      </c>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
         <v>35.2</v>
       </c>
@@ -4685,9 +4535,7 @@
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="n">
-        <v>114</v>
-      </c>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
         <v>40.1</v>
       </c>
@@ -4742,9 +4590,7 @@
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="n">
-        <v>137.35</v>
-      </c>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
         <v>25</v>
       </c>
@@ -4795,9 +4641,7 @@
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="n">
-        <v>43.67</v>
-      </c>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
         <v>35</v>
       </c>
@@ -4850,9 +4694,7 @@
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="n">
-        <v>242.67</v>
-      </c>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
         <v>23.3</v>
       </c>
@@ -4905,9 +4747,7 @@
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="n">
-        <v>224.57</v>
-      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
         <v>18</v>
       </c>
@@ -4962,9 +4802,7 @@
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="n">
-        <v>336.21</v>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
         <v>47.7</v>
       </c>
@@ -5013,9 +4851,7 @@
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="n">
-        <v>300.53</v>
-      </c>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
         <v>42.1</v>
       </c>
@@ -5068,9 +4904,7 @@
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
-      <c r="M84" t="n">
-        <v>129.3</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
         <v>32.2</v>
       </c>
@@ -5125,9 +4959,7 @@
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="n">
-        <v>517.8200000000001</v>
-      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
         <v>8.1</v>
       </c>
@@ -5182,9 +5014,7 @@
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="n">
-        <v>96.14</v>
-      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
         <v>10</v>
       </c>
@@ -5239,9 +5069,7 @@
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="n">
-        <v>539</v>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
         <v>91.90000000000001</v>
       </c>
@@ -5296,9 +5124,7 @@
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="n">
-        <v>422.46</v>
-      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
         <v>15.7</v>
       </c>
@@ -5353,9 +5179,7 @@
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="n">
-        <v>728.3200000000001</v>
-      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
         <v>30.7</v>
       </c>
@@ -5408,9 +5232,7 @@
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="n">
-        <v>245.29</v>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
         <v>16.8</v>
       </c>
@@ -5463,9 +5285,7 @@
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="n">
-        <v>333.36</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
         <v>5.3</v>
       </c>
@@ -5518,9 +5338,7 @@
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="n">
-        <v>507.78</v>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
         <v>10.3</v>
       </c>
@@ -5575,9 +5393,7 @@
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="n">
-        <v>393.45</v>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
         <v>4.8</v>
       </c>
@@ -5634,9 +5450,7 @@
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
-      <c r="M94" t="n">
-        <v>1745</v>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
         <v>42.3</v>
       </c>
@@ -5693,9 +5507,7 @@
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="n">
-        <v>378.13</v>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
@@ -5728,9 +5540,7 @@
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="n">
-        <v>63.8</v>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
